--- a/research/traditional_assets/database/data/sweden/sweden_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ28"/>
+  <dimension ref="A1:AQ31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.276</v>
+        <v>0.0571</v>
       </c>
       <c r="E2">
-        <v>0.356</v>
+        <v>0.127</v>
       </c>
       <c r="F2">
-        <v>0.472</v>
+        <v>0.117</v>
       </c>
       <c r="G2">
-        <v>0.2409201392291989</v>
+        <v>0.5308326899338813</v>
       </c>
       <c r="H2">
-        <v>0.240269427541731</v>
+        <v>0.530824096952886</v>
       </c>
       <c r="I2">
-        <v>0.4364424902217806</v>
+        <v>-0.1948086794263841</v>
       </c>
       <c r="J2">
-        <v>0.4155400029741918</v>
+        <v>-0.1861861839400979</v>
       </c>
       <c r="K2">
-        <v>2561.229</v>
+        <v>-1051.84</v>
       </c>
       <c r="L2">
-        <v>0.4482575698176187</v>
+        <v>-0.2259610282532918</v>
       </c>
       <c r="M2">
-        <v>385.96</v>
+        <v>441.863</v>
       </c>
       <c r="N2">
-        <v>0.005980066342232521</v>
+        <v>0.01424082382603276</v>
       </c>
       <c r="O2">
-        <v>0.1506932804524703</v>
+        <v>-0.4200857544873746</v>
       </c>
       <c r="P2">
-        <v>365.6</v>
+        <v>422.986</v>
       </c>
       <c r="Q2">
-        <v>0.005664608391336434</v>
+        <v>0.01363243608738068</v>
       </c>
       <c r="R2">
-        <v>0.1427439717416912</v>
+        <v>-0.4021391086096745</v>
       </c>
       <c r="S2">
-        <v>20.36</v>
+        <v>18.877</v>
       </c>
       <c r="T2">
-        <v>0.05275158047466059</v>
+        <v>0.04272138649309853</v>
       </c>
       <c r="U2">
-        <v>1394.076</v>
+        <v>2765.848</v>
       </c>
       <c r="V2">
-        <v>0.02159982113720112</v>
+        <v>0.08914064788765985</v>
       </c>
       <c r="W2">
-        <v>0.2250369264795725</v>
+        <v>-0.03546910755148741</v>
       </c>
       <c r="X2">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y2">
-        <v>0.1811639623880902</v>
+        <v>-0.1079233265921923</v>
       </c>
       <c r="Z2">
-        <v>1.334408661507727</v>
+        <v>0.5113480089396006</v>
       </c>
       <c r="AA2">
-        <v>0.1479873957538154</v>
+        <v>-0.03804411249854125</v>
       </c>
       <c r="AB2">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC2">
-        <v>0.1039098865446301</v>
+        <v>-0.1104983315392461</v>
       </c>
       <c r="AD2">
-        <v>1869.451</v>
+        <v>3585.45</v>
       </c>
       <c r="AE2">
-        <v>0.1167007512146672</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1869.567700751215</v>
+        <v>3585.45</v>
       </c>
       <c r="AG2">
-        <v>475.4917007512147</v>
+        <v>819.6019999999999</v>
       </c>
       <c r="AH2">
-        <v>0.02815162152399624</v>
+        <v>0.1035857252806431</v>
       </c>
       <c r="AI2">
-        <v>0.1475578303847869</v>
+        <v>0.2889680991049883</v>
       </c>
       <c r="AJ2">
-        <v>0.007313391265934868</v>
+        <v>0.02573519714821051</v>
       </c>
       <c r="AK2">
-        <v>0.04216850396577865</v>
+        <v>0.08500399764652757</v>
       </c>
       <c r="AL2">
-        <v>78.175</v>
+        <v>69.709</v>
       </c>
       <c r="AM2">
-        <v>62.95699999999999</v>
+        <v>60.28700000000001</v>
       </c>
       <c r="AN2">
-        <v>0.7845987969869272</v>
+        <v>-4.941665345838703</v>
       </c>
       <c r="AO2">
-        <v>31.89918771985929</v>
+        <v>-13.00875066347243</v>
       </c>
       <c r="AP2">
-        <v>0.199561377317015</v>
+        <v>-1.129620773063379</v>
       </c>
       <c r="AQ2">
-        <v>39.60987658242928</v>
+        <v>-15.04183323104483</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Linc AB (OM:LINC)</t>
+          <t>Coeli Private Equity AB (publ) (NGM:CPE I)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -731,49 +731,52 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9659367396593674</v>
+        <v>0.9829545454545454</v>
       </c>
       <c r="J3">
-        <v>0.8495852687458527</v>
+        <v>0.9829545454545454</v>
       </c>
       <c r="K3">
-        <v>34.9</v>
+        <v>69.2</v>
       </c>
       <c r="L3">
-        <v>0.8491484184914841</v>
+        <v>0.9829545454545454</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>10.77</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.09547872340425534</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.155635838150289</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07943262411347518</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1294797687861272</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.81</v>
+      </c>
+      <c r="T3">
+        <v>0.1680594243268338</v>
       </c>
       <c r="U3">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="V3">
-        <v>0.1584562284279887</v>
+        <v>0.06205673758865248</v>
       </c>
       <c r="X3">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AB3">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -785,7 +788,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-101</v>
+        <v>-7</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -794,22 +797,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1882923191648024</v>
+        <v>-0.06616257088846882</v>
       </c>
       <c r="AK3">
-        <v>-0.3234069804674992</v>
+        <v>-0.045425048669695</v>
       </c>
       <c r="AL3">
-        <v>0.134</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>0.08400000000000001</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="AO3">
-        <v>296.2686567164179</v>
+        <v>9885.714285714286</v>
       </c>
       <c r="AQ3">
-        <v>472.6190476190476</v>
+        <v>-804.6511627906978</v>
       </c>
     </row>
     <row r="4">
@@ -820,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Coeli Private Equity AB (publ) (NGM:CPE I)</t>
+          <t>Case Group AB (publ) (OM:CASE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,58 +832,64 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.9078156312625251</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.9078156312625251</v>
       </c>
       <c r="I4">
-        <v>0.9761904761904762</v>
+        <v>0.0344689378757515</v>
       </c>
       <c r="J4">
-        <v>0.9754761904761905</v>
+        <v>0.0344689378757515</v>
       </c>
       <c r="K4">
-        <v>45.1</v>
+        <v>-0.849</v>
       </c>
       <c r="L4">
-        <v>0.9761904761904762</v>
+        <v>-0.1701402805611222</v>
       </c>
       <c r="M4">
-        <v>11.2</v>
+        <v>0.1</v>
       </c>
       <c r="N4">
-        <v>0.06184428492545554</v>
+        <v>0.002994011976047904</v>
       </c>
       <c r="O4">
-        <v>0.2483370288248337</v>
+        <v>-0.1177856301531213</v>
       </c>
       <c r="P4">
-        <v>6.19</v>
+        <v>0.1</v>
       </c>
       <c r="Q4">
-        <v>0.03418001104362231</v>
+        <v>0.002994011976047904</v>
       </c>
       <c r="R4">
-        <v>0.1372505543237251</v>
+        <v>-0.1177856301531213</v>
       </c>
       <c r="S4">
-        <v>5.009999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.4473214285714285</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.06826347305389222</v>
+      </c>
+      <c r="W4">
+        <v>-0.1337007874015748</v>
       </c>
       <c r="X4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y4">
+        <v>-0.2061550064422797</v>
       </c>
       <c r="AB4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -892,25 +901,31 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>-0.07326478149100257</v>
+      </c>
+      <c r="AK4">
+        <v>-0.6570605187319883</v>
       </c>
       <c r="AL4">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.117</v>
-      </c>
-      <c r="AO4">
-        <v>22550</v>
-      </c>
-      <c r="AQ4">
-        <v>-385.4700854700855</v>
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-13.10344827586207</v>
       </c>
     </row>
     <row r="5">
@@ -921,7 +936,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Case Group AB (publ) (OM:CASE)</t>
+          <t>EQT AB (publ) (OM:EQT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -929,41 +944,44 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="F5">
+        <v>0.2</v>
+      </c>
       <c r="G5">
-        <v>0.17109375</v>
+        <v>0.7046944198405669</v>
       </c>
       <c r="H5">
-        <v>0.17109375</v>
+        <v>0.7046944198405669</v>
       </c>
       <c r="I5">
-        <v>0.36328125</v>
+        <v>0.5382934750516681</v>
       </c>
       <c r="J5">
-        <v>0.334375</v>
+        <v>0.5382934750516681</v>
       </c>
       <c r="K5">
-        <v>4.28</v>
+        <v>817.9</v>
       </c>
       <c r="L5">
-        <v>0.334375</v>
+        <v>0.4829642751697668</v>
       </c>
       <c r="M5">
-        <v>2.72</v>
+        <v>261.2</v>
       </c>
       <c r="N5">
-        <v>0.02477231329690346</v>
+        <v>0.01040152598191281</v>
       </c>
       <c r="O5">
-        <v>0.6355140186915887</v>
+        <v>0.3193544443085952</v>
       </c>
       <c r="P5">
-        <v>2.72</v>
+        <v>261.2</v>
       </c>
       <c r="Q5">
-        <v>0.02477231329690346</v>
+        <v>0.01040152598191281</v>
       </c>
       <c r="R5">
-        <v>0.6355140186915887</v>
+        <v>0.3193544443085952</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -972,46 +990,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2031.2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.08088659867711066</v>
+      </c>
+      <c r="W5">
+        <v>0.2997947364562715</v>
       </c>
       <c r="X5">
-        <v>0.04387296409148227</v>
+        <v>0.07479801359026107</v>
+      </c>
+      <c r="Y5">
+        <v>0.2249967228660105</v>
+      </c>
+      <c r="Z5">
+        <v>0.8401964675530862</v>
+      </c>
+      <c r="AA5">
+        <v>0.4522722762452869</v>
       </c>
       <c r="AB5">
-        <v>0.04387296409148227</v>
+        <v>0.07228787923814849</v>
+      </c>
+      <c r="AC5">
+        <v>0.3799843970071384</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2202.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2202.6</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>171.3999999999999</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.08063907916366152</v>
+      </c>
+      <c r="AI5">
+        <v>0.3906912393351899</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>0.006779231977091411</v>
+      </c>
+      <c r="AK5">
+        <v>0.04752530153888808</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>5.643</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>2.166847024102312</v>
+      </c>
+      <c r="AO5">
+        <v>145.3907496012759</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>0.1686178061977372</v>
+      </c>
+      <c r="AQ5">
+        <v>161.545277334751</v>
       </c>
     </row>
     <row r="6">
@@ -1022,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Flat Capital AB (publ) (OM:FLAT B)</t>
+          <t>NAXS AB (publ) (OM:NAXS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1030,6 +1075,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.131</v>
+      </c>
+      <c r="E6">
+        <v>0.127</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1037,49 +1088,67 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.8640000000000001</v>
+        <v>0.9135802469135803</v>
       </c>
       <c r="J6">
-        <v>0.8640000000000001</v>
+        <v>0.9135802469135803</v>
       </c>
       <c r="K6">
-        <v>3.21</v>
+        <v>13.5</v>
       </c>
       <c r="L6">
-        <v>0.856</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>3.929</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.0618740157480315</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.291037037037037</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>3.51</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.0552755905511811</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.26</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.419</v>
+      </c>
+      <c r="T6">
+        <v>0.1066429116823619</v>
       </c>
       <c r="U6">
-        <v>0.632</v>
+        <v>22</v>
       </c>
       <c r="V6">
-        <v>0.006416243654822335</v>
+        <v>0.3464566929133858</v>
+      </c>
+      <c r="W6">
+        <v>0.154639175257732</v>
       </c>
       <c r="X6">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y6">
+        <v>0.08218495621702711</v>
+      </c>
+      <c r="Z6">
+        <v>0.2842105263157895</v>
+      </c>
+      <c r="AA6">
+        <v>0.2596491228070176</v>
       </c>
       <c r="AB6">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC6">
+        <v>0.1871949037663127</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1091,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-0.632</v>
+        <v>-22</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1100,22 +1169,22 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.006457677688314873</v>
+        <v>-0.5301204819277109</v>
       </c>
       <c r="AK6">
-        <v>-0.02890067678800073</v>
+        <v>-0.3594771241830065</v>
       </c>
       <c r="AL6">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="AM6">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="AO6">
-        <v>98.18181818181819</v>
+        <v>1138.461538461539</v>
       </c>
       <c r="AQ6">
-        <v>98.18181818181819</v>
+        <v>1138.461538461539</v>
       </c>
     </row>
     <row r="7">
@@ -1126,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EQT AB (publ) (OM:EQT)</t>
+          <t>Catella AB (publ) (OM:CAT B)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1134,44 +1203,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F7">
-        <v>0.472</v>
+      <c r="D7">
+        <v>0.0571</v>
+      </c>
+      <c r="E7">
+        <v>0.247</v>
       </c>
       <c r="G7">
-        <v>0.2954017106513634</v>
+        <v>0.09843205574912893</v>
       </c>
       <c r="H7">
-        <v>0.2927114555157541</v>
+        <v>0.09843205574912893</v>
       </c>
       <c r="I7">
-        <v>0.6091088529863294</v>
+        <v>0.3397212543554007</v>
       </c>
       <c r="J7">
-        <v>0.5564638717532554</v>
+        <v>0.2789097781383505</v>
       </c>
       <c r="K7">
-        <v>822</v>
+        <v>44</v>
       </c>
       <c r="L7">
-        <v>0.6009211199649097</v>
+        <v>0.1916376306620209</v>
       </c>
       <c r="M7">
-        <v>255.9</v>
+        <v>7.92</v>
       </c>
       <c r="N7">
-        <v>0.004758778821853562</v>
+        <v>0.02572263721987659</v>
       </c>
       <c r="O7">
-        <v>0.3113138686131387</v>
+        <v>0.18</v>
       </c>
       <c r="P7">
-        <v>255.9</v>
+        <v>7.92</v>
       </c>
       <c r="Q7">
-        <v>0.004758778821853562</v>
+        <v>0.02572263721987659</v>
       </c>
       <c r="R7">
-        <v>0.3113138686131387</v>
+        <v>0.18</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1180,73 +1252,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>458.9</v>
+        <v>144.2</v>
       </c>
       <c r="V7">
-        <v>0.008533816339775692</v>
+        <v>0.4683338746346216</v>
       </c>
       <c r="W7">
-        <v>0.7845757373293881</v>
+        <v>0.2426916712630998</v>
       </c>
       <c r="X7">
-        <v>0.04416512988295024</v>
+        <v>0.09290971025781412</v>
       </c>
       <c r="Y7">
-        <v>0.7404106074464378</v>
+        <v>0.1497819610052857</v>
       </c>
       <c r="Z7">
-        <v>5.706716729244887</v>
+        <v>0.7653333333333333</v>
       </c>
       <c r="AA7">
-        <v>3.175581686154684</v>
+        <v>0.2134589502018843</v>
       </c>
       <c r="AB7">
-        <v>0.04388781532069357</v>
+        <v>0.06890893327516734</v>
       </c>
       <c r="AC7">
-        <v>3.13169387083399</v>
+        <v>0.1445500169267169</v>
       </c>
       <c r="AD7">
-        <v>687.7</v>
+        <v>235.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>687.7</v>
+        <v>235.7</v>
       </c>
       <c r="AG7">
-        <v>228.8000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="AH7">
-        <v>0.0126271528772355</v>
+        <v>0.4335908756438558</v>
       </c>
       <c r="AI7">
-        <v>0.2013232237477678</v>
+        <v>0.5350737797956867</v>
       </c>
       <c r="AJ7">
-        <v>0.004236793813688474</v>
+        <v>0.2290936404606911</v>
       </c>
       <c r="AK7">
-        <v>0.07737571863375045</v>
+        <v>0.3088086398920014</v>
       </c>
       <c r="AL7">
-        <v>23.4</v>
+        <v>7.11</v>
       </c>
       <c r="AM7">
-        <v>17.83</v>
+        <v>3.87</v>
       </c>
       <c r="AN7">
-        <v>0.7899150011486331</v>
+        <v>3.117724867724868</v>
       </c>
       <c r="AO7">
-        <v>35.60683760683761</v>
+        <v>10.9704641350211</v>
       </c>
       <c r="AP7">
-        <v>0.2628072593613601</v>
+        <v>1.21031746031746</v>
       </c>
       <c r="AQ7">
-        <v>46.73022994952328</v>
+        <v>20.15503875968992</v>
       </c>
     </row>
     <row r="8">
@@ -1257,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VNV Global AB (publ) (OM:VNV)</t>
+          <t>Ratos AB (publ) (OM:RATO B)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1266,121 +1338,124 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.427</v>
+        <v>0.0246</v>
       </c>
       <c r="E8">
-        <v>0.42</v>
+        <v>-0.164</v>
+      </c>
+      <c r="F8">
+        <v>0.117</v>
       </c>
       <c r="G8">
-        <v>0.4664015072221059</v>
+        <v>0.08205148963730569</v>
       </c>
       <c r="H8">
-        <v>0.4664015072221059</v>
+        <v>0.08205148963730569</v>
       </c>
       <c r="I8">
-        <v>0.9688088758635127</v>
+        <v>0.05035621761658031</v>
       </c>
       <c r="J8">
-        <v>0.9679393773563585</v>
+        <v>0.04509020793118629</v>
       </c>
       <c r="K8">
-        <v>454.2</v>
+        <v>80.2</v>
       </c>
       <c r="L8">
-        <v>0.9508059451538623</v>
+        <v>0.03246437823834197</v>
       </c>
       <c r="M8">
-        <v>4.76</v>
+        <v>35.1</v>
       </c>
       <c r="N8">
-        <v>0.003559943160571386</v>
+        <v>0.02669810603179433</v>
       </c>
       <c r="O8">
-        <v>0.01047996477322765</v>
+        <v>0.4376558603491272</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>35.1</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.02669810603179433</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.4376558603491272</v>
       </c>
       <c r="S8">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>58.5</v>
+        <v>171.2</v>
       </c>
       <c r="V8">
-        <v>0.04375140228853489</v>
+        <v>0.1302198220126264</v>
       </c>
       <c r="W8">
-        <v>0.5031571950814223</v>
+        <v>0.05872446364501721</v>
       </c>
       <c r="X8">
-        <v>0.04642561728361626</v>
+        <v>0.0896167597808198</v>
       </c>
       <c r="Y8">
-        <v>0.456731577797806</v>
+        <v>-0.03089229613580259</v>
       </c>
       <c r="Z8">
-        <v>0.5240811848601207</v>
+        <v>3.070727159726538</v>
       </c>
       <c r="AA8">
-        <v>0.5072788157576879</v>
+        <v>0.1384597261320107</v>
       </c>
       <c r="AB8">
-        <v>0.04362266586203536</v>
+        <v>0.07164749297570459</v>
       </c>
       <c r="AC8">
-        <v>0.4636561498956525</v>
+        <v>0.06681223315630612</v>
       </c>
       <c r="AD8">
-        <v>149.4</v>
+        <v>844.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>149.4</v>
+        <v>844.4</v>
       </c>
       <c r="AG8">
-        <v>90.90000000000001</v>
+        <v>673.2</v>
       </c>
       <c r="AH8">
-        <v>0.1005045408678103</v>
+        <v>0.39108887962577</v>
       </c>
       <c r="AI8">
-        <v>0.09110867178924259</v>
+        <v>0.404502994011976</v>
       </c>
       <c r="AJ8">
-        <v>0.06365546218487396</v>
+        <v>0.3386488253936315</v>
       </c>
       <c r="AK8">
-        <v>0.0574843483210017</v>
+        <v>0.3513019882064395</v>
       </c>
       <c r="AL8">
-        <v>7.78</v>
+        <v>30.2</v>
       </c>
       <c r="AM8">
-        <v>7.485</v>
+        <v>29.57</v>
       </c>
       <c r="AN8">
-        <v>0.3227478937135451</v>
+        <v>5.017231134878193</v>
       </c>
       <c r="AO8">
-        <v>59.48586118251928</v>
+        <v>4.119205298013245</v>
       </c>
       <c r="AP8">
-        <v>0.1963707064160726</v>
+        <v>4</v>
       </c>
       <c r="AQ8">
-        <v>61.83032732130928</v>
+        <v>4.206966520121745</v>
       </c>
     </row>
     <row r="9">
@@ -1391,7 +1466,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VEF AB (Publ) (OM:VEFAB)</t>
+          <t>eBlitz Group AB (publ) (NGM:EBLITZ)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1400,22 +1475,22 @@
         </is>
       </c>
       <c r="G9">
-        <v>0.5747460087082729</v>
+        <v>0.2111111111111111</v>
       </c>
       <c r="H9">
-        <v>0.5747460087082729</v>
+        <v>0.2111111111111111</v>
       </c>
       <c r="I9">
-        <v>0.9310595065312046</v>
+        <v>0.2013071895424837</v>
       </c>
       <c r="J9">
-        <v>0.9305870719650491</v>
+        <v>0.2013071895424837</v>
       </c>
       <c r="K9">
-        <v>128</v>
+        <v>0.273</v>
       </c>
       <c r="L9">
-        <v>0.9288824383164005</v>
+        <v>0.1784313725490196</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1439,70 +1514,70 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>11.5</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="V9">
-        <v>0.01650401836969001</v>
+        <v>0.4677685950413223</v>
       </c>
       <c r="W9">
-        <v>0.4772557792692021</v>
+        <v>0.1034090909090909</v>
       </c>
       <c r="X9">
-        <v>0.04387352146442904</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y9">
-        <v>0.4333822578047731</v>
+        <v>0.03095487186838605</v>
       </c>
       <c r="Z9">
-        <v>0.5177803829620946</v>
+        <v>0.6083499005964215</v>
       </c>
       <c r="AA9">
-        <v>0.4818397305016374</v>
+        <v>0.1224652087475149</v>
       </c>
       <c r="AB9">
-        <v>0.04387299278522145</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC9">
-        <v>0.4379667377164159</v>
+        <v>0.05001098970681005</v>
       </c>
       <c r="AD9">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>-11.483</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="AH9">
-        <v>2.439664933547833e-05</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>3.070714952756147e-05</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.01675574952905006</v>
+        <v>-0.8788819875776397</v>
       </c>
       <c r="AK9">
-        <v>-0.02118177441401026</v>
+        <v>-0.2374161073825503</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.06900000000000001</v>
+        <v>-0.006</v>
       </c>
       <c r="AN9">
-        <v>0.000132398753894081</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>-0.08943146417445483</v>
+        <v>-1.752321981424148</v>
       </c>
       <c r="AQ9">
-        <v>-1859.420289855072</v>
+        <v>-51.33333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -1513,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AB Traction (OM:TRAC B)</t>
+          <t>Stockwik Förvaltning AB (publ) (OM:STWK)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1522,109 +1597,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.289</v>
-      </c>
-      <c r="E10">
-        <v>0.297</v>
+        <v>0.515</v>
+      </c>
+      <c r="F10">
+        <v>-0.11</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.08686244204018546</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.08686244204018546</v>
       </c>
       <c r="I10">
-        <v>0.9926590538336053</v>
+        <v>0.05285935085007728</v>
       </c>
       <c r="J10">
-        <v>0.9926590538336053</v>
+        <v>0.02642967542503864</v>
       </c>
       <c r="K10">
-        <v>121.7</v>
+        <v>-0.018</v>
       </c>
       <c r="L10">
-        <v>0.9926590538336053</v>
+        <v>-0.0002782071097372488</v>
       </c>
       <c r="M10">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.007463016118348422</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.02777321281840591</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.38</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.007463016118348422</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.02777321281840591</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>55.7</v>
+        <v>13.4</v>
       </c>
       <c r="V10">
-        <v>0.1229852064473394</v>
+        <v>1.107438016528926</v>
       </c>
       <c r="W10">
-        <v>0.4017827665896336</v>
+        <v>-0.000631578947368421</v>
       </c>
       <c r="X10">
-        <v>0.04387296409148227</v>
+        <v>0.1755857654196741</v>
       </c>
       <c r="Y10">
-        <v>0.3579098024981513</v>
+        <v>-0.1762173443670425</v>
       </c>
       <c r="Z10">
-        <v>0.4615963855421687</v>
+        <v>2.662551440329219</v>
       </c>
       <c r="AA10">
-        <v>0.4582078313253013</v>
+        <v>0.07037037037037039</v>
       </c>
       <c r="AB10">
-        <v>0.04387296409148227</v>
+        <v>0.07081593131935471</v>
       </c>
       <c r="AC10">
-        <v>0.414334867233819</v>
+        <v>-0.0004455609489843193</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="AG10">
-        <v>-55.7</v>
+        <v>33.3</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.7942176870748299</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.6758321273516643</v>
       </c>
       <c r="AJ10">
-        <v>-0.1402316213494461</v>
+        <v>0.7334801762114538</v>
       </c>
       <c r="AK10">
-        <v>-0.1494098712446352</v>
+        <v>0.5978456014362658</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>2.763</v>
+      </c>
+      <c r="AN10">
+        <v>8.150087260034903</v>
+      </c>
+      <c r="AO10">
+        <v>1.055555555555555</v>
+      </c>
+      <c r="AP10">
+        <v>5.81151832460733</v>
+      </c>
+      <c r="AQ10">
+        <v>1.237785016286645</v>
       </c>
     </row>
     <row r="11">
@@ -1635,7 +1719,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bure Equity AB (publ) (OM:BURE)</t>
+          <t>Seafire AB (publ) (OM:SEAF)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1644,121 +1728,115 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.06150000000000001</v>
-      </c>
-      <c r="E11">
-        <v>0.0694</v>
+        <v>1.289</v>
       </c>
       <c r="G11">
-        <v>0.5723920218108767</v>
+        <v>0.0439124487004104</v>
       </c>
       <c r="H11">
-        <v>0.5723920218108767</v>
+        <v>0.04336525307797538</v>
       </c>
       <c r="I11">
-        <v>0.9375807145931985</v>
+        <v>0.05759233926128592</v>
       </c>
       <c r="J11">
-        <v>0.9374165047276837</v>
+        <v>0.02879616963064296</v>
       </c>
       <c r="K11">
-        <v>649.7</v>
+        <v>0.367</v>
       </c>
       <c r="L11">
-        <v>0.9322714880183671</v>
+        <v>0.005020519835841314</v>
       </c>
       <c r="M11">
-        <v>24.79</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.006901447661469933</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.03815607203324611</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>16.9</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.00470489977728285</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.02601200554101893</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>7.890000000000001</v>
-      </c>
-      <c r="T11">
-        <v>0.318273497377975</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>76.2</v>
+        <v>21.9</v>
       </c>
       <c r="V11">
-        <v>0.02121380846325167</v>
+        <v>0.3821989528795812</v>
       </c>
       <c r="W11">
-        <v>0.3424520345772718</v>
+        <v>0.01548523206751055</v>
       </c>
       <c r="X11">
-        <v>0.0438766021091759</v>
+        <v>0.0995021090103827</v>
       </c>
       <c r="Y11">
-        <v>0.2985754324680959</v>
+        <v>-0.08401687694287215</v>
       </c>
       <c r="Z11">
-        <v>0.400862812769629</v>
+        <v>2.428571428571429</v>
       </c>
       <c r="AA11">
-        <v>0.3757754168218135</v>
+        <v>0.06993355481727576</v>
       </c>
       <c r="AB11">
-        <v>0.04387256757372453</v>
+        <v>0.07141657282129167</v>
       </c>
       <c r="AC11">
-        <v>0.3319028492480889</v>
+        <v>-0.001483018004015915</v>
       </c>
       <c r="AD11">
-        <v>0.572</v>
+        <v>58</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.572</v>
+        <v>58</v>
       </c>
       <c r="AG11">
-        <v>-75.628</v>
+        <v>36.1</v>
       </c>
       <c r="AH11">
-        <v>0.0001592174074729748</v>
+        <v>0.5030355594102341</v>
       </c>
       <c r="AI11">
-        <v>0.0002206388342863491</v>
+        <v>0.5440900562851783</v>
       </c>
       <c r="AJ11">
-        <v>-0.02150739455324977</v>
+        <v>0.386509635974304</v>
       </c>
       <c r="AK11">
-        <v>-0.03005557427813845</v>
+        <v>0.4262101534828808</v>
       </c>
       <c r="AL11">
-        <v>0.88</v>
+        <v>4.75</v>
       </c>
       <c r="AM11">
-        <v>0.5369999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="AN11">
-        <v>0.0008736826027188024</v>
+        <v>7.988980716253444</v>
       </c>
       <c r="AO11">
-        <v>742.5</v>
+        <v>0.8863157894736842</v>
       </c>
       <c r="AP11">
-        <v>-0.1155155032839468</v>
+        <v>4.972451790633609</v>
       </c>
       <c r="AQ11">
-        <v>1216.759776536313</v>
+        <v>0.8863157894736842</v>
       </c>
     </row>
     <row r="12">
@@ -1769,7 +1847,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dividend Sweden AB (publ) (NGM:DIVI B)</t>
+          <t>Transferator AB (publ) (NGM:TRAN A)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1778,115 +1856,115 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.358</v>
-      </c>
-      <c r="E12">
-        <v>0.6579999999999999</v>
+        <v>0.0336</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.08067940552016985</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.08067940552016985</v>
       </c>
       <c r="I12">
-        <v>0.1728323699421965</v>
+        <v>0.02016985138004246</v>
       </c>
       <c r="J12">
-        <v>0.1487828216907091</v>
+        <v>0.02016985138004246</v>
       </c>
       <c r="K12">
-        <v>5.87</v>
+        <v>8.59</v>
       </c>
       <c r="L12">
-        <v>0.3393063583815029</v>
+        <v>1.823779193205945</v>
       </c>
       <c r="M12">
-        <v>5.8</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.4360902255639098</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.9880749574105622</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>5.8</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.4360902255639098</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.9880749574105622</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0.171</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>0.01285714285714286</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>0.7310087173100872</v>
+        <v>1.199720670391061</v>
       </c>
       <c r="X12">
-        <v>0.04387296409148227</v>
+        <v>0.0760930027613908</v>
       </c>
       <c r="Y12">
-        <v>0.687135753218605</v>
+        <v>1.123627667629671</v>
       </c>
       <c r="Z12">
-        <v>2.235142118863049</v>
+        <v>0.690615835777126</v>
       </c>
       <c r="AA12">
-        <v>0.3325507513241947</v>
+        <v>0.01392961876832845</v>
       </c>
       <c r="AB12">
-        <v>0.04387296409148227</v>
+        <v>0.07256861103061113</v>
       </c>
       <c r="AC12">
-        <v>0.2886777872327124</v>
+        <v>-0.05863899226228268</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AG12">
-        <v>-0.171</v>
+        <v>1.31</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.1198536139066789</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.2179700499168054</v>
       </c>
       <c r="AJ12">
-        <v>-0.0130246020260492</v>
+        <v>0.1198536139066789</v>
       </c>
       <c r="AK12">
-        <v>-0.01995565410199556</v>
+        <v>0.2179700499168054</v>
       </c>
       <c r="AL12">
-        <v>0.298</v>
+        <v>0.397</v>
       </c>
       <c r="AM12">
-        <v>-2.282</v>
+        <v>0.397</v>
+      </c>
+      <c r="AN12">
+        <v>2.462406015037594</v>
       </c>
       <c r="AO12">
-        <v>10.03355704697987</v>
+        <v>0.2392947103274559</v>
+      </c>
+      <c r="AP12">
+        <v>2.462406015037594</v>
       </c>
       <c r="AQ12">
-        <v>-1.310254163014899</v>
+        <v>0.2392947103274559</v>
       </c>
     </row>
     <row r="13">
@@ -1897,7 +1975,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAXS AB (publ) (OM:NAXS)</t>
+          <t>ACQ Bure AB (publ) (OM:ACQ SPAC)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1905,80 +1983,56 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D13">
-        <v>0.276</v>
-      </c>
-      <c r="E13">
-        <v>0.356</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0.907514450867052</v>
-      </c>
-      <c r="J13">
-        <v>0.907514450867052</v>
-      </c>
       <c r="K13">
-        <v>15.8</v>
-      </c>
-      <c r="L13">
-        <v>0.9132947976878613</v>
+        <v>-0.855</v>
       </c>
       <c r="M13">
-        <v>4.1</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.05131414267834793</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.2594936708860759</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.05131414267834793</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.2594936708860759</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>30.3</v>
+        <v>27.3</v>
       </c>
       <c r="V13">
-        <v>0.3792240300375469</v>
+        <v>0.08584905660377359</v>
       </c>
       <c r="W13">
-        <v>0.2095490716180371</v>
+        <v>-0.002172808132147395</v>
       </c>
       <c r="X13">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y13">
-        <v>0.1656761075265548</v>
+        <v>-0.07462702717285224</v>
       </c>
       <c r="Z13">
-        <v>0.3365758754863813</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0.3054474708171206</v>
+        <v>-0.003223997757218951</v>
       </c>
       <c r="AB13">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC13">
-        <v>0.2615745067256383</v>
+        <v>-0.0756782167979238</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -1990,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-30.3</v>
+        <v>-27.3</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -1999,22 +2053,19 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.6108870967741935</v>
+        <v>-0.09391124871001033</v>
       </c>
       <c r="AK13">
-        <v>-0.531578947368421</v>
+        <v>-0.09687721788502483</v>
       </c>
       <c r="AL13">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>0.06999999999999999</v>
-      </c>
-      <c r="AO13">
-        <v>215.0684931506849</v>
+        <v>-0.306</v>
       </c>
       <c r="AQ13">
-        <v>224.2857142857143</v>
+        <v>3.758169934640523</v>
       </c>
     </row>
     <row r="14">
@@ -2025,7 +2076,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ratos AB (publ) (OM:RATO B)</t>
+          <t>Aligro Planet Acquisition Company AB (publ) (OM:APAC SPAC A)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2033,119 +2084,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.0292</v>
-      </c>
-      <c r="G14">
-        <v>0.09390791122609857</v>
-      </c>
-      <c r="H14">
-        <v>0.09390791122609857</v>
-      </c>
-      <c r="I14">
-        <v>0.0750293083235639</v>
-      </c>
-      <c r="J14">
-        <v>0.05122254045043308</v>
-      </c>
       <c r="K14">
-        <v>268.2</v>
-      </c>
-      <c r="L14">
-        <v>0.1084205845494603</v>
+        <v>-0.861</v>
       </c>
       <c r="M14">
-        <v>58.3</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.02749092280850663</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.2173750932140194</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>58.3</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.02749092280850663</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.2173750932140194</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>318.7</v>
+        <v>0.949</v>
       </c>
       <c r="V14">
-        <v>0.150280567737068</v>
+        <v>0.008435555555555556</v>
       </c>
       <c r="W14">
-        <v>0.2469840685145961</v>
+        <v>-0.007493472584856396</v>
       </c>
       <c r="X14">
-        <v>0.05115533115816712</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y14">
-        <v>0.195828737356429</v>
+        <v>-0.07994769162556126</v>
       </c>
       <c r="Z14">
-        <v>4.867571822117274</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>0.2493293945537903</v>
+        <v>-0.005035335689045936</v>
       </c>
       <c r="AB14">
-        <v>0.04327099678191016</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC14">
-        <v>0.2060583977718801</v>
+        <v>-0.07748955472975079</v>
       </c>
       <c r="AD14">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>676</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>357.3</v>
+        <v>-0.949</v>
       </c>
       <c r="AH14">
-        <v>0.2417134479922766</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>0.3122401847575058</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>0.1441888619854721</v>
+        <v>-0.008507319522012353</v>
       </c>
       <c r="AK14">
-        <v>0.1935221794941234</v>
+        <v>-0.01069283726380548</v>
       </c>
       <c r="AL14">
-        <v>30.4</v>
+        <v>0.231</v>
       </c>
       <c r="AM14">
-        <v>28.69</v>
-      </c>
-      <c r="AN14">
-        <v>2.756933115823817</v>
+        <v>0.201</v>
       </c>
       <c r="AO14">
-        <v>6.105263157894737</v>
-      </c>
-      <c r="AP14">
-        <v>1.457177814029364</v>
+        <v>-2.467532467532467</v>
       </c>
       <c r="AQ14">
-        <v>6.469153014987801</v>
+        <v>-2.835820895522388</v>
       </c>
     </row>
     <row r="15">
@@ -2156,7 +2180,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Seafire AB (publ) (OM:SEAF)</t>
+          <t>Flat Capital AB (publ) (OM:FLAT B)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2165,22 +2189,22 @@
         </is>
       </c>
       <c r="G15">
-        <v>0.08480211081794195</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.08390501319261215</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0.05329815303430079</v>
+        <v>-2.205882352941176</v>
       </c>
       <c r="J15">
-        <v>0.05329815303430079</v>
+        <v>-2.205882352941176</v>
       </c>
       <c r="K15">
-        <v>-1.08</v>
+        <v>-0.224</v>
       </c>
       <c r="L15">
-        <v>-0.02849604221635884</v>
+        <v>-1.647058823529412</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2204,73 +2228,64 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>32</v>
+        <v>6.98</v>
       </c>
       <c r="V15">
-        <v>0.4444444444444444</v>
+        <v>0.2406896551724138</v>
       </c>
       <c r="W15">
-        <v>-0.3898916967509026</v>
+        <v>-0.009955555555555556</v>
       </c>
       <c r="X15">
-        <v>0.05605735528542197</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y15">
-        <v>-0.4459490520363245</v>
+        <v>-0.08240977459626041</v>
       </c>
       <c r="Z15">
-        <v>3.211864406779661</v>
+        <v>0.006219132979696361</v>
       </c>
       <c r="AA15">
-        <v>0.1711864406779661</v>
+        <v>-0.01371867569050668</v>
       </c>
       <c r="AB15">
-        <v>0.04428205432688843</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC15">
-        <v>0.1269043863510777</v>
+        <v>-0.08617289473121154</v>
       </c>
       <c r="AD15">
-        <v>38.4</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>38.4</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>6.399999999999999</v>
+        <v>-6.98</v>
       </c>
       <c r="AH15">
-        <v>0.3478260869565217</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>0.6183574879227054</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>0.08163265306122447</v>
+        <v>-0.3169845594913715</v>
       </c>
       <c r="AK15">
-        <v>0.212624584717608</v>
+        <v>-0.2735109717868339</v>
       </c>
       <c r="AL15">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>3.31</v>
-      </c>
-      <c r="AN15">
-        <v>13.81294964028777</v>
-      </c>
-      <c r="AO15">
-        <v>0.6029850746268657</v>
-      </c>
-      <c r="AP15">
-        <v>2.302158273381294</v>
+        <v>-0.076</v>
       </c>
       <c r="AQ15">
-        <v>0.6102719033232629</v>
+        <v>3.947368421052631</v>
       </c>
     </row>
     <row r="16">
@@ -2281,7 +2296,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Havsfrun Investment AB (publ) (OM:HAV B)</t>
+          <t>AB Traction (OM:TRAC B)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2289,44 +2304,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.341</v>
-      </c>
-      <c r="G16">
-        <v>-1.390728476821192</v>
-      </c>
-      <c r="H16">
-        <v>-1.390728476821192</v>
-      </c>
-      <c r="I16">
-        <v>0.4880794701986755</v>
-      </c>
-      <c r="J16">
-        <v>0.4880794701986755</v>
-      </c>
       <c r="K16">
-        <v>0.735</v>
-      </c>
-      <c r="L16">
-        <v>0.4867549668874172</v>
+        <v>-9.69</v>
       </c>
       <c r="M16">
-        <v>2.08</v>
+        <v>6.46</v>
       </c>
       <c r="N16">
-        <v>0.05265822784810126</v>
+        <v>0.02157648630594523</v>
       </c>
       <c r="O16">
-        <v>2.829931972789116</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="P16">
-        <v>2.08</v>
+        <v>6.46</v>
       </c>
       <c r="Q16">
-        <v>0.05265822784810126</v>
+        <v>0.02157648630594523</v>
       </c>
       <c r="R16">
-        <v>2.829931972789116</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2335,31 +2332,31 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>10.2</v>
+        <v>20</v>
       </c>
       <c r="V16">
-        <v>0.2582278481012658</v>
+        <v>0.06680026720106881</v>
       </c>
       <c r="W16">
-        <v>0.04323529411764706</v>
+        <v>-0.0233437725849193</v>
       </c>
       <c r="X16">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y16">
-        <v>-0.0006376699738352143</v>
+        <v>-0.09579799162562415</v>
       </c>
       <c r="Z16">
-        <v>0.2556721977649847</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>0.1247883508296647</v>
+        <v>-0.02657595112468759</v>
       </c>
       <c r="AB16">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC16">
-        <v>0.08091538673818247</v>
+        <v>-0.09903017016539245</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2371,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>-10.2</v>
+        <v>-20</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2380,28 +2377,16 @@
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.3481228668941979</v>
+        <v>-0.07158196134574088</v>
       </c>
       <c r="AK16">
-        <v>-1.758620689655172</v>
+        <v>-0.06635700066357002</v>
       </c>
       <c r="AL16">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>0.002</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-      <c r="AO16">
-        <v>184.25</v>
-      </c>
-      <c r="AP16">
-        <v>-13.82113821138211</v>
-      </c>
-      <c r="AQ16">
-        <v>368.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2412,7 +2397,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stockwik Förvaltning AB (publ) (OM:STWK)</t>
+          <t>DS Plattformen AB (NGM:DSPAB B)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2421,115 +2406,112 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.6609999999999999</v>
+        <v>-0.124</v>
       </c>
       <c r="G17">
-        <v>0.04661290322580645</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0.04661290322580645</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0.025</v>
+        <v>-0.0944927536231884</v>
       </c>
       <c r="J17">
-        <v>0.025</v>
+        <v>-0.0944927536231884</v>
       </c>
       <c r="K17">
-        <v>-2.59</v>
+        <v>-0.31</v>
       </c>
       <c r="L17">
-        <v>-0.04177419354838709</v>
+        <v>-0.08985507246376812</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>4.11</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>2.024630541871922</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-13.25806451612903</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>4.11</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>2.024630541871922</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-13.25806451612903</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>23.5</v>
+        <v>0.045</v>
       </c>
       <c r="V17">
-        <v>0.376</v>
+        <v>0.02216748768472906</v>
       </c>
       <c r="W17">
-        <v>-0.185</v>
+        <v>-0.03546910755148741</v>
       </c>
       <c r="X17">
-        <v>0.06200333818806454</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y17">
-        <v>-0.2470033381880645</v>
+        <v>-0.1079233265921923</v>
       </c>
       <c r="Z17">
-        <v>2.828467153284671</v>
+        <v>0.4026140739876298</v>
       </c>
       <c r="AA17">
-        <v>0.07071167883211678</v>
+        <v>-0.03804411249854125</v>
       </c>
       <c r="AB17">
-        <v>0.04439335898504979</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC17">
-        <v>0.02631831984706699</v>
+        <v>-0.1104983315392461</v>
       </c>
       <c r="AD17">
-        <v>49.6</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>49.6</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>26.1</v>
+        <v>-0.045</v>
       </c>
       <c r="AH17">
-        <v>0.4424620874219447</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.6350832266325225</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>0.2945823927765238</v>
+        <v>-0.02267002518891688</v>
       </c>
       <c r="AK17">
-        <v>0.478021978021978</v>
+        <v>-0.1136363636363636</v>
       </c>
       <c r="AL17">
-        <v>3.31</v>
+        <v>2.43</v>
       </c>
       <c r="AM17">
-        <v>3.161</v>
-      </c>
-      <c r="AN17">
-        <v>11.725768321513</v>
+        <v>2.43</v>
       </c>
       <c r="AO17">
-        <v>0.4682779456193353</v>
-      </c>
-      <c r="AP17">
-        <v>6.170212765957446</v>
+        <v>-0.1341563786008231</v>
       </c>
       <c r="AQ17">
-        <v>0.4903511546978804</v>
+        <v>-0.1341563786008231</v>
       </c>
     </row>
     <row r="18">
@@ -2540,7 +2522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Transferator AB (publ) (NGM:TRAN A)</t>
+          <t>Havsfrun Investment AB (publ) (OM:HAV B)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2548,119 +2530,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D18">
-        <v>-0.00468</v>
-      </c>
-      <c r="E18">
-        <v>0.613</v>
-      </c>
-      <c r="G18">
-        <v>0.206423982869379</v>
-      </c>
-      <c r="H18">
-        <v>0.206423982869379</v>
-      </c>
-      <c r="I18">
-        <v>0.02548179871520342</v>
-      </c>
-      <c r="J18">
-        <v>0.02548179871520342</v>
-      </c>
       <c r="K18">
-        <v>1.65</v>
-      </c>
-      <c r="L18">
-        <v>0.3533190578158458</v>
+        <v>-0.624</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.05828877005347594</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.6606060606060606</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.09</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.05828877005347594</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.6606060606060606</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>2.14</v>
+        <v>9.43</v>
       </c>
       <c r="V18">
-        <v>0.1144385026737968</v>
+        <v>0.5482558139534883</v>
       </c>
       <c r="W18">
-        <v>0.2405247813411079</v>
+        <v>-0.039</v>
       </c>
       <c r="X18">
-        <v>0.04607201865188583</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y18">
-        <v>0.194452762689222</v>
+        <v>-0.1114542190407048</v>
       </c>
       <c r="Z18">
-        <v>0.7959775012783364</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>0.02028293846940515</v>
+        <v>-0.08758620689655172</v>
       </c>
       <c r="AB18">
-        <v>0.04418864298854867</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC18">
-        <v>-0.02390570451914352</v>
+        <v>-0.1600404259372566</v>
       </c>
       <c r="AD18">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>-0.3400000000000001</v>
+        <v>-9.43</v>
       </c>
       <c r="AH18">
-        <v>0.0878048780487805</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>0.2008928571428571</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-0.01851851851851852</v>
+        <v>-1.213642213642214</v>
       </c>
       <c r="AK18">
-        <v>-0.04985337243401761</v>
+        <v>-3.669260700389104</v>
       </c>
       <c r="AL18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>2.643171806167401</v>
+        <v>-0</v>
       </c>
       <c r="AP18">
-        <v>-0.499265785609398</v>
-      </c>
-      <c r="AQ18">
-        <v>-0.08500000000000001</v>
+        <v>18.59960552268245</v>
       </c>
     </row>
     <row r="19">
@@ -2671,7 +2626,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Catella AB (publ) (OM:CAT B)</t>
+          <t>First Venture Sweden AB (publ) (OM:FIRST B)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2679,122 +2634,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D19">
-        <v>-0.0317</v>
-      </c>
-      <c r="E19">
-        <v>-0.276</v>
-      </c>
       <c r="G19">
-        <v>0.2735309412376495</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.2735309412376495</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>0.01903276131045242</v>
+        <v>-110</v>
       </c>
       <c r="J19">
-        <v>0.009516380655226208</v>
+        <v>-110</v>
       </c>
       <c r="K19">
-        <v>8.119999999999999</v>
+        <v>-2.65</v>
       </c>
       <c r="L19">
-        <v>0.0422256890275611</v>
+        <v>-203.8461538461538</v>
       </c>
       <c r="M19">
-        <v>9.140000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.01988685813751088</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>1.125615763546798</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>9.140000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.01988685813751088</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>1.125615763546798</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>147.2</v>
+        <v>3.67</v>
       </c>
       <c r="V19">
-        <v>0.320278503046127</v>
+        <v>0.2621428571428571</v>
       </c>
       <c r="W19">
-        <v>0.04650630011454753</v>
+        <v>-0.07507082152974505</v>
       </c>
       <c r="X19">
-        <v>0.05709028466291082</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y19">
-        <v>-0.01058398454836329</v>
+        <v>-0.1475250405704499</v>
       </c>
       <c r="Z19">
-        <v>1.133176193282263</v>
+        <v>0.0009352517985611511</v>
       </c>
       <c r="AA19">
-        <v>0.0107837360047142</v>
+        <v>-0.1028776978417266</v>
       </c>
       <c r="AB19">
-        <v>0.04296021162722075</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC19">
-        <v>-0.03217647562250655</v>
+        <v>-0.1753319168824315</v>
       </c>
       <c r="AD19">
-        <v>265.9</v>
+        <v>0</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>265.9</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>118.7</v>
+        <v>-3.67</v>
       </c>
       <c r="AH19">
-        <v>0.3665058580289455</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>0.5793028322440087</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>0.2052567871347052</v>
+        <v>-0.3552758954501452</v>
       </c>
       <c r="AK19">
-        <v>0.3806927517639513</v>
+        <v>-0.1712552496500233</v>
       </c>
       <c r="AL19">
-        <v>7.43</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.83</v>
-      </c>
-      <c r="AN19">
-        <v>27.35596707818929</v>
-      </c>
-      <c r="AO19">
-        <v>0.4925975773889637</v>
-      </c>
-      <c r="AP19">
-        <v>12.2119341563786</v>
+        <v>-0.115</v>
       </c>
       <c r="AQ19">
-        <v>0.6277873070325901</v>
+        <v>12.43478260869565</v>
       </c>
     </row>
     <row r="20">
@@ -2805,7 +2742,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EOS Russia (OM:EOS)</t>
+          <t>VEF AB (Publ) (OM:VEFAB)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2813,35 +2750,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D20">
-        <v>-0.344</v>
-      </c>
-      <c r="G20">
-        <v>-18.95161290322581</v>
-      </c>
-      <c r="H20">
-        <v>-18.95161290322581</v>
-      </c>
-      <c r="I20">
-        <v>-0.2805848288739249</v>
-      </c>
-      <c r="J20">
-        <v>-0.2805848288739249</v>
-      </c>
       <c r="K20">
-        <v>-0.278</v>
-      </c>
-      <c r="L20">
-        <v>-0.280241935483871</v>
+        <v>-107.9</v>
       </c>
       <c r="M20">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="N20">
-        <v>0.02419871794871795</v>
+        <v>0.005140758873929009</v>
       </c>
       <c r="O20">
-        <v>-5.431654676258993</v>
+        <v>-0.01167747914735866</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2853,79 +2772,79 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="T20">
         <v>1</v>
       </c>
       <c r="U20">
-        <v>5.67</v>
+        <v>10.7</v>
       </c>
       <c r="V20">
-        <v>0.09086538461538461</v>
+        <v>0.04365565075479396</v>
       </c>
       <c r="W20">
-        <v>-0.00349685534591195</v>
+        <v>-0.1949060693641619</v>
       </c>
       <c r="X20">
-        <v>0.04393838956802826</v>
+        <v>0.07716399723928261</v>
       </c>
       <c r="Y20">
-        <v>-0.04743524491394021</v>
+        <v>-0.2720700666034445</v>
       </c>
       <c r="Z20">
-        <v>0.01313164594507894</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>-0.003684540630332944</v>
+        <v>-0.2053062346320075</v>
       </c>
       <c r="AB20">
-        <v>0.04386585241601999</v>
+        <v>0.07214512564463464</v>
       </c>
       <c r="AC20">
-        <v>-0.04755039304635293</v>
+        <v>-0.2774513602766421</v>
       </c>
       <c r="AD20">
-        <v>0.062</v>
+        <v>43.2</v>
       </c>
       <c r="AE20">
-        <v>0.1167007512146672</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.1787007512146672</v>
+        <v>43.2</v>
       </c>
       <c r="AG20">
-        <v>-5.491299248785332</v>
+        <v>32.5</v>
       </c>
       <c r="AH20">
-        <v>0.002855616193201303</v>
+        <v>0.149843912591051</v>
       </c>
       <c r="AI20">
-        <v>0.002355084489395485</v>
+        <v>0.08850645359557469</v>
       </c>
       <c r="AJ20">
-        <v>-0.09649314035109342</v>
+        <v>0.1170749279538905</v>
       </c>
       <c r="AK20">
-        <v>-0.07821394200476398</v>
+        <v>0.06807708420611647</v>
       </c>
       <c r="AL20">
-        <v>0.053</v>
+        <v>1.79</v>
       </c>
       <c r="AM20">
-        <v>0.037</v>
+        <v>1.789</v>
       </c>
       <c r="AN20">
-        <v>-0.2627118644067796</v>
+        <v>-0.3881401617250674</v>
       </c>
       <c r="AO20">
-        <v>-5.283018867924529</v>
+        <v>-62.17877094972066</v>
       </c>
       <c r="AP20">
-        <v>23.26821715587005</v>
+        <v>-0.2920035938903863</v>
       </c>
       <c r="AQ20">
-        <v>-7.567567567567568</v>
+        <v>-62.21352711011738</v>
       </c>
     </row>
     <row r="21">
@@ -2936,7 +2855,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>eBlitz Group AB (publ) (NGM:EBLITZ)</t>
+          <t>Linc AB (OM:LINC)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2944,23 +2863,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G21">
-        <v>-0.9377593360995852</v>
-      </c>
-      <c r="H21">
-        <v>-0.9377593360995852</v>
-      </c>
-      <c r="I21">
-        <v>-1.008298755186722</v>
-      </c>
-      <c r="J21">
-        <v>-1.008298755186722</v>
-      </c>
       <c r="K21">
-        <v>0.025</v>
-      </c>
-      <c r="L21">
-        <v>0.1037344398340249</v>
+        <v>-72.8</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -2969,7 +2873,7 @@
         <v>-0</v>
       </c>
       <c r="O21">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P21">
         <v>-0</v>
@@ -2978,37 +2882,37 @@
         <v>-0</v>
       </c>
       <c r="R21">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.125</v>
+        <v>57.2</v>
       </c>
       <c r="V21">
-        <v>0.03993610223642172</v>
+        <v>0.1731759006963367</v>
       </c>
       <c r="W21">
-        <v>0.01436781609195402</v>
+        <v>-0.1761432373578514</v>
       </c>
       <c r="X21">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y21">
-        <v>-0.02950514799952825</v>
+        <v>-0.2485974563985563</v>
       </c>
       <c r="Z21">
-        <v>0.1594970218398412</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>-0.1608206485771013</v>
+        <v>-0.2808197246237592</v>
       </c>
       <c r="AB21">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC21">
-        <v>-0.2046936126685835</v>
+        <v>-0.3532739436644641</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -3020,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>-0.125</v>
+        <v>-57.2</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -3029,22 +2933,19 @@
         <v>0</v>
       </c>
       <c r="AJ21">
-        <v>-0.0415973377703827</v>
+        <v>-0.2094470889783962</v>
       </c>
       <c r="AK21">
-        <v>-0.04970178926441352</v>
+        <v>-0.2924335378323108</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>-0</v>
-      </c>
-      <c r="AP21">
-        <v>0.5530973451327433</v>
+        <v>-0.024</v>
+      </c>
+      <c r="AQ21">
+        <v>3654.166666666667</v>
       </c>
     </row>
     <row r="22">
@@ -3064,22 +2965,22 @@
         </is>
       </c>
       <c r="G22">
-        <v>-29.11111111111111</v>
+        <v>-39.63636363636364</v>
       </c>
       <c r="H22">
-        <v>-29.11111111111111</v>
+        <v>-39.63636363636364</v>
       </c>
       <c r="I22">
-        <v>-52.44444444444444</v>
+        <v>-66.54545454545455</v>
       </c>
       <c r="J22">
-        <v>-52.44444444444444</v>
+        <v>-66.54545454545455</v>
       </c>
       <c r="K22">
-        <v>-1.12</v>
+        <v>-2.1</v>
       </c>
       <c r="L22">
-        <v>-62.22222222222224</v>
+        <v>-190.9090909090909</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -3103,31 +3004,31 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>1.04</v>
+        <v>0.2</v>
       </c>
       <c r="V22">
-        <v>0.2626262626262627</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="W22">
-        <v>-0.4307692307692308</v>
+        <v>-0.4233870967741936</v>
       </c>
       <c r="X22">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y22">
-        <v>-0.4746421948607131</v>
+        <v>-0.4958413158148984</v>
       </c>
       <c r="Z22">
-        <v>0.02163461538461537</v>
+        <v>0.004435483870967742</v>
       </c>
       <c r="AA22">
-        <v>-1.134615384615384</v>
+        <v>-0.2951612903225806</v>
       </c>
       <c r="AB22">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC22">
-        <v>-1.178488348706866</v>
+        <v>-0.3676155093632855</v>
       </c>
       <c r="AD22">
         <v>0</v>
@@ -3139,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>-1.04</v>
+        <v>-0.2</v>
       </c>
       <c r="AH22">
         <v>0</v>
@@ -3148,28 +3049,28 @@
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>-0.3561643835616439</v>
+        <v>-0.1219512195121951</v>
       </c>
       <c r="AK22">
-        <v>-0.2653061224489796</v>
+        <v>-0.0664451827242525</v>
       </c>
       <c r="AL22">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="AM22">
-        <v>-1.087</v>
+        <v>0.014</v>
       </c>
       <c r="AN22">
         <v>-0</v>
       </c>
       <c r="AO22">
-        <v>-314.6666666666666</v>
+        <v>-52.28571428571428</v>
       </c>
       <c r="AP22">
-        <v>2.011605415860735</v>
+        <v>0.5037783375314862</v>
       </c>
       <c r="AQ22">
-        <v>0.8684452621895122</v>
+        <v>-52.28571428571428</v>
       </c>
     </row>
     <row r="23">
@@ -3180,7 +3081,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACQ Bure AB (publ) (OM:ACQ SPAC)</t>
+          <t>Bure Equity AB (publ) (OM:BURE)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3189,70 +3090,100 @@
         </is>
       </c>
       <c r="K23">
-        <v>-1.17</v>
+        <v>-933.9</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>28.4</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>0.01620357163233868</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>-0.03041010814862405</v>
       </c>
       <c r="P23">
-        <v>-0</v>
+        <v>28.4</v>
       </c>
       <c r="Q23">
-        <v>-0</v>
+        <v>0.01620357163233868</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>-0.03041010814862405</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
       <c r="U23">
-        <v>36.8</v>
+        <v>39.2</v>
       </c>
       <c r="V23">
-        <v>0.09406952965235173</v>
+        <v>0.02236549323900268</v>
+      </c>
+      <c r="W23">
+        <v>-0.360523471278567</v>
       </c>
       <c r="X23">
-        <v>0.04387296409148227</v>
+        <v>0.07245833542769517</v>
+      </c>
+      <c r="Y23">
+        <v>-0.4329818067062622</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>-0.3713656745024996</v>
       </c>
       <c r="AB23">
-        <v>0.04387296409148227</v>
+        <v>0.07245390132410784</v>
+      </c>
+      <c r="AC23">
+        <v>-0.4438195758266074</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AG23">
-        <v>-36.8</v>
+        <v>-38.93</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>0.0001540243130230409</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>0.0002469655254420226</v>
       </c>
       <c r="AJ23">
-        <v>-0.1038374717832957</v>
+        <v>-0.02271600039678603</v>
       </c>
       <c r="AK23">
-        <v>-0.1031679282310064</v>
+        <v>-0.03693303101312057</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>-0.7200000000000001</v>
+      </c>
+      <c r="AN23">
+        <v>-0.0002892650524962503</v>
+      </c>
+      <c r="AO23">
+        <v>-10376.66666666667</v>
+      </c>
+      <c r="AP23">
+        <v>0.04170773516177416</v>
+      </c>
+      <c r="AQ23">
+        <v>1297.083333333333</v>
       </c>
     </row>
     <row r="24">
@@ -3263,7 +3194,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aligro Planet Acquisition Company AB (publ) (OM:APAC SPAC A)</t>
+          <t>Nordic Asia Investment Group 1987 AB (publ) (OM:NAIG B)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3272,40 +3203,58 @@
         </is>
       </c>
       <c r="K24">
-        <v>-1.52</v>
+        <v>-5.28</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>1.736</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.09591160220994474</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>-0.3287878787878788</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>0.266</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.01469613259668508</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>-0.05037878787878788</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.47</v>
+      </c>
+      <c r="T24">
+        <v>0.8467741935483871</v>
       </c>
       <c r="U24">
-        <v>1.7</v>
+        <v>4.13</v>
       </c>
       <c r="V24">
-        <v>0.01263001485884101</v>
+        <v>0.2281767955801105</v>
+      </c>
+      <c r="W24">
+        <v>-0.4292682926829268</v>
       </c>
       <c r="X24">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y24">
+        <v>-0.5017225117236317</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>-0.4835164835164835</v>
       </c>
       <c r="AB24">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC24">
+        <v>-0.5559707025571883</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -3317,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>-1.7</v>
+        <v>-4.13</v>
       </c>
       <c r="AH24">
         <v>0</v>
@@ -3326,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>-0.0127915726109857</v>
+        <v>-0.2956335003579098</v>
       </c>
       <c r="AK24">
-        <v>-0.01501766784452297</v>
+        <v>-0.2652536929993577</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3346,7 +3295,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tbd30 AB (publ) (OM:TBD30 SPAC A)</t>
+          <t>VNV Global AB (publ) (OM:VNV)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3355,16 +3304,16 @@
         </is>
       </c>
       <c r="K25">
-        <v>-3.52</v>
+        <v>-917.9</v>
       </c>
       <c r="M25">
-        <v>1.19</v>
+        <v>11</v>
       </c>
       <c r="N25">
-        <v>0.01023215821152193</v>
+        <v>0.03842123646524624</v>
       </c>
       <c r="O25">
-        <v>-0.3380681818181818</v>
+        <v>-0.01198387623924175</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3376,58 +3325,79 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>1.19</v>
+        <v>11</v>
       </c>
       <c r="T25">
         <v>1</v>
       </c>
       <c r="U25">
-        <v>0.698</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="V25">
-        <v>0.006001719690455718</v>
+        <v>0.3147048550471533</v>
+      </c>
+      <c r="W25">
+        <v>-0.6158749329039184</v>
       </c>
       <c r="X25">
-        <v>0.04387296409148227</v>
+        <v>0.08650094699287778</v>
+      </c>
+      <c r="Y25">
+        <v>-0.7023758798967962</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>-0.5911591728324795</v>
       </c>
       <c r="AB25">
-        <v>0.04387296409148227</v>
+        <v>0.07174348929501123</v>
+      </c>
+      <c r="AC25">
+        <v>-0.6629026621274907</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>150.5</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>150.5</v>
       </c>
       <c r="AG25">
-        <v>-0.698</v>
+        <v>60.40000000000001</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>0.344551282051282</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>0.1789323504934015</v>
       </c>
       <c r="AJ25">
-        <v>-0.006037957820798947</v>
+        <v>0.1742140178828959</v>
       </c>
       <c r="AK25">
-        <v>-0.007678598930716595</v>
+        <v>0.08042609853528629</v>
       </c>
       <c r="AL25">
-        <v>0.384</v>
+        <v>13</v>
       </c>
       <c r="AM25">
-        <v>0.384</v>
+        <v>12.996</v>
+      </c>
+      <c r="AN25">
+        <v>-0.1609970047068892</v>
       </c>
       <c r="AO25">
-        <v>-8.177083333333334</v>
+        <v>-71.9076923076923</v>
+      </c>
+      <c r="AP25">
+        <v>-0.06461275139067181</v>
       </c>
       <c r="AQ25">
-        <v>-8.177083333333334</v>
+        <v>-71.92982456140351</v>
       </c>
     </row>
     <row r="26">
@@ -3438,7 +3408,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>First Venture Sweden AB (publ) (OM:FIRST B)</t>
+          <t>Athanase Innovation AB (publ) (OM:ATIN)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3447,73 +3417,100 @@
         </is>
       </c>
       <c r="K26">
-        <v>-0.883</v>
+        <v>-10.4</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>66.968</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.9445416078984485</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>-6.439230769230769</v>
       </c>
       <c r="P26">
-        <v>-0</v>
+        <v>66.96000000000001</v>
       </c>
       <c r="Q26">
-        <v>-0</v>
+        <v>0.9444287729196051</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>-6.438461538461539</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>0.007999999999995566</v>
+      </c>
+      <c r="T26">
+        <v>0.0001194600406163476</v>
       </c>
       <c r="U26">
-        <v>21.4</v>
+        <v>59.3</v>
       </c>
       <c r="V26">
-        <v>0.6970684039087948</v>
+        <v>0.8363892806770098</v>
+      </c>
+      <c r="W26">
+        <v>-0.3104477611940298</v>
       </c>
       <c r="X26">
-        <v>0.04387296409148227</v>
+        <v>0.07246929461188586</v>
+      </c>
+      <c r="Y26">
+        <v>-0.3829170558059157</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>-0.6994547557415871</v>
       </c>
       <c r="AB26">
-        <v>0.04387296409148227</v>
+        <v>0.07245305593434886</v>
+      </c>
+      <c r="AC26">
+        <v>-0.7719078116759359</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AG26">
-        <v>-21.4</v>
+        <v>-59.26</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>0.0005638567803777839</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>0.0005591277606933184</v>
       </c>
       <c r="AJ26">
-        <v>-2.301075268817204</v>
+        <v>-5.091065292096216</v>
       </c>
       <c r="AK26">
-        <v>-1.539568345323741</v>
+        <v>-4.841503267973855</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AM26">
-        <v>-0.074</v>
+        <v>-1.813</v>
+      </c>
+      <c r="AN26">
+        <v>-0.003539823008849557</v>
+      </c>
+      <c r="AO26">
+        <v>-747.0588235294117</v>
+      </c>
+      <c r="AP26">
+        <v>5.244247787610619</v>
       </c>
       <c r="AQ26">
-        <v>6.554054054054054</v>
+        <v>7.00496414782129</v>
       </c>
     </row>
     <row r="27">
@@ -3524,7 +3521,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nordic Asia Investment Group 1987 AB (publ) (OM:NAIG B)</t>
+          <t>byNordic Acquisition Corporation (NasdaqGM:BYNO)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3532,23 +3529,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G27">
-        <v>-0</v>
-      </c>
-      <c r="H27">
-        <v>-0</v>
-      </c>
-      <c r="I27">
-        <v>1.106741573033708</v>
-      </c>
-      <c r="J27">
-        <v>1.106741573033708</v>
-      </c>
       <c r="K27">
-        <v>-1.9</v>
-      </c>
-      <c r="L27">
-        <v>1.067415730337079</v>
+        <v>-0.14</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3572,16 +3554,31 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>0.004217854217854218</v>
+      </c>
+      <c r="W27">
+        <v>4.375</v>
       </c>
       <c r="X27">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="Y27">
+        <v>4.302545780959295</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>-2.508417508417508</v>
       </c>
       <c r="AB27">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AC27">
+        <v>-2.580871727458213</v>
       </c>
       <c r="AD27">
         <v>0</v>
@@ -3593,25 +3590,28 @@
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
+      <c r="AI27">
+        <v>-0</v>
+      </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>-0.004235719866759881</v>
+      </c>
+      <c r="AK27">
+        <v>0.1672077922077922</v>
       </c>
       <c r="AL27">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>-0.063</v>
-      </c>
-      <c r="AO27">
-        <v>-49.25</v>
+        <v>-0.805</v>
       </c>
       <c r="AQ27">
-        <v>31.26984126984127</v>
+        <v>0.9254658385093167</v>
       </c>
     </row>
     <row r="28">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abelco Investment Group AB (NGM:ABIG)</t>
+          <t>EPTI AB (OM:EPTI)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3631,22 +3631,22 @@
         </is>
       </c>
       <c r="G28">
-        <v>-1.105575326215896</v>
+        <v>-0.267</v>
       </c>
       <c r="H28">
-        <v>-1.110320284697509</v>
+        <v>-0.267</v>
       </c>
       <c r="I28">
-        <v>-1.180308422301305</v>
+        <v>-0.4635</v>
       </c>
       <c r="J28">
-        <v>-1.180308422301305</v>
+        <v>-0.4635</v>
       </c>
       <c r="K28">
-        <v>11.8</v>
+        <v>-16.2</v>
       </c>
       <c r="L28">
-        <v>13.9976275207592</v>
+        <v>-0.8099999999999999</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3655,7 +3655,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3664,58 +3664,370 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>0.02261904761904762</v>
       </c>
       <c r="X28">
-        <v>0.04387296409148227</v>
+        <v>0.07679645465243179</v>
       </c>
       <c r="AB28">
-        <v>0.04387296409148227</v>
+        <v>0.0721658749698338</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.1397849462365591</v>
+      </c>
+      <c r="AI28">
+        <v>0.1329761324890404</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>0.1227154046997389</v>
+      </c>
+      <c r="AK28">
+        <v>0.1166253101736973</v>
       </c>
       <c r="AL28">
-        <v>0.601</v>
+        <v>0.147</v>
       </c>
       <c r="AM28">
-        <v>0.596</v>
+        <v>0.133</v>
       </c>
       <c r="AN28">
-        <v>-0</v>
+        <v>-0.4542429284525791</v>
       </c>
       <c r="AO28">
-        <v>-1.655574043261231</v>
+        <v>-63.06122448979592</v>
       </c>
       <c r="AP28">
-        <v>-0</v>
+        <v>-0.3910149750415974</v>
       </c>
       <c r="AQ28">
-        <v>-1.669463087248322</v>
+        <v>-69.69924812030077</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MTI Investment SE (OM:MTI)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>-0.4840659340659341</v>
+      </c>
+      <c r="H29">
+        <v>-0.4840659340659341</v>
+      </c>
+      <c r="I29">
+        <v>-0.7912087912087912</v>
+      </c>
+      <c r="J29">
+        <v>-0.7912087912087912</v>
+      </c>
+      <c r="K29">
+        <v>-1.44</v>
+      </c>
+      <c r="L29">
+        <v>-0.7912087912087912</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>1.17</v>
+      </c>
+      <c r="V29">
+        <v>0.5545023696682464</v>
+      </c>
+      <c r="X29">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB29">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>-1.17</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>-1.24468085106383</v>
+      </c>
+      <c r="AK29">
+        <v>-1.329545454545455</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-0.031</v>
+      </c>
+      <c r="AN29">
+        <v>-0</v>
+      </c>
+      <c r="AP29">
+        <v>1.044642857142857</v>
+      </c>
+      <c r="AQ29">
+        <v>46.45161290322581</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Creaspac AB (publ) (OM:CPAC SPAC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K30">
+        <v>-0.459</v>
+      </c>
+      <c r="M30">
+        <v>2.91</v>
+      </c>
+      <c r="N30">
+        <v>0.01275756247259974</v>
+      </c>
+      <c r="O30">
+        <v>-6.339869281045751</v>
+      </c>
+      <c r="P30">
+        <v>-0</v>
+      </c>
+      <c r="Q30">
+        <v>-0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>2.91</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30">
+        <v>19.8</v>
+      </c>
+      <c r="V30">
+        <v>0.08680403331871986</v>
+      </c>
+      <c r="X30">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB30">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>-19.8</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0</v>
+      </c>
+      <c r="AJ30">
+        <v>-0.09505520883341335</v>
+      </c>
+      <c r="AK30">
+        <v>-0.09840954274353877</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-0.27</v>
+      </c>
+      <c r="AQ30">
+        <v>0.5592592592592592</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Katalysen Ventures AB (publ) (NGM:KAV)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>-1.238805970149254</v>
+      </c>
+      <c r="H31">
+        <v>-1.238805970149254</v>
+      </c>
+      <c r="I31">
+        <v>-2.885572139303482</v>
+      </c>
+      <c r="J31">
+        <v>-2.885572139303482</v>
+      </c>
+      <c r="K31">
+        <v>-1.27</v>
+      </c>
+      <c r="L31">
+        <v>-3.159203980099502</v>
+      </c>
+      <c r="M31">
+        <v>-0</v>
+      </c>
+      <c r="N31">
+        <v>-0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0.518</v>
+      </c>
+      <c r="V31">
+        <v>0.0343046357615894</v>
+      </c>
+      <c r="X31">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AB31">
+        <v>0.07245421904070486</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>-0.518</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>0</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.0355232478398025</v>
+      </c>
+      <c r="AK31">
+        <v>-0.06143263757115751</v>
+      </c>
+      <c r="AL31">
+        <v>0.003</v>
+      </c>
+      <c r="AM31">
+        <v>-0.03</v>
+      </c>
+      <c r="AN31">
+        <v>-0</v>
+      </c>
+      <c r="AO31">
+        <v>-386.6666666666666</v>
+      </c>
+      <c r="AP31">
+        <v>0.4543859649122808</v>
+      </c>
+      <c r="AQ31">
+        <v>38.66666666666666</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ31"/>
+  <dimension ref="A1:AQ30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0571</v>
+        <v>0.0805</v>
       </c>
       <c r="E2">
-        <v>0.127</v>
+        <v>0.114</v>
       </c>
       <c r="F2">
-        <v>0.117</v>
+        <v>0.2145</v>
       </c>
       <c r="G2">
-        <v>0.5308326899338813</v>
+        <v>-0.1694191225570515</v>
       </c>
       <c r="H2">
-        <v>0.530824096952886</v>
+        <v>-0.169468819332178</v>
       </c>
       <c r="I2">
-        <v>-0.1948086794263841</v>
+        <v>0.2158710060685912</v>
       </c>
       <c r="J2">
-        <v>-0.1861861839400979</v>
+        <v>0.2042441903381113</v>
       </c>
       <c r="K2">
-        <v>-1051.84</v>
+        <v>524.355</v>
       </c>
       <c r="L2">
-        <v>-0.2259610282532918</v>
+        <v>0.08686250840496709</v>
       </c>
       <c r="M2">
-        <v>441.863</v>
+        <v>554.7424</v>
       </c>
       <c r="N2">
-        <v>0.01424082382603276</v>
+        <v>0.01344389752592545</v>
       </c>
       <c r="O2">
-        <v>-0.4200857544873746</v>
+        <v>1.057951960027081</v>
       </c>
       <c r="P2">
-        <v>422.986</v>
+        <v>407.4004</v>
       </c>
       <c r="Q2">
-        <v>0.01363243608738068</v>
+        <v>0.009873139730478575</v>
       </c>
       <c r="R2">
-        <v>-0.4021391086096745</v>
+        <v>0.7769553069962144</v>
       </c>
       <c r="S2">
-        <v>18.877</v>
+        <v>147.342</v>
       </c>
       <c r="T2">
-        <v>0.04272138649309853</v>
+        <v>0.2656043597893364</v>
       </c>
       <c r="U2">
-        <v>2765.848</v>
+        <v>1087.368</v>
       </c>
       <c r="V2">
-        <v>0.08914064788765985</v>
+        <v>0.02635180574798411</v>
       </c>
       <c r="W2">
-        <v>-0.03546910755148741</v>
+        <v>-0.05779938811188811</v>
       </c>
       <c r="X2">
-        <v>0.07245421904070486</v>
+        <v>0.0623166206290144</v>
       </c>
       <c r="Y2">
-        <v>-0.1079233265921923</v>
+        <v>-0.1201160087409025</v>
       </c>
       <c r="Z2">
-        <v>0.5113480089396006</v>
+        <v>0.8250709050658699</v>
       </c>
       <c r="AA2">
-        <v>-0.03804411249854125</v>
+        <v>-0.02813085086486497</v>
       </c>
       <c r="AB2">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC2">
-        <v>-0.1104983315392461</v>
+        <v>-0.08808905203558953</v>
       </c>
       <c r="AD2">
-        <v>3585.45</v>
+        <v>3749.99</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.005709636438899753</v>
       </c>
       <c r="AF2">
-        <v>3585.45</v>
+        <v>3749.995709636439</v>
       </c>
       <c r="AG2">
-        <v>819.6019999999999</v>
+        <v>2662.627709636439</v>
       </c>
       <c r="AH2">
-        <v>0.1035857252806431</v>
+        <v>0.08330823495121918</v>
       </c>
       <c r="AI2">
-        <v>0.2889680991049883</v>
+        <v>0.2278282894395498</v>
       </c>
       <c r="AJ2">
-        <v>0.02573519714821051</v>
+        <v>0.06061602154136844</v>
       </c>
       <c r="AK2">
-        <v>0.08500399764652757</v>
+        <v>0.173208579695991</v>
       </c>
       <c r="AL2">
-        <v>69.709</v>
+        <v>157.397</v>
       </c>
       <c r="AM2">
-        <v>60.28700000000001</v>
+        <v>116.526</v>
       </c>
       <c r="AN2">
-        <v>-4.941665345838703</v>
+        <v>2.258506310283458</v>
       </c>
       <c r="AO2">
-        <v>-13.00875066347243</v>
+        <v>8.279217520028972</v>
       </c>
       <c r="AP2">
-        <v>-1.129620773063379</v>
+        <v>1.603620672094989</v>
       </c>
       <c r="AQ2">
-        <v>-15.04183323104483</v>
+        <v>11.18311793076223</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coeli Private Equity AB (publ) (NGM:CPE I)</t>
+          <t>Bure Equity AB (publ) (OM:BURE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,95 +724,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.5670000000000001</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>-2.279506299820005</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>-2.279506299820005</v>
       </c>
       <c r="I3">
-        <v>0.9829545454545454</v>
+        <v>0.9843147338647468</v>
       </c>
       <c r="J3">
-        <v>0.9829545454545454</v>
+        <v>0.9843147338647468</v>
       </c>
       <c r="K3">
-        <v>69.2</v>
+        <v>383.8</v>
       </c>
       <c r="L3">
-        <v>0.9829545454545454</v>
+        <v>0.9868860889688867</v>
       </c>
       <c r="M3">
-        <v>10.77</v>
+        <v>15.392</v>
       </c>
       <c r="N3">
-        <v>0.09547872340425534</v>
+        <v>0.007325686545143022</v>
       </c>
       <c r="O3">
-        <v>0.155635838150289</v>
+        <v>0.04010422094841063</v>
       </c>
       <c r="P3">
-        <v>8.960000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="Q3">
-        <v>0.07943262411347518</v>
+        <v>0.007281899957165295</v>
       </c>
       <c r="R3">
-        <v>0.1294797687861272</v>
+        <v>0.03986451276706618</v>
       </c>
       <c r="S3">
-        <v>1.81</v>
+        <v>0.09200000000000053</v>
       </c>
       <c r="T3">
-        <v>0.1680594243268338</v>
+        <v>0.00597713097713101</v>
       </c>
       <c r="U3">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="V3">
-        <v>0.06205673758865248</v>
+        <v>0.02760458807291419</v>
+      </c>
+      <c r="W3">
+        <v>0.3515295841729255</v>
       </c>
       <c r="X3">
-        <v>0.07245421904070486</v>
+        <v>0.06231083156880186</v>
+      </c>
+      <c r="Y3">
+        <v>0.2892187526041236</v>
+      </c>
+      <c r="Z3">
+        <v>0.3693713373920807</v>
+      </c>
+      <c r="AA3">
+        <v>0.3635776496623515</v>
       </c>
       <c r="AB3">
-        <v>0.07245421904070486</v>
+        <v>0.06230796140548907</v>
+      </c>
+      <c r="AC3">
+        <v>0.3012696882568625</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="AG3">
-        <v>-7</v>
+        <v>-57.725</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0001308666944262685</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.0001854630675591374</v>
       </c>
       <c r="AJ3">
-        <v>-0.06616257088846882</v>
+        <v>-0.02824983177341408</v>
       </c>
       <c r="AK3">
-        <v>-0.045425048669695</v>
+        <v>-0.04051516906178168</v>
       </c>
       <c r="AL3">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.08599999999999999</v>
-      </c>
-      <c r="AO3">
-        <v>9885.714285714286</v>
+        <v>-1.1</v>
+      </c>
+      <c r="AN3">
+        <v>0.0007174536916253587</v>
+      </c>
+      <c r="AP3">
+        <v>-0.1506000521784503</v>
       </c>
       <c r="AQ3">
-        <v>-804.6511627906978</v>
+        <v>-348</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Case Group AB (publ) (OM:CASE)</t>
+          <t>Investment AB Spiltan (NGM:SPLTN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,40 +853,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.9078156312625251</v>
+        <v>0.187035786630655</v>
       </c>
       <c r="H4">
-        <v>0.9078156312625251</v>
+        <v>0.187035786630655</v>
       </c>
       <c r="I4">
-        <v>0.0344689378757515</v>
+        <v>0.9817690749493586</v>
       </c>
       <c r="J4">
-        <v>0.0344689378757515</v>
+        <v>0.9794804916327537</v>
       </c>
       <c r="K4">
-        <v>-0.849</v>
+        <v>147.6</v>
       </c>
       <c r="L4">
-        <v>-0.1701402805611222</v>
+        <v>0.9966239027683997</v>
       </c>
       <c r="M4">
-        <v>0.1</v>
+        <v>2.85</v>
       </c>
       <c r="N4">
-        <v>0.002994011976047904</v>
+        <v>0.004252461951656222</v>
       </c>
       <c r="O4">
-        <v>-0.1177856301531213</v>
+        <v>0.0193089430894309</v>
       </c>
       <c r="P4">
-        <v>0.1</v>
+        <v>2.85</v>
       </c>
       <c r="Q4">
-        <v>0.002994011976047904</v>
+        <v>0.004252461951656222</v>
       </c>
       <c r="R4">
-        <v>-0.1177856301531213</v>
+        <v>0.0193089430894309</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -874,22 +895,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>-16.7</v>
       </c>
       <c r="V4">
-        <v>0.06826347305389222</v>
+        <v>-0.0249179349447926</v>
       </c>
       <c r="W4">
-        <v>-0.1337007874015748</v>
+        <v>0.2200685850603847</v>
       </c>
       <c r="X4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y4">
-        <v>-0.2061550064422797</v>
+        <v>0.157760196524583</v>
+      </c>
+      <c r="Z4">
+        <v>0.2241392357169883</v>
+      </c>
+      <c r="AA4">
+        <v>0.2195400087942654</v>
       </c>
       <c r="AB4">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AC4">
+        <v>0.1572316202584637</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -901,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-2.28</v>
+        <v>16.7</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -910,22 +940,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.07326478149100257</v>
+        <v>0.02431212694715388</v>
       </c>
       <c r="AK4">
-        <v>-0.6570605187319883</v>
+        <v>0.01959633888758507</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.401</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.506</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>362.5935162094763</v>
+      </c>
       <c r="AP4">
-        <v>-13.10344827586207</v>
+        <v>0.1148555708390646</v>
+      </c>
+      <c r="AQ4">
+        <v>-287.3517786561265</v>
       </c>
     </row>
     <row r="5">
@@ -936,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EQT AB (publ) (OM:EQT)</t>
+          <t>Ratos AB (publ) (OM:RATO B)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -944,44 +980,44 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F5">
-        <v>0.2</v>
+      <c r="D5">
+        <v>0.0848</v>
       </c>
       <c r="G5">
-        <v>0.7046944198405669</v>
+        <v>0.05695228322216521</v>
       </c>
       <c r="H5">
-        <v>0.7046944198405669</v>
+        <v>0.05695228322216521</v>
       </c>
       <c r="I5">
-        <v>0.5382934750516681</v>
+        <v>0.05233453052847614</v>
       </c>
       <c r="J5">
-        <v>0.5382934750516681</v>
+        <v>0.04190169083809644</v>
       </c>
       <c r="K5">
-        <v>817.9</v>
+        <v>65</v>
       </c>
       <c r="L5">
-        <v>0.4829642751697668</v>
+        <v>0.02084402257567983</v>
       </c>
       <c r="M5">
-        <v>261.2</v>
+        <v>25.1</v>
       </c>
       <c r="N5">
-        <v>0.01040152598191281</v>
+        <v>0.02130910943204007</v>
       </c>
       <c r="O5">
-        <v>0.3193544443085952</v>
+        <v>0.3861538461538462</v>
       </c>
       <c r="P5">
-        <v>261.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q5">
-        <v>0.01040152598191281</v>
+        <v>0.02130910943204007</v>
       </c>
       <c r="R5">
-        <v>0.3193544443085952</v>
+        <v>0.3861538461538462</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -990,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2031.2</v>
+        <v>173.9</v>
       </c>
       <c r="V5">
-        <v>0.08088659867711066</v>
+        <v>0.1476356227183971</v>
       </c>
       <c r="W5">
-        <v>0.2997947364562715</v>
+        <v>0.05842696629213483</v>
       </c>
       <c r="X5">
-        <v>0.07479801359026107</v>
+        <v>0.07787604697257199</v>
       </c>
       <c r="Y5">
-        <v>0.2249967228660105</v>
+        <v>-0.01944908068043715</v>
       </c>
       <c r="Z5">
-        <v>0.8401964675530862</v>
+        <v>4.734892195566352</v>
       </c>
       <c r="AA5">
-        <v>0.4522722762452869</v>
+        <v>0.1983999889303369</v>
       </c>
       <c r="AB5">
-        <v>0.07228787923814849</v>
+        <v>0.06082414369161346</v>
       </c>
       <c r="AC5">
-        <v>0.3799843970071384</v>
+        <v>0.1375758452387235</v>
       </c>
       <c r="AD5">
-        <v>2202.6</v>
+        <v>982.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2202.6</v>
+        <v>982.4</v>
       </c>
       <c r="AG5">
-        <v>171.3999999999999</v>
+        <v>808.5</v>
       </c>
       <c r="AH5">
-        <v>0.08063907916366152</v>
+        <v>0.4547516548627505</v>
       </c>
       <c r="AI5">
-        <v>0.3906912393351899</v>
+        <v>0.4334627603247441</v>
       </c>
       <c r="AJ5">
-        <v>0.006779231977091411</v>
+        <v>0.4070177204993959</v>
       </c>
       <c r="AK5">
-        <v>0.04752530153888808</v>
+        <v>0.3863799283154122</v>
       </c>
       <c r="AL5">
-        <v>6.27</v>
+        <v>54.3</v>
       </c>
       <c r="AM5">
-        <v>5.643</v>
+        <v>48.23999999999999</v>
       </c>
       <c r="AN5">
-        <v>2.166847024102312</v>
+        <v>4.565055762081784</v>
       </c>
       <c r="AO5">
-        <v>145.3907496012759</v>
+        <v>3.005524861878453</v>
       </c>
       <c r="AP5">
-        <v>0.1686178061977372</v>
+        <v>3.756970260223048</v>
       </c>
       <c r="AQ5">
-        <v>161.545277334751</v>
+        <v>3.383084577114428</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAXS AB (publ) (OM:NAXS)</t>
+          <t>EQT AB (publ) (OM:EQT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1075,116 +1111,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.131</v>
-      </c>
-      <c r="E6">
-        <v>0.127</v>
+      <c r="F6">
+        <v>0.332</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.4121390872399876</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.4121390872399876</v>
       </c>
       <c r="I6">
-        <v>0.9135802469135803</v>
+        <v>0.3188968229328366</v>
       </c>
       <c r="J6">
-        <v>0.9135802469135803</v>
+        <v>0.1594484114664183</v>
       </c>
       <c r="K6">
-        <v>13.5</v>
+        <v>-51</v>
       </c>
       <c r="L6">
-        <v>0.8333333333333334</v>
+        <v>-0.02638932008692953</v>
       </c>
       <c r="M6">
-        <v>3.929</v>
+        <v>335.2</v>
       </c>
       <c r="N6">
-        <v>0.0618740157480315</v>
+        <v>0.009534374377791052</v>
       </c>
       <c r="O6">
-        <v>0.291037037037037</v>
+        <v>-6.572549019607843</v>
       </c>
       <c r="P6">
-        <v>3.51</v>
+        <v>335.2</v>
       </c>
       <c r="Q6">
-        <v>0.0552755905511811</v>
+        <v>0.009534374377791052</v>
       </c>
       <c r="R6">
-        <v>0.26</v>
+        <v>-6.572549019607843</v>
       </c>
       <c r="S6">
-        <v>0.419</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.1066429116823619</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>22</v>
+        <v>541.5</v>
       </c>
       <c r="V6">
-        <v>0.3464566929133858</v>
+        <v>0.01540233808345422</v>
       </c>
       <c r="W6">
-        <v>0.154639175257732</v>
+        <v>-0.01484672935285727</v>
       </c>
       <c r="X6">
-        <v>0.07245421904070486</v>
+        <v>0.06353482070433294</v>
       </c>
       <c r="Y6">
-        <v>0.08218495621702711</v>
+        <v>-0.07838155005719022</v>
       </c>
       <c r="Z6">
-        <v>0.2842105263157895</v>
+        <v>0.7900739953395201</v>
       </c>
       <c r="AA6">
-        <v>0.2596491228070176</v>
+        <v>0.1259760434978128</v>
       </c>
       <c r="AB6">
-        <v>0.07245421904070486</v>
+        <v>0.0621071577975881</v>
       </c>
       <c r="AC6">
-        <v>0.1871949037663127</v>
+        <v>0.06386888570022473</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="AG6">
-        <v>-22</v>
+        <v>1768.5</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.06165425574505565</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.2611349762604567</v>
       </c>
       <c r="AJ6">
-        <v>-0.5301204819277109</v>
+        <v>0.04789373197383922</v>
       </c>
       <c r="AK6">
-        <v>-0.3594771241830065</v>
+        <v>0.2129568306339936</v>
       </c>
       <c r="AL6">
-        <v>0.013</v>
+        <v>59.8</v>
       </c>
       <c r="AM6">
-        <v>0.013</v>
+        <v>50.52</v>
+      </c>
+      <c r="AN6">
+        <v>2.436965924675599</v>
       </c>
       <c r="AO6">
-        <v>1138.461538461539</v>
+        <v>10.30602006688963</v>
+      </c>
+      <c r="AP6">
+        <v>1.865703133241903</v>
       </c>
       <c r="AQ6">
-        <v>1138.461538461539</v>
+        <v>12.19912905779889</v>
       </c>
     </row>
     <row r="7">
@@ -1195,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Catella AB (publ) (OM:CAT B)</t>
+          <t>Stockwik Förvaltning AB (publ) (OM:STWK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,121 +1243,115 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0571</v>
-      </c>
-      <c r="E7">
-        <v>0.247</v>
+        <v>0.477</v>
       </c>
       <c r="G7">
-        <v>0.09843205574912893</v>
+        <v>0.07228915662650602</v>
       </c>
       <c r="H7">
-        <v>0.09843205574912893</v>
+        <v>0.07228915662650602</v>
       </c>
       <c r="I7">
-        <v>0.3397212543554007</v>
+        <v>0.04096385542168675</v>
       </c>
       <c r="J7">
-        <v>0.2789097781383505</v>
+        <v>0.04096385542168675</v>
       </c>
       <c r="K7">
-        <v>44</v>
+        <v>-1.33</v>
       </c>
       <c r="L7">
-        <v>0.1916376306620209</v>
+        <v>-0.0178045515394913</v>
       </c>
       <c r="M7">
-        <v>7.92</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.02572263721987659</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>7.92</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.02572263721987659</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>144.2</v>
+        <v>2.21</v>
       </c>
       <c r="V7">
-        <v>0.4683338746346216</v>
+        <v>0.2065420560747664</v>
       </c>
       <c r="W7">
-        <v>0.2426916712630998</v>
+        <v>-0.059375</v>
       </c>
       <c r="X7">
-        <v>0.09290971025781412</v>
+        <v>0.1327843403204774</v>
       </c>
       <c r="Y7">
-        <v>0.1497819610052857</v>
+        <v>-0.1921593403204774</v>
       </c>
       <c r="Z7">
-        <v>0.7653333333333333</v>
+        <v>2.929411764705883</v>
       </c>
       <c r="AA7">
-        <v>0.2134589502018843</v>
+        <v>0.12</v>
       </c>
       <c r="AB7">
-        <v>0.06890893327516734</v>
+        <v>0.05972796065418998</v>
       </c>
       <c r="AC7">
-        <v>0.1445500169267169</v>
+        <v>0.06027203934581005</v>
       </c>
       <c r="AD7">
-        <v>235.7</v>
+        <v>40.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>235.7</v>
+        <v>40.4</v>
       </c>
       <c r="AG7">
-        <v>91.5</v>
+        <v>38.19</v>
       </c>
       <c r="AH7">
-        <v>0.4335908756438558</v>
+        <v>0.7906066536203523</v>
       </c>
       <c r="AI7">
-        <v>0.5350737797956867</v>
+        <v>0.6495176848874598</v>
       </c>
       <c r="AJ7">
-        <v>0.2290936404606911</v>
+        <v>0.7811413376968704</v>
       </c>
       <c r="AK7">
-        <v>0.3088086398920014</v>
+        <v>0.6366061010168361</v>
       </c>
       <c r="AL7">
-        <v>7.11</v>
+        <v>5.31</v>
       </c>
       <c r="AM7">
-        <v>3.87</v>
+        <v>5.31</v>
       </c>
       <c r="AN7">
-        <v>3.117724867724868</v>
+        <v>7.318840579710145</v>
       </c>
       <c r="AO7">
-        <v>10.9704641350211</v>
+        <v>0.576271186440678</v>
       </c>
       <c r="AP7">
-        <v>1.21031746031746</v>
+        <v>6.918478260869565</v>
       </c>
       <c r="AQ7">
-        <v>20.15503875968992</v>
+        <v>0.576271186440678</v>
       </c>
     </row>
     <row r="8">
@@ -1329,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ratos AB (publ) (OM:RATO B)</t>
+          <t>Linc AB (OM:LINC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1337,125 +1370,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.0246</v>
-      </c>
-      <c r="E8">
-        <v>-0.164</v>
-      </c>
-      <c r="F8">
-        <v>0.117</v>
-      </c>
       <c r="G8">
-        <v>0.08205148963730569</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.08205148963730569</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.05035621761658031</v>
+        <v>0.9610894941634242</v>
       </c>
       <c r="J8">
-        <v>0.04509020793118629</v>
+        <v>0.7818093385214008</v>
       </c>
       <c r="K8">
-        <v>80.2</v>
+        <v>21.2</v>
       </c>
       <c r="L8">
-        <v>0.03246437823834197</v>
+        <v>0.8249027237354085</v>
       </c>
       <c r="M8">
-        <v>35.1</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.02669810603179433</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.4376558603491272</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>35.1</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.02669810603179433</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.4376558603491272</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>171.2</v>
+        <v>54.2</v>
       </c>
       <c r="V8">
-        <v>0.1302198220126264</v>
+        <v>0.1461310326233486</v>
       </c>
       <c r="W8">
-        <v>0.05872446364501721</v>
+        <v>0.08386075949367088</v>
       </c>
       <c r="X8">
-        <v>0.0896167597808198</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y8">
-        <v>-0.03089229613580259</v>
+        <v>0.02155237095786924</v>
       </c>
       <c r="Z8">
-        <v>3.070727159726538</v>
+        <v>0.1313905930470347</v>
       </c>
       <c r="AA8">
-        <v>0.1384597261320107</v>
+        <v>0.1027223926380368</v>
       </c>
       <c r="AB8">
-        <v>0.07164749297570459</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC8">
-        <v>0.06681223315630612</v>
+        <v>0.04041400410223515</v>
       </c>
       <c r="AD8">
-        <v>844.4</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>844.4</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>673.2</v>
+        <v>-54.2</v>
       </c>
       <c r="AH8">
-        <v>0.39108887962577</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.404502994011976</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.3386488253936315</v>
+        <v>-0.1711398800126303</v>
       </c>
       <c r="AK8">
-        <v>0.3513019882064395</v>
+        <v>-0.2413178984861977</v>
       </c>
       <c r="AL8">
-        <v>30.2</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>29.57</v>
-      </c>
-      <c r="AN8">
-        <v>5.017231134878193</v>
-      </c>
-      <c r="AO8">
-        <v>4.119205298013245</v>
-      </c>
-      <c r="AP8">
-        <v>4</v>
+        <v>-1.33</v>
       </c>
       <c r="AQ8">
-        <v>4.206966520121745</v>
+        <v>-18.57142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -1466,7 +1478,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eBlitz Group AB (publ) (NGM:EBLITZ)</t>
+          <t>Havsfrun Investment AB (publ) (OM:HAV B)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1474,71 +1486,77 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>0.226</v>
+      </c>
       <c r="G9">
-        <v>0.2111111111111111</v>
+        <v>-0.6071964017991005</v>
       </c>
       <c r="H9">
-        <v>0.2111111111111111</v>
+        <v>-0.6071964017991005</v>
       </c>
       <c r="I9">
-        <v>0.2013071895424837</v>
+        <v>0.328335832083958</v>
       </c>
       <c r="J9">
-        <v>0.2013071895424837</v>
+        <v>0.328335832083958</v>
       </c>
       <c r="K9">
-        <v>0.273</v>
+        <v>0.322</v>
       </c>
       <c r="L9">
-        <v>0.1784313725490196</v>
+        <v>0.4827586206896551</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>1.11</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.06201117318435755</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>3.4472049689441</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>1.11</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.06201117318435755</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>3.4472049689441</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0.5659999999999999</v>
+        <v>7.31</v>
       </c>
       <c r="V9">
-        <v>0.4677685950413223</v>
+        <v>0.4083798882681564</v>
       </c>
       <c r="W9">
-        <v>0.1034090909090909</v>
+        <v>0.02683333333333333</v>
       </c>
       <c r="X9">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y9">
-        <v>0.03095487186838605</v>
+        <v>-0.0354750552024683</v>
       </c>
       <c r="Z9">
-        <v>0.6083499005964215</v>
+        <v>0.2595330739299611</v>
       </c>
       <c r="AA9">
-        <v>0.1224652087475149</v>
+        <v>0.08521400778210116</v>
       </c>
       <c r="AB9">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC9">
-        <v>0.05001098970681005</v>
+        <v>0.02290561924629952</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -1550,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>-0.5659999999999999</v>
+        <v>-7.31</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1559,25 +1577,25 @@
         <v>0</v>
       </c>
       <c r="AJ9">
-        <v>-0.8788819875776397</v>
+        <v>-0.6902738432483475</v>
       </c>
       <c r="AK9">
-        <v>-0.2374161073825503</v>
+        <v>-1.787286063569682</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.006</v>
+        <v>-0.238</v>
       </c>
       <c r="AN9">
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>-1.752321981424148</v>
+        <v>-33.22727272727273</v>
       </c>
       <c r="AQ9">
-        <v>-51.33333333333333</v>
+        <v>-0.9201680672268908</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1606,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stockwik Förvaltning AB (publ) (OM:STWK)</t>
+          <t>NAXS AB (publ) (OM:NAXS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,118 +1615,112 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.515</v>
-      </c>
-      <c r="F10">
-        <v>-0.11</v>
+        <v>0.06269999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.227</v>
       </c>
       <c r="G10">
-        <v>0.08686244204018546</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.08686244204018546</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.05285935085007728</v>
+        <v>0.7356902356902356</v>
       </c>
       <c r="J10">
-        <v>0.02642967542503864</v>
+        <v>0.7355419110459432</v>
       </c>
       <c r="K10">
-        <v>-0.018</v>
+        <v>4.96</v>
       </c>
       <c r="L10">
-        <v>-0.0002782071097372488</v>
+        <v>0.835016835016835</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>3.81</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.0485969387755102</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>0.7681451612903226</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>3.81</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.0485969387755102</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>0.7681451612903226</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>13.4</v>
+        <v>20.8</v>
       </c>
       <c r="V10">
-        <v>1.107438016528926</v>
+        <v>0.2653061224489796</v>
       </c>
       <c r="W10">
-        <v>-0.000631578947368421</v>
+        <v>0.05961538461538461</v>
       </c>
       <c r="X10">
-        <v>0.1755857654196741</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y10">
-        <v>-0.1762173443670425</v>
+        <v>-0.00269300392041702</v>
       </c>
       <c r="Z10">
-        <v>2.662551440329219</v>
+        <v>0.09705882352941177</v>
       </c>
       <c r="AA10">
-        <v>0.07037037037037039</v>
+        <v>0.0713908325426945</v>
       </c>
       <c r="AB10">
-        <v>0.07081593131935471</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC10">
-        <v>-0.0004455609489843193</v>
+        <v>0.00908244400689287</v>
       </c>
       <c r="AD10">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>33.3</v>
+        <v>-20.8</v>
       </c>
       <c r="AH10">
-        <v>0.7942176870748299</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.6758321273516643</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.7334801762114538</v>
+        <v>-0.361111111111111</v>
       </c>
       <c r="AK10">
-        <v>0.5978456014362658</v>
+        <v>-0.3195084485407066</v>
       </c>
       <c r="AL10">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.763</v>
-      </c>
-      <c r="AN10">
-        <v>8.150087260034903</v>
-      </c>
-      <c r="AO10">
-        <v>1.055555555555555</v>
-      </c>
-      <c r="AP10">
-        <v>5.81151832460733</v>
+        <v>-0.603</v>
       </c>
       <c r="AQ10">
-        <v>1.237785016286645</v>
+        <v>-7.24709784411277</v>
       </c>
     </row>
     <row r="11">
@@ -1719,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Seafire AB (publ) (OM:SEAF)</t>
+          <t>AB Traction (OM:TRAC B)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1728,115 +1740,109 @@
         </is>
       </c>
       <c r="D11">
-        <v>1.289</v>
+        <v>0.0629</v>
+      </c>
+      <c r="E11">
+        <v>0.06269999999999999</v>
       </c>
       <c r="G11">
-        <v>0.0439124487004104</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.04336525307797538</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.05759233926128592</v>
+        <v>0.9468085106382979</v>
       </c>
       <c r="J11">
-        <v>0.02879616963064296</v>
+        <v>0.9297340425531915</v>
       </c>
       <c r="K11">
-        <v>0.367</v>
+        <v>17.5</v>
       </c>
       <c r="L11">
-        <v>0.005020519835841314</v>
+        <v>0.9308510638297872</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>11.9</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.03353057199211046</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.68</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>11.9</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.03353057199211046</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.68</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>21.9</v>
+        <v>18.4</v>
       </c>
       <c r="V11">
-        <v>0.3821989528795812</v>
+        <v>0.05184559030712877</v>
       </c>
       <c r="W11">
-        <v>0.01548523206751055</v>
+        <v>0.05444928438083386</v>
       </c>
       <c r="X11">
-        <v>0.0995021090103827</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y11">
-        <v>-0.08401687694287215</v>
+        <v>-0.007859104154967773</v>
       </c>
       <c r="Z11">
-        <v>2.428571428571429</v>
+        <v>0.06237558062375581</v>
       </c>
       <c r="AA11">
-        <v>0.06993355481727576</v>
+        <v>0.05799270072992701</v>
       </c>
       <c r="AB11">
-        <v>0.07141657282129167</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC11">
-        <v>-0.001483018004015915</v>
+        <v>-0.004315687805874623</v>
       </c>
       <c r="AD11">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>36.1</v>
+        <v>-18.4</v>
       </c>
       <c r="AH11">
-        <v>0.5030355594102341</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.5440900562851783</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>0.386509635974304</v>
+        <v>-0.05468053491827637</v>
       </c>
       <c r="AK11">
-        <v>0.4262101534828808</v>
+        <v>-0.05846838258659039</v>
       </c>
       <c r="AL11">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>4.75</v>
-      </c>
-      <c r="AN11">
-        <v>7.988980716253444</v>
-      </c>
-      <c r="AO11">
-        <v>0.8863157894736842</v>
-      </c>
-      <c r="AP11">
-        <v>4.972451790633609</v>
-      </c>
-      <c r="AQ11">
-        <v>0.8863157894736842</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Transferator AB (publ) (NGM:TRAN A)</t>
+          <t>Case Group AB (publ) (OM:CASE)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1855,26 +1861,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.0336</v>
-      </c>
       <c r="G12">
-        <v>0.08067940552016985</v>
+        <v>0.01520912547528517</v>
       </c>
       <c r="H12">
-        <v>0.08067940552016985</v>
+        <v>0.01520912547528517</v>
       </c>
       <c r="I12">
-        <v>0.02016985138004246</v>
+        <v>0.01197718631178707</v>
       </c>
       <c r="J12">
-        <v>0.02016985138004246</v>
+        <v>0.01197718631178707</v>
       </c>
       <c r="K12">
-        <v>8.59</v>
+        <v>-2.59</v>
       </c>
       <c r="L12">
-        <v>1.823779193205945</v>
+        <v>-0.4923954372623574</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1883,7 +1886,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1892,79 +1895,76 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>0.648</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>0.02666666666666667</v>
       </c>
       <c r="W12">
-        <v>1.199720670391061</v>
+        <v>-0.4504347826086956</v>
       </c>
       <c r="X12">
-        <v>0.0760930027613908</v>
+        <v>0.06545005731911334</v>
       </c>
       <c r="Y12">
-        <v>1.123627667629671</v>
+        <v>-0.515884839927809</v>
       </c>
       <c r="Z12">
-        <v>0.690615835777126</v>
+        <v>1.515850144092219</v>
       </c>
       <c r="AA12">
-        <v>0.01392961876832845</v>
+        <v>0.01815561959654179</v>
       </c>
       <c r="AB12">
-        <v>0.07256861103061113</v>
+        <v>0.0618381814425662</v>
       </c>
       <c r="AC12">
-        <v>-0.05863899226228268</v>
+        <v>-0.04368256184602441</v>
       </c>
       <c r="AD12">
-        <v>1.31</v>
+        <v>4.09</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.31</v>
+        <v>4.09</v>
       </c>
       <c r="AG12">
-        <v>1.31</v>
+        <v>3.442</v>
       </c>
       <c r="AH12">
-        <v>0.1198536139066789</v>
+        <v>0.1440648115533638</v>
       </c>
       <c r="AI12">
-        <v>0.2179700499168054</v>
+        <v>0.1401164782459746</v>
       </c>
       <c r="AJ12">
-        <v>0.1198536139066789</v>
+        <v>0.1240718044841756</v>
       </c>
       <c r="AK12">
-        <v>0.2179700499168054</v>
+        <v>0.1205942120383995</v>
       </c>
       <c r="AL12">
-        <v>0.397</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.397</v>
+        <v>-0.158</v>
       </c>
       <c r="AN12">
-        <v>2.462406015037594</v>
-      </c>
-      <c r="AO12">
-        <v>0.2392947103274559</v>
+        <v>63.90625</v>
       </c>
       <c r="AP12">
-        <v>2.462406015037594</v>
+        <v>53.78124999999999</v>
       </c>
       <c r="AQ12">
-        <v>0.2392947103274559</v>
+        <v>-0.3987341772151899</v>
       </c>
     </row>
     <row r="13">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ACQ Bure AB (publ) (OM:ACQ SPAC)</t>
+          <t>Seafire AB (publ) (OM:SEAF)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1983,8 +1983,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.9790000000000001</v>
+      </c>
+      <c r="G13">
+        <v>0.07703703703703704</v>
+      </c>
+      <c r="H13">
+        <v>0.07703703703703704</v>
+      </c>
+      <c r="I13">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="J13">
+        <v>0.01428571428571429</v>
+      </c>
       <c r="K13">
-        <v>-0.855</v>
+        <v>-5.19</v>
+      </c>
+      <c r="L13">
+        <v>-0.05492063492063493</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2008,64 +2026,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>27.3</v>
+        <v>5.78</v>
       </c>
       <c r="V13">
-        <v>0.08584905660377359</v>
+        <v>0.1823343848580442</v>
       </c>
       <c r="W13">
-        <v>-0.002172808132147395</v>
+        <v>-0.1067901234567901</v>
       </c>
       <c r="X13">
-        <v>0.07245421904070486</v>
+        <v>0.07808882075444612</v>
       </c>
       <c r="Y13">
-        <v>-0.07462702717285224</v>
+        <v>-0.1848789442112362</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.115702479338843</v>
       </c>
       <c r="AA13">
-        <v>-0.003223997757218951</v>
+        <v>0.01593860684769776</v>
       </c>
       <c r="AB13">
-        <v>0.07245421904070486</v>
+        <v>0.06081315100711011</v>
       </c>
       <c r="AC13">
-        <v>-0.0756782167979238</v>
+        <v>-0.04487454415941235</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="AG13">
-        <v>-27.3</v>
+        <v>21.02</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.4581196581196582</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>0.2815126050420168</v>
       </c>
       <c r="AJ13">
-        <v>-0.09391124871001033</v>
+        <v>0.3987101669195751</v>
       </c>
       <c r="AK13">
-        <v>-0.09687721788502483</v>
+        <v>0.2350704540371281</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>6.29</v>
       </c>
       <c r="AM13">
-        <v>-0.306</v>
+        <v>5.712</v>
+      </c>
+      <c r="AN13">
+        <v>5.224171539961014</v>
+      </c>
+      <c r="AO13">
+        <v>0.2146263910969793</v>
+      </c>
+      <c r="AP13">
+        <v>4.097465886939571</v>
       </c>
       <c r="AQ13">
-        <v>3.758169934640523</v>
+        <v>0.2363445378151261</v>
       </c>
     </row>
     <row r="14">
@@ -2076,7 +2103,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aligro Planet Acquisition Company AB (publ) (OM:APAC SPAC A)</t>
+          <t>VNV Global AB (publ) (OM:VNV)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2084,8 +2111,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D14">
+        <v>-0.4</v>
+      </c>
+      <c r="G14">
+        <v>-54.6875</v>
+      </c>
+      <c r="H14">
+        <v>-54.6875</v>
+      </c>
+      <c r="I14">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="J14">
+        <v>0.2722222222222222</v>
+      </c>
       <c r="K14">
-        <v>-0.861</v>
+        <v>-10.6</v>
+      </c>
+      <c r="L14">
+        <v>-0.736111111111111</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2109,67 +2154,73 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0.949</v>
+        <v>50.3</v>
       </c>
       <c r="V14">
-        <v>0.008435555555555556</v>
+        <v>0.1844517785111844</v>
       </c>
       <c r="W14">
-        <v>-0.007493472584856396</v>
+        <v>-0.01534897190848537</v>
       </c>
       <c r="X14">
-        <v>0.07245421904070486</v>
+        <v>0.07221275624382369</v>
       </c>
       <c r="Y14">
-        <v>-0.07994769162556126</v>
+        <v>-0.08756172815230906</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>0.01917443408788282</v>
       </c>
       <c r="AA14">
-        <v>-0.005035335689045936</v>
+        <v>0.00521970705725699</v>
       </c>
       <c r="AB14">
-        <v>0.07245421904070486</v>
+        <v>0.06117690732316895</v>
       </c>
       <c r="AC14">
-        <v>-0.07748955472975079</v>
+        <v>-0.05595720026591196</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>144.7</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>144.7</v>
       </c>
       <c r="AG14">
-        <v>-0.949</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.3466698610445615</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.1692595625219324</v>
       </c>
       <c r="AJ14">
-        <v>-0.008507319522012353</v>
+        <v>0.257150640152547</v>
       </c>
       <c r="AK14">
-        <v>-0.01069283726380548</v>
+        <v>0.1173253790703455</v>
       </c>
       <c r="AL14">
-        <v>0.231</v>
+        <v>9.67</v>
       </c>
       <c r="AM14">
-        <v>0.201</v>
+        <v>9.095000000000001</v>
+      </c>
+      <c r="AN14">
+        <v>36.7258883248731</v>
       </c>
       <c r="AO14">
-        <v>-2.467532467532467</v>
+        <v>0.405377456049638</v>
+      </c>
+      <c r="AP14">
+        <v>23.95939086294416</v>
       </c>
       <c r="AQ14">
-        <v>-2.835820895522388</v>
+        <v>0.4310060472787245</v>
       </c>
     </row>
     <row r="15">
@@ -2180,7 +2231,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Flat Capital AB (publ) (OM:FLAT B)</t>
+          <t>Creaspac AB (publ) (OM:CPAC SPAC)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2188,23 +2239,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>-2.205882352941176</v>
-      </c>
-      <c r="J15">
-        <v>-2.205882352941176</v>
-      </c>
       <c r="K15">
-        <v>-0.224</v>
-      </c>
-      <c r="L15">
-        <v>-1.647058823529412</v>
+        <v>5.48</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2213,7 +2249,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2222,37 +2258,37 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>6.98</v>
+        <v>1.84</v>
       </c>
       <c r="V15">
-        <v>0.2406896551724138</v>
+        <v>0.007622203811101905</v>
       </c>
       <c r="W15">
-        <v>-0.009955555555555556</v>
+        <v>0.02479638009049774</v>
       </c>
       <c r="X15">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y15">
-        <v>-0.08240977459626041</v>
+        <v>-0.03751200844530389</v>
       </c>
       <c r="Z15">
-        <v>0.006219132979696361</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>-0.01371867569050668</v>
+        <v>-0.002785108625356296</v>
       </c>
       <c r="AB15">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC15">
-        <v>-0.08617289473121154</v>
+        <v>-0.06509349716115793</v>
       </c>
       <c r="AD15">
         <v>0</v>
@@ -2264,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>-6.98</v>
+        <v>-1.84</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2273,19 +2309,19 @@
         <v>0</v>
       </c>
       <c r="AJ15">
-        <v>-0.3169845594913715</v>
+        <v>-0.007680748038069795</v>
       </c>
       <c r="AK15">
-        <v>-0.2735109717868339</v>
+        <v>-0.00803633822501747</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.076</v>
+        <v>-6.44</v>
       </c>
       <c r="AQ15">
-        <v>3.947368421052631</v>
+        <v>0.09223602484472049</v>
       </c>
     </row>
     <row r="16">
@@ -2296,7 +2332,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AB Traction (OM:TRAC B)</t>
+          <t>Catella AB (publ) (OM:CAT B)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2304,26 +2340,50 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D16">
+        <v>-0.0126</v>
+      </c>
+      <c r="E16">
+        <v>0.114</v>
+      </c>
+      <c r="F16">
+        <v>0.09699999999999999</v>
+      </c>
+      <c r="G16">
+        <v>0.229897463572585</v>
+      </c>
+      <c r="H16">
+        <v>0.229897463572585</v>
+      </c>
+      <c r="I16">
+        <v>-0.06098219104155424</v>
+      </c>
+      <c r="J16">
+        <v>-0.04350062960964202</v>
+      </c>
       <c r="K16">
-        <v>-9.69</v>
+        <v>13.9</v>
+      </c>
+      <c r="L16">
+        <v>0.07501349163518618</v>
       </c>
       <c r="M16">
-        <v>6.46</v>
+        <v>9.73</v>
       </c>
       <c r="N16">
-        <v>0.02157648630594523</v>
+        <v>0.03429679238632358</v>
       </c>
       <c r="O16">
-        <v>-0.6666666666666667</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="P16">
-        <v>6.46</v>
+        <v>9.73</v>
       </c>
       <c r="Q16">
-        <v>0.02157648630594523</v>
+        <v>0.03429679238632358</v>
       </c>
       <c r="R16">
-        <v>-0.6666666666666667</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2332,61 +2392,73 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>20</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="V16">
-        <v>0.06680026720106881</v>
+        <v>0.3239337328163553</v>
       </c>
       <c r="W16">
-        <v>-0.0233437725849193</v>
+        <v>0.07574931880108993</v>
       </c>
       <c r="X16">
-        <v>0.07245421904070486</v>
+        <v>0.07748040584530658</v>
       </c>
       <c r="Y16">
-        <v>-0.09579799162562415</v>
+        <v>-0.00173108704421665</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>0.6738181818181819</v>
       </c>
       <c r="AA16">
-        <v>-0.02657595112468759</v>
+        <v>-0.02931151515151516</v>
       </c>
       <c r="AB16">
-        <v>0.07245421904070486</v>
+        <v>0.05877581622304778</v>
       </c>
       <c r="AC16">
-        <v>-0.09903017016539245</v>
+        <v>-0.08808733137456294</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>230.6</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>230.6</v>
       </c>
       <c r="AG16">
-        <v>-20</v>
+        <v>138.7</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.4483764339879448</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.5405532114392874</v>
       </c>
       <c r="AJ16">
-        <v>-0.07158196134574088</v>
+        <v>0.3283617424242424</v>
       </c>
       <c r="AK16">
-        <v>-0.06635700066357002</v>
+        <v>0.4144009560800717</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>12.6</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>7.64</v>
+      </c>
+      <c r="AN16">
+        <v>-25.39647577092511</v>
+      </c>
+      <c r="AO16">
+        <v>-0.8968253968253969</v>
+      </c>
+      <c r="AP16">
+        <v>-15.27533039647577</v>
+      </c>
+      <c r="AQ16">
+        <v>-1.479057591623037</v>
       </c>
     </row>
     <row r="17">
@@ -2397,7 +2469,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DS Plattformen AB (NGM:DSPAB B)</t>
+          <t>Abelco Investment Group AB (NGM:ABIG)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2405,113 +2477,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D17">
-        <v>-0.124</v>
-      </c>
       <c r="G17">
-        <v>0</v>
+        <v>-2.403183023872679</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>-2.403183023872679</v>
       </c>
       <c r="I17">
-        <v>-0.0944927536231884</v>
+        <v>-1.206896551724138</v>
       </c>
       <c r="J17">
-        <v>-0.0944927536231884</v>
+        <v>-1.206896551724138</v>
       </c>
       <c r="K17">
-        <v>-0.31</v>
+        <v>-5.49</v>
       </c>
       <c r="L17">
-        <v>-0.08985507246376812</v>
+        <v>-14.56233421750663</v>
       </c>
       <c r="M17">
-        <v>4.11</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>2.024630541871922</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>-13.25806451612903</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.11</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>2.024630541871922</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>-13.25806451612903</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0.045</v>
+        <v>0.244</v>
       </c>
       <c r="V17">
-        <v>0.02216748768472906</v>
+        <v>0.04979591836734693</v>
       </c>
       <c r="W17">
-        <v>-0.03546910755148741</v>
+        <v>-0.4007299270072993</v>
       </c>
       <c r="X17">
-        <v>0.07245421904070486</v>
+        <v>0.07270782795579639</v>
       </c>
       <c r="Y17">
-        <v>-0.1079233265921923</v>
+        <v>-0.4734377549630957</v>
       </c>
       <c r="Z17">
-        <v>0.4026140739876298</v>
+        <v>0.02233015459337796</v>
       </c>
       <c r="AA17">
-        <v>-0.03804411249854125</v>
+        <v>-0.02695018657821478</v>
       </c>
       <c r="AB17">
-        <v>0.07245421904070486</v>
+        <v>0.06114058611840135</v>
       </c>
       <c r="AC17">
-        <v>-0.1104983315392461</v>
+        <v>-0.08809077269661612</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AG17">
-        <v>-0.045</v>
+        <v>2.486</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>0.3577981651376146</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>0.2284518828451883</v>
       </c>
       <c r="AJ17">
-        <v>-0.02267002518891688</v>
+        <v>0.3365827240725697</v>
       </c>
       <c r="AK17">
-        <v>-0.1136363636363636</v>
+        <v>0.2123697249273876</v>
       </c>
       <c r="AL17">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="AM17">
-        <v>2.43</v>
+        <v>2.17</v>
+      </c>
+      <c r="AN17">
+        <v>-6.176470588235294</v>
       </c>
       <c r="AO17">
-        <v>-0.1341563786008231</v>
+        <v>-0.2096774193548387</v>
+      </c>
+      <c r="AP17">
+        <v>-5.624434389140271</v>
       </c>
       <c r="AQ17">
-        <v>-0.1341563786008231</v>
+        <v>-0.2096774193548387</v>
       </c>
     </row>
     <row r="18">
@@ -2522,7 +2594,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Havsfrun Investment AB (publ) (OM:HAV B)</t>
+          <t>VEF AB (publ) (OM:VEFAB)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2531,16 +2603,16 @@
         </is>
       </c>
       <c r="K18">
-        <v>-0.624</v>
+        <v>-20.9</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>1.65</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.008688783570300158</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0.07894736842105263</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2552,34 +2624,37 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.65</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>9.43</v>
+        <v>6.73</v>
       </c>
       <c r="V18">
-        <v>0.5482558139534883</v>
+        <v>0.03543970510795155</v>
       </c>
       <c r="W18">
-        <v>-0.039</v>
+        <v>-0.04697684873005169</v>
       </c>
       <c r="X18">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y18">
-        <v>-0.1114542190407048</v>
+        <v>-0.1092852372658533</v>
       </c>
       <c r="Z18">
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>-0.08758620689655172</v>
+        <v>-0.03058232090490155</v>
       </c>
       <c r="AB18">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC18">
-        <v>-0.1600404259372566</v>
+        <v>-0.09289070944070318</v>
       </c>
       <c r="AD18">
         <v>0</v>
@@ -2591,7 +2666,7 @@
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>-9.43</v>
+        <v>-6.73</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -2600,22 +2675,28 @@
         <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-1.213642213642214</v>
+        <v>-0.03674182453458535</v>
       </c>
       <c r="AK18">
-        <v>-3.669260700389104</v>
+        <v>-0.01617905137389716</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>5.159999999999999</v>
       </c>
       <c r="AN18">
         <v>-0</v>
       </c>
+      <c r="AO18">
+        <v>-2.708719851576995</v>
+      </c>
       <c r="AP18">
-        <v>18.59960552268245</v>
+        <v>0.4609589041095891</v>
+      </c>
+      <c r="AQ18">
+        <v>-2.829457364341085</v>
       </c>
     </row>
     <row r="19">
@@ -2626,7 +2707,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>First Venture Sweden AB (publ) (OM:FIRST B)</t>
+          <t>Transferator AB (publ) (NGM:TRAN A)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2634,104 +2715,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D19">
+        <v>0.0762</v>
+      </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.1351669941060904</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>0.1351669941060904</v>
       </c>
       <c r="I19">
-        <v>-110</v>
+        <v>-0.04027504911591356</v>
       </c>
       <c r="J19">
-        <v>-110</v>
+        <v>-0.04027504911591356</v>
       </c>
       <c r="K19">
-        <v>-2.65</v>
+        <v>2.15</v>
       </c>
       <c r="L19">
-        <v>-203.8461538461538</v>
+        <v>0.4223968565815324</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>2.1164</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.08332283464566929</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>0.9843720930232559</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>2.1164</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.08332283464566929</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>0.9843720930232559</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
       <c r="U19">
-        <v>3.67</v>
+        <v>0.119</v>
       </c>
       <c r="V19">
-        <v>0.2621428571428571</v>
+        <v>0.00468503937007874</v>
       </c>
       <c r="W19">
-        <v>-0.07507082152974505</v>
+        <v>0.4574468085106382</v>
       </c>
       <c r="X19">
-        <v>0.07245421904070486</v>
+        <v>0.06347682948819959</v>
       </c>
       <c r="Y19">
-        <v>-0.1475250405704499</v>
+        <v>0.3939699790224386</v>
       </c>
       <c r="Z19">
-        <v>0.0009352517985611511</v>
+        <v>0.8469217970049917</v>
       </c>
       <c r="AA19">
-        <v>-0.1028776978417266</v>
+        <v>-0.03410981697171381</v>
       </c>
       <c r="AB19">
-        <v>0.07245421904070486</v>
+        <v>0.06224095509597145</v>
       </c>
       <c r="AC19">
-        <v>-0.1753319168824315</v>
+        <v>-0.09635077206768526</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG19">
-        <v>-3.67</v>
+        <v>1.471</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.05891070766950723</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>0.2472783825816486</v>
       </c>
       <c r="AJ19">
-        <v>-0.3552758954501452</v>
+        <v>0.05474303152097057</v>
       </c>
       <c r="AK19">
-        <v>-0.1712552496500233</v>
+        <v>0.2330850895262241</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="AM19">
-        <v>-0.115</v>
+        <v>-1.946</v>
+      </c>
+      <c r="AN19">
+        <v>3.541202672605791</v>
+      </c>
+      <c r="AO19">
+        <v>-2.180851063829787</v>
+      </c>
+      <c r="AP19">
+        <v>3.276169265033408</v>
       </c>
       <c r="AQ19">
-        <v>12.43478260869565</v>
+        <v>0.105344295991778</v>
       </c>
     </row>
     <row r="20">
@@ -2742,7 +2838,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VEF AB (Publ) (OM:VEFAB)</t>
+          <t>First Venture Sweden AB (publ) (OM:FIRST B)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2751,16 +2847,16 @@
         </is>
       </c>
       <c r="K20">
-        <v>-107.9</v>
+        <v>-6.7</v>
       </c>
       <c r="M20">
-        <v>1.26</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.005140758873929009</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0.01167747914735866</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2772,79 +2868,67 @@
         <v>0</v>
       </c>
       <c r="S20">
-        <v>1.26</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>10.7</v>
+        <v>0.406</v>
       </c>
       <c r="V20">
-        <v>0.04365565075479396</v>
+        <v>0.03903846153846154</v>
       </c>
       <c r="W20">
-        <v>-0.1949060693641619</v>
+        <v>-0.2669322709163346</v>
       </c>
       <c r="X20">
-        <v>0.07716399723928261</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y20">
-        <v>-0.2720700666034445</v>
+        <v>-0.3292406594521363</v>
       </c>
       <c r="Z20">
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>-0.2053062346320075</v>
+        <v>-0.0597293513765749</v>
       </c>
       <c r="AB20">
-        <v>0.07214512564463464</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC20">
-        <v>-0.2774513602766421</v>
+        <v>-0.1220377399123765</v>
       </c>
       <c r="AD20">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>32.5</v>
+        <v>-0.406</v>
       </c>
       <c r="AH20">
-        <v>0.149843912591051</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>0.08850645359557469</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>0.1170749279538905</v>
+        <v>-0.04062437462477487</v>
       </c>
       <c r="AK20">
-        <v>0.06807708420611647</v>
+        <v>-0.02195306585919758</v>
       </c>
       <c r="AL20">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>1.789</v>
-      </c>
-      <c r="AN20">
-        <v>-0.3881401617250674</v>
-      </c>
-      <c r="AO20">
-        <v>-62.17877094972066</v>
-      </c>
-      <c r="AP20">
-        <v>-0.2920035938903863</v>
+        <v>-0.031</v>
       </c>
       <c r="AQ20">
-        <v>-62.21352711011738</v>
+        <v>41.29032258064516</v>
       </c>
     </row>
     <row r="21">
@@ -2855,7 +2939,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Linc AB (OM:LINC)</t>
+          <t>eBlitz Group AB (publ) (NGM:EBLITZ)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2863,8 +2947,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G21">
+        <v>-3.090909090909091</v>
+      </c>
+      <c r="H21">
+        <v>-3.090909090909091</v>
+      </c>
+      <c r="I21">
+        <v>-3.363636363636364</v>
+      </c>
+      <c r="J21">
+        <v>-3.363636363636364</v>
+      </c>
       <c r="K21">
-        <v>-72.8</v>
+        <v>-0.634</v>
+      </c>
+      <c r="L21">
+        <v>-5.763636363636364</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -2888,31 +2987,31 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>57.2</v>
+        <v>0.106</v>
       </c>
       <c r="V21">
-        <v>0.1731759006963367</v>
+        <v>0.09906542056074766</v>
       </c>
       <c r="W21">
-        <v>-0.1761432373578514</v>
+        <v>-0.2330882352941176</v>
       </c>
       <c r="X21">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y21">
-        <v>-0.2485974563985563</v>
+        <v>-0.2953966238299193</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>0.04623791509037411</v>
       </c>
       <c r="AA21">
-        <v>-0.2808197246237592</v>
+        <v>-0.1555275325767129</v>
       </c>
       <c r="AB21">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC21">
-        <v>-0.3532739436644641</v>
+        <v>-0.2178359211125145</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -2924,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>-57.2</v>
+        <v>-0.106</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -2933,19 +3032,25 @@
         <v>0</v>
       </c>
       <c r="AJ21">
-        <v>-0.2094470889783962</v>
+        <v>-0.1099585062240664</v>
       </c>
       <c r="AK21">
-        <v>-0.2924335378323108</v>
+        <v>-0.039939713639789</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-0.024</v>
+        <v>-0.001</v>
+      </c>
+      <c r="AN21">
+        <v>-0</v>
+      </c>
+      <c r="AP21">
+        <v>0.2969187675070028</v>
       </c>
       <c r="AQ21">
-        <v>3654.166666666667</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22">
@@ -2956,7 +3061,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Northern CapSek Ventures AB (publ) (NGM:CAPS)</t>
+          <t>Nordic Asia Investment Group 1987 AB (publ) (OM:NAIG B)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2964,84 +3069,72 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G22">
-        <v>-39.63636363636364</v>
-      </c>
-      <c r="H22">
-        <v>-39.63636363636364</v>
-      </c>
-      <c r="I22">
-        <v>-66.54545454545455</v>
-      </c>
-      <c r="J22">
-        <v>-66.54545454545455</v>
-      </c>
       <c r="K22">
+        <v>-2.7</v>
+      </c>
+      <c r="M22">
+        <v>0.284</v>
+      </c>
+      <c r="N22">
+        <v>0.02581818181818182</v>
+      </c>
+      <c r="O22">
+        <v>-0.1051851851851852</v>
+      </c>
+      <c r="P22">
+        <v>0.284</v>
+      </c>
+      <c r="Q22">
+        <v>0.02581818181818182</v>
+      </c>
+      <c r="R22">
+        <v>-0.1051851851851852</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>2.1</v>
+      </c>
+      <c r="V22">
+        <v>0.1909090909090909</v>
+      </c>
+      <c r="W22">
+        <v>-0.1370558375634518</v>
+      </c>
+      <c r="X22">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1993642260992534</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>-0.1766217084136159</v>
+      </c>
+      <c r="AB22">
+        <v>0.06230838853580163</v>
+      </c>
+      <c r="AC22">
+        <v>-0.2389300969494176</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
         <v>-2.1</v>
       </c>
-      <c r="L22">
-        <v>-190.9090909090909</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0.2</v>
-      </c>
-      <c r="V22">
-        <v>0.108695652173913</v>
-      </c>
-      <c r="W22">
-        <v>-0.4233870967741936</v>
-      </c>
-      <c r="X22">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y22">
-        <v>-0.4958413158148984</v>
-      </c>
-      <c r="Z22">
-        <v>0.004435483870967742</v>
-      </c>
-      <c r="AA22">
-        <v>-0.2951612903225806</v>
-      </c>
-      <c r="AB22">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC22">
-        <v>-0.3676155093632855</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>-0.2</v>
-      </c>
       <c r="AH22">
         <v>0</v>
       </c>
@@ -3049,28 +3142,28 @@
         <v>0</v>
       </c>
       <c r="AJ22">
-        <v>-0.1219512195121951</v>
+        <v>-0.2359550561797753</v>
       </c>
       <c r="AK22">
-        <v>-0.0664451827242525</v>
+        <v>-0.1532846715328467</v>
       </c>
       <c r="AL22">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="AM22">
-        <v>0.014</v>
+        <v>-0.046</v>
       </c>
       <c r="AN22">
         <v>-0</v>
       </c>
       <c r="AO22">
-        <v>-52.28571428571428</v>
+        <v>-458.3333333333333</v>
       </c>
       <c r="AP22">
-        <v>0.5037783375314862</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AQ22">
-        <v>-52.28571428571428</v>
+        <v>59.78260869565217</v>
       </c>
     </row>
     <row r="23">
@@ -3081,7 +3174,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bure Equity AB (publ) (OM:BURE)</t>
+          <t>Katalysen Ventures AB (publ) (NGM:KAV)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3089,101 +3182,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G23">
+        <v>-5.640138408304498</v>
+      </c>
+      <c r="H23">
+        <v>-5.640138408304498</v>
+      </c>
+      <c r="I23">
+        <v>-6.678200692041523</v>
+      </c>
+      <c r="J23">
+        <v>-6.678200692041523</v>
+      </c>
       <c r="K23">
-        <v>-933.9</v>
+        <v>-3.71</v>
+      </c>
+      <c r="L23">
+        <v>-12.83737024221453</v>
       </c>
       <c r="M23">
-        <v>28.4</v>
+        <v>-0</v>
       </c>
       <c r="N23">
-        <v>0.01620357163233868</v>
+        <v>-0</v>
       </c>
       <c r="O23">
-        <v>-0.03041010814862405</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>28.4</v>
+        <v>-0</v>
       </c>
       <c r="Q23">
-        <v>0.01620357163233868</v>
+        <v>-0</v>
       </c>
       <c r="R23">
-        <v>-0.03041010814862405</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
       <c r="U23">
-        <v>39.2</v>
+        <v>0.042</v>
       </c>
       <c r="V23">
-        <v>0.02236549323900268</v>
+        <v>0.004620462046204621</v>
       </c>
       <c r="W23">
-        <v>-0.360523471278567</v>
+        <v>-0.419683257918552</v>
       </c>
       <c r="X23">
-        <v>0.07245833542769517</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y23">
-        <v>-0.4329818067062622</v>
+        <v>-0.4819916464543537</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>0.03472722903148281</v>
       </c>
       <c r="AA23">
-        <v>-0.3713656745024996</v>
+        <v>-0.231915404950733</v>
       </c>
       <c r="AB23">
-        <v>0.07245390132410784</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC23">
-        <v>-0.4438195758266074</v>
+        <v>-0.2942237934865347</v>
       </c>
       <c r="AD23">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>-38.93</v>
+        <v>-0.042</v>
       </c>
       <c r="AH23">
-        <v>0.0001540243130230409</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>0.0002469655254420226</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>-0.02271600039678603</v>
+        <v>-0.004641909814323607</v>
       </c>
       <c r="AK23">
-        <v>-0.03693303101312057</v>
+        <v>-0.005484460694698354</v>
       </c>
       <c r="AL23">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>-0.7200000000000001</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="AN23">
-        <v>-0.0002892650524962503</v>
-      </c>
-      <c r="AO23">
-        <v>-10376.66666666667</v>
+        <v>-0</v>
       </c>
       <c r="AP23">
-        <v>0.04170773516177416</v>
+        <v>0.0227027027027027</v>
       </c>
       <c r="AQ23">
-        <v>1297.083333333333</v>
+        <v>26.80555555555556</v>
       </c>
     </row>
     <row r="24">
@@ -3194,7 +3296,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nordic Asia Investment Group 1987 AB (publ) (OM:NAIG B)</t>
+          <t>Flat Capital AB (publ) (OM:FLAT B)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3203,58 +3305,55 @@
         </is>
       </c>
       <c r="K24">
-        <v>-5.28</v>
+        <v>-6.64</v>
       </c>
       <c r="M24">
-        <v>1.736</v>
+        <v>-0</v>
       </c>
       <c r="N24">
-        <v>0.09591160220994474</v>
+        <v>-0</v>
       </c>
       <c r="O24">
-        <v>-0.3287878787878788</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>0.266</v>
+        <v>-0</v>
       </c>
       <c r="Q24">
-        <v>0.01469613259668508</v>
+        <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0.05037878787878788</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>1.47</v>
-      </c>
-      <c r="T24">
-        <v>0.8467741935483871</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>4.13</v>
+        <v>15.7</v>
       </c>
       <c r="V24">
-        <v>0.2281767955801105</v>
+        <v>0.2674616695059625</v>
       </c>
       <c r="W24">
-        <v>-0.4292682926829268</v>
+        <v>-0.2043076923076923</v>
       </c>
       <c r="X24">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y24">
-        <v>-0.5017225117236317</v>
+        <v>-0.2666160808434939</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>-0.4835164835164835</v>
+        <v>-0.2641065830721003</v>
       </c>
       <c r="AB24">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC24">
-        <v>-0.5559707025571883</v>
+        <v>-0.3264149716079019</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -3266,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>-4.13</v>
+        <v>-15.7</v>
       </c>
       <c r="AH24">
         <v>0</v>
@@ -3275,16 +3374,25 @@
         <v>0</v>
       </c>
       <c r="AJ24">
-        <v>-0.2956335003579098</v>
+        <v>-0.3651162790697674</v>
       </c>
       <c r="AK24">
-        <v>-0.2652536929993577</v>
+        <v>-0.6408163265306122</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>-0.078</v>
+      </c>
+      <c r="AN24">
+        <v>-0</v>
+      </c>
+      <c r="AP24">
+        <v>2.329376854599406</v>
+      </c>
+      <c r="AQ24">
+        <v>86.41025641025641</v>
       </c>
     </row>
     <row r="25">
@@ -3295,7 +3403,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VNV Global AB (publ) (OM:VNV)</t>
+          <t>Northern CapSek Ventures AB (publ) (NGM:CAPS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3303,17 +3411,32 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G25">
+        <v>-30.26666666666667</v>
+      </c>
+      <c r="H25">
+        <v>-30.26666666666667</v>
+      </c>
+      <c r="I25">
+        <v>-57.6</v>
+      </c>
+      <c r="J25">
+        <v>-57.6</v>
+      </c>
       <c r="K25">
-        <v>-917.9</v>
+        <v>-0.913</v>
+      </c>
+      <c r="L25">
+        <v>-60.86666666666667</v>
       </c>
       <c r="M25">
-        <v>11</v>
+        <v>-0</v>
       </c>
       <c r="N25">
-        <v>0.03842123646524624</v>
+        <v>-0</v>
       </c>
       <c r="O25">
-        <v>-0.01198387623924175</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>-0</v>
@@ -3325,79 +3448,73 @@
         <v>0</v>
       </c>
       <c r="S25">
-        <v>11</v>
-      </c>
-      <c r="T25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>90.09999999999999</v>
+        <v>0.356</v>
       </c>
       <c r="V25">
-        <v>0.3147048550471533</v>
+        <v>0.2617647058823529</v>
       </c>
       <c r="W25">
-        <v>-0.6158749329039184</v>
+        <v>-0.284423676012461</v>
       </c>
       <c r="X25">
-        <v>0.08650094699287778</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y25">
-        <v>-0.7023758798967962</v>
+        <v>-0.3467320645482627</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>0.00679040289723857</v>
       </c>
       <c r="AA25">
-        <v>-0.5911591728324795</v>
+        <v>-0.3911272068809417</v>
       </c>
       <c r="AB25">
-        <v>0.07174348929501123</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC25">
-        <v>-0.6629026621274907</v>
+        <v>-0.4534355954167433</v>
       </c>
       <c r="AD25">
-        <v>150.5</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>150.5</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>60.40000000000001</v>
+        <v>-0.356</v>
       </c>
       <c r="AH25">
-        <v>0.344551282051282</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>0.1789323504934015</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>0.1742140178828959</v>
+        <v>-0.3545816733067729</v>
       </c>
       <c r="AK25">
-        <v>0.08042609853528629</v>
+        <v>-0.1104218362282878</v>
       </c>
       <c r="AL25">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>12.996</v>
+        <v>-0.015</v>
       </c>
       <c r="AN25">
-        <v>-0.1609970047068892</v>
-      </c>
-      <c r="AO25">
-        <v>-71.9076923076923</v>
+        <v>-0</v>
       </c>
       <c r="AP25">
-        <v>-0.06461275139067181</v>
+        <v>0.7049504950495049</v>
       </c>
       <c r="AQ25">
-        <v>-71.92982456140351</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="26">
@@ -3416,101 +3533,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G26">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="H26">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="I26">
+        <v>-1.812121212121212</v>
+      </c>
+      <c r="J26">
+        <v>-1.812121212121212</v>
+      </c>
       <c r="K26">
-        <v>-10.4</v>
+        <v>-4.02</v>
+      </c>
+      <c r="L26">
+        <v>-1.218181818181818</v>
       </c>
       <c r="M26">
-        <v>66.968</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.9445416078984485</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>-6.439230769230769</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>66.96000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.9444287729196051</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>-6.438461538461539</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>0.007999999999995566</v>
-      </c>
-      <c r="T26">
-        <v>0.0001194600406163476</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>59.3</v>
+        <v>49.3</v>
       </c>
       <c r="V26">
-        <v>0.8363892806770098</v>
+        <v>1.157276995305164</v>
       </c>
       <c r="W26">
-        <v>-0.3104477611940298</v>
+        <v>-0.05622377622377622</v>
       </c>
       <c r="X26">
-        <v>0.07246929461188586</v>
+        <v>0.06232240968922693</v>
       </c>
       <c r="Y26">
-        <v>-0.3829170558059157</v>
+        <v>-0.1185461859130031</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>0.2696078431372547</v>
       </c>
       <c r="AA26">
-        <v>-0.6994547557415871</v>
+        <v>-0.4885620915032676</v>
       </c>
       <c r="AB26">
-        <v>0.07245305593434886</v>
+        <v>0.06230593865174205</v>
       </c>
       <c r="AC26">
-        <v>-0.7719078116759359</v>
+        <v>-0.5508680301550097</v>
       </c>
       <c r="AD26">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="AG26">
-        <v>-59.26</v>
+        <v>-49.268</v>
       </c>
       <c r="AH26">
-        <v>0.0005638567803777839</v>
+        <v>0.0007506098705197974</v>
       </c>
       <c r="AI26">
-        <v>0.0005591277606933184</v>
+        <v>0.0004997501249375313</v>
       </c>
       <c r="AJ26">
-        <v>-5.091065292096216</v>
+        <v>7.388722255548891</v>
       </c>
       <c r="AK26">
-        <v>-4.841503267973855</v>
+        <v>-3.344284550638067</v>
       </c>
       <c r="AL26">
-        <v>0.017</v>
+        <v>0.309</v>
       </c>
       <c r="AM26">
-        <v>-1.813</v>
+        <v>-0.871</v>
       </c>
       <c r="AN26">
-        <v>-0.003539823008849557</v>
+        <v>-0.006956521739130435</v>
       </c>
       <c r="AO26">
-        <v>-747.0588235294117</v>
+        <v>-19.35275080906149</v>
       </c>
       <c r="AP26">
-        <v>5.244247787610619</v>
+        <v>10.7104347826087</v>
       </c>
       <c r="AQ26">
-        <v>7.00496414782129</v>
+        <v>6.865671641791045</v>
       </c>
     </row>
     <row r="27">
@@ -3521,7 +3650,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>byNordic Acquisition Corporation (NasdaqGM:BYNO)</t>
+          <t>oodash Group AB (publ) (OM:OODA)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3529,8 +3658,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G27">
+        <v>-0.06260162601626017</v>
+      </c>
+      <c r="H27">
+        <v>-0.08699186991869919</v>
+      </c>
+      <c r="I27">
+        <v>-0.4065040650406504</v>
+      </c>
+      <c r="J27">
+        <v>-0.4065040650406504</v>
+      </c>
       <c r="K27">
-        <v>-0.14</v>
+        <v>-15.2</v>
+      </c>
+      <c r="L27">
+        <v>-1.235772357723577</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3554,64 +3698,73 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>1.03</v>
+        <v>0.049</v>
       </c>
       <c r="V27">
-        <v>0.004217854217854218</v>
+        <v>0.02987804878048781</v>
       </c>
       <c r="W27">
-        <v>4.375</v>
+        <v>-0.8172043010752688</v>
       </c>
       <c r="X27">
-        <v>0.07245421904070486</v>
+        <v>0.08848583923341195</v>
       </c>
       <c r="Y27">
-        <v>4.302545780959295</v>
+        <v>-0.9056901403086807</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.43859649122807</v>
       </c>
       <c r="AA27">
-        <v>-2.508417508417508</v>
+        <v>-0.5847953216374268</v>
       </c>
       <c r="AB27">
-        <v>0.07245421904070486</v>
+        <v>0.06504924013776539</v>
       </c>
       <c r="AC27">
-        <v>-2.580871727458213</v>
+        <v>-0.6498445617751921</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG27">
-        <v>-1.03</v>
+        <v>2.251</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>0.5837563451776649</v>
       </c>
       <c r="AI27">
-        <v>-0</v>
+        <v>0.1631205673758865</v>
       </c>
       <c r="AJ27">
-        <v>-0.004235719866759881</v>
+        <v>0.578514520688769</v>
       </c>
       <c r="AK27">
-        <v>0.1672077922077922</v>
+        <v>0.1602021208454914</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>0.742</v>
       </c>
       <c r="AM27">
-        <v>-0.805</v>
+        <v>0.629</v>
+      </c>
+      <c r="AN27">
+        <v>-1.138613861386139</v>
+      </c>
+      <c r="AO27">
+        <v>-6.738544474393531</v>
+      </c>
+      <c r="AP27">
+        <v>-1.114356435643564</v>
       </c>
       <c r="AQ27">
-        <v>0.9254658385093167</v>
+        <v>-7.94912559618442</v>
       </c>
     </row>
     <row r="28">
@@ -3622,7 +3775,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EPTI AB (OM:EPTI)</t>
+          <t>byNordic Acquisition Corporation (NasdaqGM:BYNO)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3630,32 +3783,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G28">
-        <v>-0.267</v>
-      </c>
-      <c r="H28">
-        <v>-0.267</v>
-      </c>
-      <c r="I28">
-        <v>-0.4635</v>
-      </c>
-      <c r="J28">
-        <v>-0.4635</v>
-      </c>
       <c r="K28">
-        <v>-16.2</v>
-      </c>
-      <c r="L28">
-        <v>-0.8099999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="M28">
-        <v>-0</v>
+        <v>145.6</v>
       </c>
       <c r="N28">
-        <v>-0</v>
+        <v>1.294222222222222</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>32.7191011235955</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3664,64 +3802,64 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>145.6</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
       </c>
       <c r="U28">
-        <v>0.38</v>
+        <v>0.923</v>
       </c>
       <c r="V28">
-        <v>0.02261904761904762</v>
+        <v>0.008204444444444445</v>
+      </c>
+      <c r="W28">
+        <v>-0.8674463937621832</v>
       </c>
       <c r="X28">
-        <v>0.07679645465243179</v>
+        <v>0.06284595955812752</v>
+      </c>
+      <c r="Y28">
+        <v>-0.9302923533203108</v>
       </c>
       <c r="AB28">
-        <v>0.0721658749698338</v>
+        <v>0.06227634483954853</v>
       </c>
       <c r="AD28">
-        <v>2.73</v>
+        <v>3.24</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.73</v>
+        <v>3.24</v>
       </c>
       <c r="AG28">
-        <v>2.35</v>
+        <v>2.317</v>
       </c>
       <c r="AH28">
-        <v>0.1397849462365591</v>
+        <v>0.02799377916018663</v>
       </c>
       <c r="AI28">
-        <v>0.1329761324890404</v>
+        <v>-0.4589235127478754</v>
       </c>
       <c r="AJ28">
-        <v>0.1227154046997389</v>
+        <v>0.0201799385108477</v>
       </c>
       <c r="AK28">
-        <v>0.1166253101736973</v>
+        <v>-0.2902417637479644</v>
       </c>
       <c r="AL28">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>0.133</v>
-      </c>
-      <c r="AN28">
-        <v>-0.4542429284525791</v>
-      </c>
-      <c r="AO28">
-        <v>-63.06122448979592</v>
-      </c>
-      <c r="AP28">
-        <v>-0.3910149750415974</v>
+        <v>-4.83</v>
       </c>
       <c r="AQ28">
-        <v>-69.69924812030077</v>
+        <v>0.3043478260869565</v>
       </c>
     </row>
     <row r="29">
@@ -3741,22 +3879,22 @@
         </is>
       </c>
       <c r="G29">
-        <v>-0.4840659340659341</v>
+        <v>-1.45748987854251</v>
       </c>
       <c r="H29">
-        <v>-0.4840659340659341</v>
+        <v>-1.45748987854251</v>
       </c>
       <c r="I29">
-        <v>-0.7912087912087912</v>
+        <v>-1.95864567539249</v>
       </c>
       <c r="J29">
-        <v>-0.7912087912087912</v>
+        <v>-1.95864567539249</v>
       </c>
       <c r="K29">
-        <v>-1.44</v>
+        <v>-0.86</v>
       </c>
       <c r="L29">
-        <v>-0.7912087912087912</v>
+        <v>-0.8704453441295547</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3780,55 +3918,64 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1.17</v>
+        <v>0.92</v>
       </c>
       <c r="V29">
-        <v>0.5545023696682464</v>
+        <v>0.8</v>
+      </c>
+      <c r="W29">
+        <v>-0.5029239766081871</v>
       </c>
       <c r="X29">
-        <v>0.07245421904070486</v>
+        <v>0.0624010616969601</v>
+      </c>
+      <c r="Y29">
+        <v>-0.5653250383051472</v>
       </c>
       <c r="AB29">
-        <v>0.07245421904070486</v>
+        <v>0.06229226386036436</v>
       </c>
       <c r="AD29">
         <v>0</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>0.005709636438899753</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>0.005709636438899753</v>
       </c>
       <c r="AG29">
-        <v>-1.17</v>
+        <v>-0.9142903635611003</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>0.004940372788179664</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>0.003076794088247839</v>
       </c>
       <c r="AJ29">
-        <v>-1.24468085106383</v>
+        <v>-3.878884110867065</v>
       </c>
       <c r="AK29">
-        <v>-1.329545454545455</v>
+        <v>-0.9771090602857138</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AM29">
-        <v>-0.031</v>
+        <v>0.182</v>
       </c>
       <c r="AN29">
         <v>-0</v>
       </c>
+      <c r="AO29">
+        <v>-10.65934065934066</v>
+      </c>
       <c r="AP29">
-        <v>1.044642857142857</v>
+        <v>0.5772035123491794</v>
       </c>
       <c r="AQ29">
-        <v>46.45161290322581</v>
+        <v>-10.65934065934066</v>
       </c>
     </row>
     <row r="30">
@@ -3839,7 +3986,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Creaspac AB (publ) (OM:CPAC SPAC)</t>
+          <t>Cardeon AB (publ) (NGM:CARDEO)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3847,17 +3994,32 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G30">
+        <v>-2.875143184421534</v>
+      </c>
+      <c r="H30">
+        <v>-2.875143184421534</v>
+      </c>
+      <c r="I30">
+        <v>-5.246277205040092</v>
+      </c>
+      <c r="J30">
+        <v>-5.246277205040092</v>
+      </c>
       <c r="K30">
-        <v>-0.459</v>
+        <v>-3.53</v>
+      </c>
+      <c r="L30">
+        <v>-4.043528064146621</v>
       </c>
       <c r="M30">
-        <v>2.91</v>
+        <v>-0</v>
       </c>
       <c r="N30">
-        <v>0.01275756247259974</v>
+        <v>-0</v>
       </c>
       <c r="O30">
-        <v>-6.339869281045751</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>-0</v>
@@ -3869,165 +4031,61 @@
         <v>0</v>
       </c>
       <c r="S30">
-        <v>2.91</v>
-      </c>
-      <c r="T30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>19.8</v>
+        <v>0.285</v>
       </c>
       <c r="V30">
-        <v>0.08680403331871986</v>
+        <v>0.285</v>
       </c>
       <c r="X30">
-        <v>0.07245421904070486</v>
+        <v>0.07785688373015791</v>
       </c>
       <c r="AB30">
-        <v>0.07245421904070486</v>
+        <v>0.08718199210592358</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="AG30">
-        <v>-19.8</v>
+        <v>0.548</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>0.4544462629569013</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>0.04619309044529474</v>
       </c>
       <c r="AJ30">
-        <v>-0.09505520883341335</v>
+        <v>0.3540051679586563</v>
       </c>
       <c r="AK30">
-        <v>-0.09840954274353877</v>
+        <v>0.03087671850349336</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AM30">
-        <v>-0.27</v>
+        <v>0.133</v>
+      </c>
+      <c r="AN30">
+        <v>-0.373542600896861</v>
+      </c>
+      <c r="AO30">
+        <v>-34.43609022556391</v>
+      </c>
+      <c r="AP30">
+        <v>-0.2457399103139014</v>
       </c>
       <c r="AQ30">
-        <v>0.5592592592592592</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Katalysen Ventures AB (publ) (NGM:KAV)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>-1.238805970149254</v>
-      </c>
-      <c r="H31">
-        <v>-1.238805970149254</v>
-      </c>
-      <c r="I31">
-        <v>-2.885572139303482</v>
-      </c>
-      <c r="J31">
-        <v>-2.885572139303482</v>
-      </c>
-      <c r="K31">
-        <v>-1.27</v>
-      </c>
-      <c r="L31">
-        <v>-3.159203980099502</v>
-      </c>
-      <c r="M31">
-        <v>-0</v>
-      </c>
-      <c r="N31">
-        <v>-0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>-0</v>
-      </c>
-      <c r="Q31">
-        <v>-0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0.518</v>
-      </c>
-      <c r="V31">
-        <v>0.0343046357615894</v>
-      </c>
-      <c r="X31">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AB31">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>-0.518</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AI31">
-        <v>0</v>
-      </c>
-      <c r="AJ31">
-        <v>-0.0355232478398025</v>
-      </c>
-      <c r="AK31">
-        <v>-0.06143263757115751</v>
-      </c>
-      <c r="AL31">
-        <v>0.003</v>
-      </c>
-      <c r="AM31">
-        <v>-0.03</v>
-      </c>
-      <c r="AN31">
-        <v>-0</v>
-      </c>
-      <c r="AO31">
-        <v>-386.6666666666666</v>
-      </c>
-      <c r="AP31">
-        <v>0.4543859649122808</v>
-      </c>
-      <c r="AQ31">
-        <v>38.66666666666666</v>
+        <v>-34.43609022556391</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.349</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="E2">
-        <v>0.12</v>
+        <v>0.2215</v>
       </c>
       <c r="F2">
-        <v>0.267</v>
+        <v>0.1555</v>
       </c>
       <c r="G2">
-        <v>0.5116210026295699</v>
+        <v>0.2802127351612188</v>
       </c>
       <c r="H2">
-        <v>0.5116210026295699</v>
+        <v>0.2802067849531137</v>
       </c>
       <c r="I2">
-        <v>0.3399779455424548</v>
+        <v>0.2726559708677811</v>
       </c>
       <c r="J2">
-        <v>0.2483477728470342</v>
+        <v>0.2681475946850833</v>
       </c>
       <c r="K2">
-        <v>312.8</v>
+        <v>1423.695</v>
       </c>
       <c r="L2">
-        <v>0.1326660446178641</v>
+        <v>0.1970065471661926</v>
       </c>
       <c r="M2">
-        <v>467.6</v>
+        <v>591.8332</v>
       </c>
       <c r="N2">
-        <v>0.0143114234295998</v>
+        <v>0.01532019825574909</v>
       </c>
       <c r="O2">
-        <v>1.494884910485933</v>
+        <v>0.415702239594857</v>
       </c>
       <c r="P2">
-        <v>361.5</v>
+        <v>472.7722</v>
       </c>
       <c r="Q2">
-        <v>0.01106411370787067</v>
+        <v>0.01223818439689875</v>
       </c>
       <c r="R2">
-        <v>1.155690537084399</v>
+        <v>0.3320740748545158</v>
       </c>
       <c r="S2">
-        <v>106.1</v>
+        <v>119.061</v>
       </c>
       <c r="T2">
-        <v>0.2269033361847733</v>
+        <v>0.201173235972568</v>
       </c>
       <c r="U2">
-        <v>863.6</v>
+        <v>1522.214</v>
       </c>
       <c r="V2">
-        <v>0.02643144840419671</v>
+        <v>0.03940404199642203</v>
       </c>
       <c r="W2">
-        <v>0.04785801713586291</v>
+        <v>-0.05361790733992713</v>
       </c>
       <c r="X2">
-        <v>0.06922044313189474</v>
+        <v>0.06792854833913502</v>
       </c>
       <c r="Y2">
-        <v>-0.02136242599603182</v>
+        <v>-0.1215464556790621</v>
       </c>
       <c r="Z2">
-        <v>0.3959960363447037</v>
+        <v>0.6375379480677407</v>
       </c>
       <c r="AA2">
-        <v>0.09834473368246037</v>
+        <v>-0.04459047172025346</v>
       </c>
       <c r="AB2">
-        <v>0.06750559275434047</v>
+        <v>0.06792854833913502</v>
       </c>
       <c r="AC2">
-        <v>0.0308391409281199</v>
+        <v>-0.1123965242970474</v>
       </c>
       <c r="AD2">
-        <v>2374.4</v>
+        <v>3838.086</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2374.4</v>
+        <v>3838.086</v>
       </c>
       <c r="AG2">
-        <v>1510.8</v>
+        <v>2315.872</v>
       </c>
       <c r="AH2">
-        <v>0.06774786290644724</v>
+        <v>0.0903738341259586</v>
       </c>
       <c r="AI2">
-        <v>0.2282440473329553</v>
+        <v>0.197340579070048</v>
       </c>
       <c r="AJ2">
-        <v>0.04419611514158672</v>
+        <v>0.05655809533457355</v>
       </c>
       <c r="AK2">
-        <v>0.1583764007841247</v>
+        <v>0.1291846769133554</v>
       </c>
       <c r="AL2">
-        <v>61.2</v>
+        <v>166.577</v>
       </c>
       <c r="AM2">
-        <v>21</v>
+        <v>96.31399999999999</v>
       </c>
       <c r="AN2">
-        <v>1.948465452158215</v>
+        <v>1.691807831158012</v>
       </c>
       <c r="AO2">
-        <v>13.09803921568627</v>
+        <v>11.8286798297484</v>
       </c>
       <c r="AP2">
-        <v>1.239783357951748</v>
+        <v>1.020824021546043</v>
       </c>
       <c r="AQ2">
-        <v>38.17142857142857</v>
+        <v>20.45793965570945</v>
       </c>
     </row>
     <row r="3">
@@ -716,133 +716,3305 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bure Equity AB (publ) (OM:BURE)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.285</v>
+      </c>
+      <c r="E3">
+        <v>0.323</v>
+      </c>
+      <c r="G3">
+        <v>0.4748361069087242</v>
+      </c>
+      <c r="H3">
+        <v>0.4748361069087242</v>
+      </c>
+      <c r="I3">
+        <v>0.9904185577407968</v>
+      </c>
+      <c r="J3">
+        <v>0.9904185577407968</v>
+      </c>
+      <c r="K3">
+        <v>986.1</v>
+      </c>
+      <c r="L3">
+        <v>0.9945537065052951</v>
+      </c>
+      <c r="M3">
+        <v>34.799</v>
+      </c>
+      <c r="N3">
+        <v>0.01360451933226475</v>
+      </c>
+      <c r="O3">
+        <v>0.0352895243890072</v>
+      </c>
+      <c r="P3">
+        <v>34.7</v>
+      </c>
+      <c r="Q3">
+        <v>0.01356581570819813</v>
+      </c>
+      <c r="R3">
+        <v>0.03518912889159315</v>
+      </c>
+      <c r="S3">
+        <v>0.09899999999999665</v>
+      </c>
+      <c r="T3">
+        <v>0.00284490933647509</v>
+      </c>
+      <c r="U3">
+        <v>53.5</v>
+      </c>
+      <c r="V3">
+        <v>0.02091559482387896</v>
+      </c>
+      <c r="W3">
+        <v>0.665743991358358</v>
+      </c>
+      <c r="X3">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y3">
+        <v>0.5978154430192231</v>
+      </c>
+      <c r="Z3">
+        <v>0.6965348882137024</v>
+      </c>
+      <c r="AA3">
+        <v>0.6898610794007621</v>
+      </c>
+      <c r="AB3">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC3">
+        <v>0.6219325310616272</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-53.5</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.02136240217217697</v>
+      </c>
+      <c r="AK3">
+        <v>-0.02133599202392822</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>-3.65</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-0.0544529262086514</v>
+      </c>
+      <c r="AQ3">
+        <v>-269.041095890411</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Linc AB (OM:LINC)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.9928940568475451</v>
+      </c>
+      <c r="J4">
+        <v>0.9928940568475451</v>
+      </c>
+      <c r="K4">
+        <v>155.9</v>
+      </c>
+      <c r="L4">
+        <v>1.007105943152455</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>153.6</v>
+      </c>
+      <c r="V4">
+        <v>0.3397478433974784</v>
+      </c>
+      <c r="W4">
+        <v>0.5591822094691535</v>
+      </c>
+      <c r="X4">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y4">
+        <v>0.4912536611300185</v>
+      </c>
+      <c r="Z4">
+        <v>0.6892252894033838</v>
+      </c>
+      <c r="AA4">
+        <v>0.684327693677649</v>
+      </c>
+      <c r="AB4">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC4">
+        <v>0.616399145338514</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-153.6</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.514572864321608</v>
+      </c>
+      <c r="AK4">
+        <v>-0.5087777409738324</v>
+      </c>
+      <c r="AL4">
+        <v>0.493</v>
+      </c>
+      <c r="AM4">
+        <v>-1.447</v>
+      </c>
+      <c r="AO4">
+        <v>311.7647058823529</v>
+      </c>
+      <c r="AQ4">
+        <v>-106.2197650310988</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AB Traction (OM:TRAC B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.9817073170731709</v>
+      </c>
+      <c r="J5">
+        <v>0.9759908536585368</v>
+      </c>
+      <c r="K5">
+        <v>64</v>
+      </c>
+      <c r="L5">
+        <v>0.9756097560975611</v>
+      </c>
+      <c r="M5">
+        <v>15.2</v>
+      </c>
+      <c r="N5">
+        <v>0.04324324324324324</v>
+      </c>
+      <c r="O5">
+        <v>0.2375</v>
+      </c>
+      <c r="P5">
+        <v>15.2</v>
+      </c>
+      <c r="Q5">
+        <v>0.04324324324324324</v>
+      </c>
+      <c r="R5">
+        <v>0.2375</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>42.1</v>
+      </c>
+      <c r="V5">
+        <v>0.1197724039829303</v>
+      </c>
+      <c r="W5">
+        <v>0.1921344941459021</v>
+      </c>
+      <c r="X5">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y5">
+        <v>0.1242059458067671</v>
+      </c>
+      <c r="Z5">
+        <v>0.2084524944391483</v>
+      </c>
+      <c r="AA5">
+        <v>0.2034477279949158</v>
+      </c>
+      <c r="AB5">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC5">
+        <v>0.1355191796557808</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-42.1</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1360698125404008</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1154690071311026</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ratos AB (publ) (OM:RATO B)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0548</v>
+      </c>
+      <c r="E6">
+        <v>0.777</v>
+      </c>
+      <c r="F6">
+        <v>0.044</v>
+      </c>
+      <c r="G6">
+        <v>0.06347962382445141</v>
+      </c>
+      <c r="H6">
+        <v>0.06347962382445141</v>
+      </c>
+      <c r="I6">
+        <v>0.03821316614420063</v>
+      </c>
+      <c r="J6">
+        <v>0.03197762095511366</v>
+      </c>
+      <c r="K6">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="L6">
+        <v>0.02959247648902821</v>
+      </c>
+      <c r="M6">
+        <v>40.497</v>
+      </c>
+      <c r="N6">
+        <v>0.04223276671185733</v>
+      </c>
+      <c r="O6">
+        <v>0.4289936440677966</v>
+      </c>
+      <c r="P6">
+        <v>40.3</v>
+      </c>
+      <c r="Q6">
+        <v>0.04202732297424132</v>
+      </c>
+      <c r="R6">
+        <v>0.4269067796610169</v>
+      </c>
+      <c r="S6">
+        <v>0.1970000000000027</v>
+      </c>
+      <c r="T6">
+        <v>0.004864557868484153</v>
+      </c>
+      <c r="U6">
+        <v>209.1</v>
+      </c>
+      <c r="V6">
+        <v>0.2180623631244134</v>
+      </c>
+      <c r="W6">
+        <v>0.08296712954825101</v>
+      </c>
+      <c r="X6">
+        <v>0.08541432923594283</v>
+      </c>
+      <c r="Y6">
+        <v>-0.002447199687691817</v>
+      </c>
+      <c r="Z6">
+        <v>5.405863412980854</v>
+      </c>
+      <c r="AA6">
+        <v>0.1728666511554188</v>
+      </c>
+      <c r="AB6">
+        <v>0.06471116222263515</v>
+      </c>
+      <c r="AC6">
+        <v>0.1081554889327836</v>
+      </c>
+      <c r="AD6">
+        <v>954.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>954.3</v>
+      </c>
+      <c r="AG6">
+        <v>745.1999999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.4987978256324483</v>
+      </c>
+      <c r="AI6">
+        <v>0.3987881320518178</v>
+      </c>
+      <c r="AJ6">
+        <v>0.4372982806173347</v>
+      </c>
+      <c r="AK6">
+        <v>0.3412244150373185</v>
+      </c>
+      <c r="AL6">
+        <v>58.8</v>
+      </c>
+      <c r="AM6">
+        <v>51.5</v>
+      </c>
+      <c r="AN6">
+        <v>5.172357723577235</v>
+      </c>
+      <c r="AO6">
+        <v>2.073129251700681</v>
+      </c>
+      <c r="AP6">
+        <v>4.039024390243902</v>
+      </c>
+      <c r="AQ6">
+        <v>2.366990291262136</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Stockwik Förvaltning AB (publ) (OM:STWK)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.269</v>
+      </c>
+      <c r="G7">
+        <v>0.1050724637681159</v>
+      </c>
+      <c r="H7">
+        <v>0.1050724637681159</v>
+      </c>
+      <c r="I7">
+        <v>0.04794685990338165</v>
+      </c>
+      <c r="J7">
+        <v>0.04794685990338165</v>
+      </c>
+      <c r="K7">
+        <v>-2.58</v>
+      </c>
+      <c r="L7">
+        <v>-0.03115942028985507</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2.2</v>
+      </c>
+      <c r="V7">
+        <v>0.2261048304213772</v>
+      </c>
+      <c r="W7">
+        <v>-0.118348623853211</v>
+      </c>
+      <c r="X7">
+        <v>0.1457569043651242</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2641055282183352</v>
+      </c>
+      <c r="Z7">
+        <v>2.979489024829075</v>
+      </c>
+      <c r="AA7">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="AB7">
+        <v>0.06428566343881617</v>
+      </c>
+      <c r="AC7">
+        <v>0.07857147941832671</v>
+      </c>
+      <c r="AD7">
+        <v>43.1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>43.1</v>
+      </c>
+      <c r="AG7">
+        <v>40.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.8158243422297937</v>
+      </c>
+      <c r="AI7">
+        <v>0.6723868954758191</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8078214497333597</v>
+      </c>
+      <c r="AK7">
+        <v>0.6607431340872375</v>
+      </c>
+      <c r="AL7">
+        <v>3.98</v>
+      </c>
+      <c r="AM7">
+        <v>3.674</v>
+      </c>
+      <c r="AN7">
+        <v>4.73106476399561</v>
+      </c>
+      <c r="AO7">
+        <v>0.9974874371859297</v>
+      </c>
+      <c r="AP7">
+        <v>4.489571899012075</v>
+      </c>
+      <c r="AQ7">
+        <v>1.08056614044638</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VEF AB (publ) (OM:VEFAB)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="E8">
+        <v>0.0336</v>
+      </c>
+      <c r="G8">
+        <v>0.9955686853766618</v>
+      </c>
+      <c r="H8">
+        <v>0.9955686853766618</v>
+      </c>
+      <c r="I8">
+        <v>0.8951255539143279</v>
+      </c>
+      <c r="J8">
+        <v>0.888029836951437</v>
+      </c>
+      <c r="K8">
+        <v>51.7</v>
+      </c>
+      <c r="L8">
+        <v>0.7636632200886263</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.04397880539499037</v>
+      </c>
+      <c r="W8">
+        <v>0.1223089661698604</v>
+      </c>
+      <c r="X8">
+        <v>0.07122082011722522</v>
+      </c>
+      <c r="Y8">
+        <v>0.05108814605263522</v>
+      </c>
+      <c r="Z8">
+        <v>0.162752121547227</v>
+      </c>
+      <c r="AA8">
+        <v>0.1445287399610844</v>
+      </c>
+      <c r="AB8">
+        <v>0.06691063381880713</v>
+      </c>
+      <c r="AC8">
+        <v>0.07761810614227729</v>
+      </c>
+      <c r="AD8">
+        <v>38.9</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>38.9</v>
+      </c>
+      <c r="AG8">
+        <v>29.77</v>
+      </c>
+      <c r="AH8">
+        <v>0.1578093306288032</v>
+      </c>
+      <c r="AI8">
+        <v>0.07569566063436467</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1254160171883557</v>
+      </c>
+      <c r="AK8">
+        <v>0.05897735602353547</v>
+      </c>
+      <c r="AL8">
+        <v>7.11</v>
+      </c>
+      <c r="AM8">
+        <v>6.384</v>
+      </c>
+      <c r="AN8">
+        <v>0.6408566721581548</v>
+      </c>
+      <c r="AO8">
+        <v>8.523206751054852</v>
+      </c>
+      <c r="AP8">
+        <v>0.4904448105436572</v>
+      </c>
+      <c r="AQ8">
+        <v>9.492481203007518</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>EQT AB (publ) (OM:EQT)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D9">
         <v>0.349</v>
       </c>
-      <c r="E3">
+      <c r="E9">
         <v>0.12</v>
       </c>
-      <c r="F3">
+      <c r="F9">
         <v>0.267</v>
       </c>
-      <c r="G3">
+      <c r="G9">
         <v>0.5116210026295699</v>
       </c>
-      <c r="H3">
+      <c r="H9">
         <v>0.5116210026295699</v>
       </c>
-      <c r="I3">
+      <c r="I9">
         <v>0.3399779455424548</v>
       </c>
-      <c r="J3">
+      <c r="J9">
         <v>0.2483477728470342</v>
       </c>
-      <c r="K3">
+      <c r="K9">
         <v>312.8</v>
       </c>
-      <c r="L3">
+      <c r="L9">
         <v>0.1326660446178641</v>
       </c>
-      <c r="M3">
+      <c r="M9">
         <v>467.6</v>
       </c>
-      <c r="N3">
+      <c r="N9">
         <v>0.0143114234295998</v>
       </c>
-      <c r="O3">
+      <c r="O9">
         <v>1.494884910485933</v>
       </c>
-      <c r="P3">
+      <c r="P9">
         <v>361.5</v>
       </c>
-      <c r="Q3">
+      <c r="Q9">
         <v>0.01106411370787067</v>
       </c>
-      <c r="R3">
+      <c r="R9">
         <v>1.155690537084399</v>
       </c>
-      <c r="S3">
+      <c r="S9">
         <v>106.1</v>
       </c>
-      <c r="T3">
+      <c r="T9">
         <v>0.2269033361847733</v>
       </c>
-      <c r="U3">
+      <c r="U9">
         <v>863.6</v>
       </c>
-      <c r="V3">
+      <c r="V9">
         <v>0.02643144840419671</v>
       </c>
-      <c r="W3">
+      <c r="W9">
         <v>0.04785801713586291</v>
       </c>
-      <c r="X3">
-        <v>0.06922044313189474</v>
-      </c>
-      <c r="Y3">
-        <v>-0.02136242599603182</v>
-      </c>
-      <c r="Z3">
+      <c r="X9">
+        <v>0.06920538586928496</v>
+      </c>
+      <c r="Y9">
+        <v>-0.02134736873342204</v>
+      </c>
+      <c r="Z9">
         <v>0.3959960363447037</v>
       </c>
-      <c r="AA3">
+      <c r="AA9">
         <v>0.09834473368246037</v>
       </c>
-      <c r="AB3">
-        <v>0.06750559275434047</v>
-      </c>
-      <c r="AC3">
-        <v>0.0308391409281199</v>
-      </c>
-      <c r="AD3">
+      <c r="AB9">
+        <v>0.06749155558909373</v>
+      </c>
+      <c r="AC9">
+        <v>0.03085317809336664</v>
+      </c>
+      <c r="AD9">
         <v>2374.4</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
         <v>2374.4</v>
       </c>
-      <c r="AG3">
+      <c r="AG9">
         <v>1510.8</v>
       </c>
-      <c r="AH3">
+      <c r="AH9">
         <v>0.06774786290644724</v>
       </c>
-      <c r="AI3">
+      <c r="AI9">
         <v>0.2282440473329553</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ9">
         <v>0.04419611514158672</v>
       </c>
-      <c r="AK3">
+      <c r="AK9">
         <v>0.1583764007841247</v>
       </c>
-      <c r="AL3">
+      <c r="AL9">
         <v>61.2</v>
       </c>
-      <c r="AM3">
+      <c r="AM9">
         <v>21</v>
       </c>
-      <c r="AN3">
+      <c r="AN9">
         <v>1.948465452158215</v>
       </c>
-      <c r="AO3">
+      <c r="AO9">
         <v>13.09803921568627</v>
       </c>
-      <c r="AP3">
+      <c r="AP9">
         <v>1.239783357951748</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ9">
         <v>38.17142857142857</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Navigo Invest AB (publ) (OM:NAVIGO STAM)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.104</v>
+      </c>
+      <c r="G10">
+        <v>0.06873462214411248</v>
+      </c>
+      <c r="H10">
+        <v>0.06836555360281195</v>
+      </c>
+      <c r="I10">
+        <v>0.03268892794376099</v>
+      </c>
+      <c r="J10">
+        <v>0.03268892794376099</v>
+      </c>
+      <c r="K10">
+        <v>-3.18</v>
+      </c>
+      <c r="L10">
+        <v>-0.05588752196836556</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>2.83</v>
+      </c>
+      <c r="V10">
+        <v>0.09041533546325879</v>
+      </c>
+      <c r="W10">
+        <v>-0.0228448275862069</v>
+      </c>
+      <c r="X10">
+        <v>0.0754505580167408</v>
+      </c>
+      <c r="Y10">
+        <v>-0.0982953856029477</v>
+      </c>
+      <c r="Z10">
+        <v>0.9516641578859344</v>
+      </c>
+      <c r="AA10">
+        <v>0.03110888108379329</v>
+      </c>
+      <c r="AB10">
+        <v>0.06658996299606235</v>
+      </c>
+      <c r="AC10">
+        <v>-0.03548108191226906</v>
+      </c>
+      <c r="AD10">
+        <v>13.4</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>13.4</v>
+      </c>
+      <c r="AG10">
+        <v>10.57</v>
+      </c>
+      <c r="AH10">
+        <v>0.2997762863534675</v>
+      </c>
+      <c r="AI10">
+        <v>0.08292079207920793</v>
+      </c>
+      <c r="AJ10">
+        <v>0.2524480534989252</v>
+      </c>
+      <c r="AK10">
+        <v>0.06657428985324684</v>
+      </c>
+      <c r="AL10">
+        <v>2.87</v>
+      </c>
+      <c r="AM10">
+        <v>2.87</v>
+      </c>
+      <c r="AN10">
+        <v>5.92920353982301</v>
+      </c>
+      <c r="AO10">
+        <v>0.6480836236933798</v>
+      </c>
+      <c r="AP10">
+        <v>4.676991150442478</v>
+      </c>
+      <c r="AQ10">
+        <v>0.6480836236933798</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Seafire AB (publ) (OM:SEAF)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.4320000000000001</v>
+      </c>
+      <c r="G11">
+        <v>0.145534729878721</v>
+      </c>
+      <c r="H11">
+        <v>0.145534729878721</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>-6.31</v>
+      </c>
+      <c r="L11">
+        <v>-0.06957001102535831</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>4.14</v>
+      </c>
+      <c r="V11">
+        <v>0.1925581395348837</v>
+      </c>
+      <c r="W11">
+        <v>-0.09225146198830408</v>
+      </c>
+      <c r="X11">
+        <v>0.08737820432398628</v>
+      </c>
+      <c r="Y11">
+        <v>-0.1796296663122904</v>
+      </c>
+      <c r="Z11">
+        <v>3.472434915773353</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06453965900586546</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06453965900586546</v>
+      </c>
+      <c r="AD11">
+        <v>23.8</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>23.8</v>
+      </c>
+      <c r="AG11">
+        <v>19.66</v>
+      </c>
+      <c r="AH11">
+        <v>0.5253863134657837</v>
+      </c>
+      <c r="AI11">
+        <v>0.262114537444934</v>
+      </c>
+      <c r="AJ11">
+        <v>0.4776482021379981</v>
+      </c>
+      <c r="AK11">
+        <v>0.2268636048926841</v>
+      </c>
+      <c r="AL11">
+        <v>2.46</v>
+      </c>
+      <c r="AM11">
+        <v>2.46</v>
+      </c>
+      <c r="AN11">
+        <v>2.567421790722762</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>2.120819848975189</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Coeli Private Equity AB (publ) (NGM:CPE I)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.416</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>-0.6556372549019609</v>
+      </c>
+      <c r="J12">
+        <v>-0.6556372549019609</v>
+      </c>
+      <c r="K12">
+        <v>-0.773</v>
+      </c>
+      <c r="L12">
+        <v>-0.9473039215686275</v>
+      </c>
+      <c r="M12">
+        <v>1.22</v>
+      </c>
+      <c r="N12">
+        <v>0.01725601131541726</v>
+      </c>
+      <c r="O12">
+        <v>-1.578266494178525</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>1.22</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>0.927</v>
+      </c>
+      <c r="V12">
+        <v>0.01311173974540311</v>
+      </c>
+      <c r="W12">
+        <v>-0.006048513302034429</v>
+      </c>
+      <c r="X12">
+        <v>0.06804584779887987</v>
+      </c>
+      <c r="Y12">
+        <v>-0.0740943611009143</v>
+      </c>
+      <c r="Z12">
+        <v>0.006404772183195321</v>
+      </c>
+      <c r="AA12">
+        <v>-0.004199207252462619</v>
+      </c>
+      <c r="AB12">
+        <v>0.06789893539286247</v>
+      </c>
+      <c r="AC12">
+        <v>-0.07209814264532509</v>
+      </c>
+      <c r="AD12">
+        <v>0.472</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0.472</v>
+      </c>
+      <c r="AG12">
+        <v>-0.4550000000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0.006631821502838195</v>
+      </c>
+      <c r="AI12">
+        <v>0.003671094795134244</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.006477329347284505</v>
+      </c>
+      <c r="AK12">
+        <v>-0.003564573622155197</v>
+      </c>
+      <c r="AL12">
+        <v>0.267</v>
+      </c>
+      <c r="AM12">
+        <v>0.238</v>
+      </c>
+      <c r="AO12">
+        <v>-2.00374531835206</v>
+      </c>
+      <c r="AQ12">
+        <v>-2.247899159663866</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Havsfrun Investment AB (publ) (OM:HAV B)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>-0.1020408163265306</v>
+      </c>
+      <c r="H13">
+        <v>-0.1020408163265306</v>
+      </c>
+      <c r="I13">
+        <v>-0.1315192743764173</v>
+      </c>
+      <c r="J13">
+        <v>-0.1315192743764173</v>
+      </c>
+      <c r="K13">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="L13">
+        <v>0.1564625850340136</v>
+      </c>
+      <c r="M13">
+        <v>1.19</v>
+      </c>
+      <c r="N13">
+        <v>0.08623188405797101</v>
+      </c>
+      <c r="O13">
+        <v>17.2463768115942</v>
+      </c>
+      <c r="P13">
+        <v>1.19</v>
+      </c>
+      <c r="Q13">
+        <v>0.08623188405797101</v>
+      </c>
+      <c r="R13">
+        <v>17.2463768115942</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>5.99</v>
+      </c>
+      <c r="V13">
+        <v>0.4340579710144927</v>
+      </c>
+      <c r="W13">
+        <v>0.006052631578947369</v>
+      </c>
+      <c r="X13">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y13">
+        <v>-0.06187591676018765</v>
+      </c>
+      <c r="Z13">
+        <v>0.1078239608801956</v>
+      </c>
+      <c r="AA13">
+        <v>-0.01418092909535452</v>
+      </c>
+      <c r="AB13">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC13">
+        <v>-0.08210947743448954</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>-5.99</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.7669654289372599</v>
+      </c>
+      <c r="AK13">
+        <v>-1.149712092130518</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-0.26</v>
+      </c>
+      <c r="AN13">
+        <v>-0</v>
+      </c>
+      <c r="AP13">
+        <v>105.0877192982456</v>
+      </c>
+      <c r="AQ13">
+        <v>0.2230769230769231</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Transferator AB (publ) (NGM:TRAN A)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.08380000000000001</v>
+      </c>
+      <c r="G14">
+        <v>0.123728813559322</v>
+      </c>
+      <c r="H14">
+        <v>0.123728813559322</v>
+      </c>
+      <c r="I14">
+        <v>-0.02050847457627119</v>
+      </c>
+      <c r="J14">
+        <v>-0.02050847457627119</v>
+      </c>
+      <c r="K14">
+        <v>3.42</v>
+      </c>
+      <c r="L14">
+        <v>0.5796610169491525</v>
+      </c>
+      <c r="M14">
+        <v>3.9442</v>
+      </c>
+      <c r="N14">
+        <v>0.2179116022099448</v>
+      </c>
+      <c r="O14">
+        <v>1.15327485380117</v>
+      </c>
+      <c r="P14">
+        <v>3.9442</v>
+      </c>
+      <c r="Q14">
+        <v>0.2179116022099448</v>
+      </c>
+      <c r="R14">
+        <v>1.15327485380117</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.7066115702479339</v>
+      </c>
+      <c r="X14">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y14">
+        <v>0.6386830219087989</v>
+      </c>
+      <c r="Z14">
+        <v>0.9348756140072889</v>
+      </c>
+      <c r="AA14">
+        <v>-0.0191728727618444</v>
+      </c>
+      <c r="AB14">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC14">
+        <v>-0.08710142110097942</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0.21</v>
+      </c>
+      <c r="AM14">
+        <v>-1.29</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>-0.5761904761904761</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0.09379844961240309</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Abelco Investment Group AB (NGM:ABIG)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>-2.343511450381679</v>
+      </c>
+      <c r="H15">
+        <v>-2.343511450381679</v>
+      </c>
+      <c r="I15">
+        <v>-2.587786259541985</v>
+      </c>
+      <c r="J15">
+        <v>-2.587786259541985</v>
+      </c>
+      <c r="K15">
+        <v>-7.61</v>
+      </c>
+      <c r="L15">
+        <v>-58.09160305343512</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0.017</v>
+      </c>
+      <c r="V15">
+        <v>0.009392265193370166</v>
+      </c>
+      <c r="W15">
+        <v>-0.7918834547346515</v>
+      </c>
+      <c r="X15">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y15">
+        <v>-0.8598120030737865</v>
+      </c>
+      <c r="Z15">
+        <v>0.01074122663168252</v>
+      </c>
+      <c r="AA15">
+        <v>-0.02779599868809446</v>
+      </c>
+      <c r="AB15">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC15">
+        <v>-0.09572454702722948</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>-0.017</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.009481316229782486</v>
+      </c>
+      <c r="AK15">
+        <v>-0.00451767207015679</v>
+      </c>
+      <c r="AL15">
+        <v>0.475</v>
+      </c>
+      <c r="AM15">
+        <v>0.475</v>
+      </c>
+      <c r="AO15">
+        <v>-0.7136842105263159</v>
+      </c>
+      <c r="AQ15">
+        <v>-0.7136842105263159</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Investment AB Spiltan (NGM:SPLTN)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K16">
+        <v>-37.5</v>
+      </c>
+      <c r="M16">
+        <v>3.06</v>
+      </c>
+      <c r="N16">
+        <v>0.004911717495987159</v>
+      </c>
+      <c r="O16">
+        <v>-0.08160000000000001</v>
+      </c>
+      <c r="P16">
+        <v>3.06</v>
+      </c>
+      <c r="Q16">
+        <v>0.004911717495987159</v>
+      </c>
+      <c r="R16">
+        <v>-0.08160000000000001</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>3.84</v>
+      </c>
+      <c r="V16">
+        <v>0.006163723916532905</v>
+      </c>
+      <c r="W16">
+        <v>-0.04488330341113106</v>
+      </c>
+      <c r="X16">
+        <v>0.06816488407694411</v>
+      </c>
+      <c r="Y16">
+        <v>-0.1130481874880752</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>-0.04459047172025346</v>
+      </c>
+      <c r="AB16">
+        <v>0.06780605257679398</v>
+      </c>
+      <c r="AC16">
+        <v>-0.1123965242970474</v>
+      </c>
+      <c r="AD16">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="AG16">
+        <v>4.540000000000001</v>
+      </c>
+      <c r="AH16">
+        <v>0.01327251417529855</v>
+      </c>
+      <c r="AI16">
+        <v>0.009640161973127188</v>
+      </c>
+      <c r="AJ16">
+        <v>0.007234598591324858</v>
+      </c>
+      <c r="AK16">
+        <v>0.005245886485487152</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-2.01</v>
+      </c>
+      <c r="AN16">
+        <v>-0.2211081794195251</v>
+      </c>
+      <c r="AP16">
+        <v>-0.1197889182058048</v>
+      </c>
+      <c r="AQ16">
+        <v>18.90547263681592</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>First Venture Sweden AB (publ) (OM:FIRST B)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K17">
+        <v>-3.36</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.01421404682274247</v>
+      </c>
+      <c r="W17">
+        <v>-0.1777777777777778</v>
+      </c>
+      <c r="X17">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y17">
+        <v>-0.2457063261169128</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>-0.06218232940413106</v>
+      </c>
+      <c r="AB17">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC17">
+        <v>-0.1301108777432661</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.01441899915182358</v>
+      </c>
+      <c r="AK17">
+        <v>-0.005055010407374369</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-0.133</v>
+      </c>
+      <c r="AQ17">
+        <v>8.646616541353382</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Catella AB (publ) (OM:CAT B)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.0864</v>
+      </c>
+      <c r="G18">
+        <v>-0.08653846153846154</v>
+      </c>
+      <c r="H18">
+        <v>-0.08653846153846154</v>
+      </c>
+      <c r="I18">
+        <v>-0.1600274725274725</v>
+      </c>
+      <c r="J18">
+        <v>-0.1600274725274725</v>
+      </c>
+      <c r="K18">
+        <v>-10.3</v>
+      </c>
+      <c r="L18">
+        <v>-0.07074175824175825</v>
+      </c>
+      <c r="M18">
+        <v>7.89</v>
+      </c>
+      <c r="N18">
+        <v>0.0355565570076611</v>
+      </c>
+      <c r="O18">
+        <v>-0.7660194174757281</v>
+      </c>
+      <c r="P18">
+        <v>7.89</v>
+      </c>
+      <c r="Q18">
+        <v>0.0355565570076611</v>
+      </c>
+      <c r="R18">
+        <v>-0.7660194174757281</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>85.7</v>
+      </c>
+      <c r="V18">
+        <v>0.3862100045065345</v>
+      </c>
+      <c r="W18">
+        <v>-0.05361790733992713</v>
+      </c>
+      <c r="X18">
+        <v>0.0913262721388927</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1449441794788198</v>
+      </c>
+      <c r="Z18">
+        <v>0.4401451027811367</v>
+      </c>
+      <c r="AA18">
+        <v>-0.07043530834340993</v>
+      </c>
+      <c r="AB18">
+        <v>0.06424463256208018</v>
+      </c>
+      <c r="AC18">
+        <v>-0.1346799409054901</v>
+      </c>
+      <c r="AD18">
+        <v>295.5</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>295.5</v>
+      </c>
+      <c r="AG18">
+        <v>209.8</v>
+      </c>
+      <c r="AH18">
+        <v>0.5711248550444531</v>
+      </c>
+      <c r="AI18">
+        <v>0.6038005721291377</v>
+      </c>
+      <c r="AJ18">
+        <v>0.4859856381746583</v>
+      </c>
+      <c r="AK18">
+        <v>0.5196928412187267</v>
+      </c>
+      <c r="AL18">
+        <v>20</v>
+      </c>
+      <c r="AM18">
+        <v>13.39</v>
+      </c>
+      <c r="AN18">
+        <v>-15.2319587628866</v>
+      </c>
+      <c r="AO18">
+        <v>-1.165</v>
+      </c>
+      <c r="AP18">
+        <v>-10.81443298969072</v>
+      </c>
+      <c r="AQ18">
+        <v>-1.740104555638536</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Katalysen Ventures AB (publ) (NGM:KAV)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>-20.95238095238095</v>
+      </c>
+      <c r="H19">
+        <v>-20.95238095238095</v>
+      </c>
+      <c r="I19">
+        <v>-10.80952380952381</v>
+      </c>
+      <c r="J19">
+        <v>-10.80952380952381</v>
+      </c>
+      <c r="K19">
+        <v>-3.5</v>
+      </c>
+      <c r="L19">
+        <v>-55.55555555555556</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0.007</v>
+      </c>
+      <c r="V19">
+        <v>0.0007494646680942184</v>
+      </c>
+      <c r="W19">
+        <v>-0.4516129032258064</v>
+      </c>
+      <c r="X19">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y19">
+        <v>-0.5195414515649415</v>
+      </c>
+      <c r="Z19">
+        <v>0.008173326414115206</v>
+      </c>
+      <c r="AA19">
+        <v>-0.08834976647638818</v>
+      </c>
+      <c r="AB19">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC19">
+        <v>-0.1562783148155232</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>-0.007</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.0007500267866709525</v>
+      </c>
+      <c r="AK19">
+        <v>-0.00110706942906848</v>
+      </c>
+      <c r="AL19">
+        <v>0.005</v>
+      </c>
+      <c r="AM19">
+        <v>-0.014</v>
+      </c>
+      <c r="AN19">
+        <v>-0</v>
+      </c>
+      <c r="AO19">
+        <v>-136.2</v>
+      </c>
+      <c r="AP19">
+        <v>0.01021897810218978</v>
+      </c>
+      <c r="AQ19">
+        <v>48.64285714285715</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NAXS AB (publ) (OM:NAXS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K20">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="M20">
+        <v>4.64</v>
+      </c>
+      <c r="N20">
+        <v>0.091699604743083</v>
+      </c>
+      <c r="O20">
+        <v>-0.5439624853458382</v>
+      </c>
+      <c r="P20">
+        <v>4.64</v>
+      </c>
+      <c r="Q20">
+        <v>0.091699604743083</v>
+      </c>
+      <c r="R20">
+        <v>-0.5439624853458382</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>21.9</v>
+      </c>
+      <c r="V20">
+        <v>0.4328063241106719</v>
+      </c>
+      <c r="W20">
+        <v>-0.09930151338766005</v>
+      </c>
+      <c r="X20">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y20">
+        <v>-0.1672300617267951</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>-0.1408602150537634</v>
+      </c>
+      <c r="AB20">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC20">
+        <v>-0.2087887633928984</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>-21.9</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.7630662020905922</v>
+      </c>
+      <c r="AK20">
+        <v>-0.3828671328671329</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-0.653</v>
+      </c>
+      <c r="AQ20">
+        <v>14.04287901990812</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VNV Global AB (publ) (OM:VNV)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K21">
+        <v>-136.2</v>
+      </c>
+      <c r="M21">
+        <v>0.015</v>
+      </c>
+      <c r="N21">
+        <v>6.902899217671422E-05</v>
+      </c>
+      <c r="O21">
+        <v>-0.0001101321585903084</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0.015</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>11.9</v>
+      </c>
+      <c r="V21">
+        <v>0.05476300046019328</v>
+      </c>
+      <c r="W21">
+        <v>-0.1917769642354266</v>
+      </c>
+      <c r="X21">
+        <v>0.07480941688099581</v>
+      </c>
+      <c r="Y21">
+        <v>-0.2665863811164224</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>-0.1554809843400447</v>
+      </c>
+      <c r="AB21">
+        <v>0.06611334030502775</v>
+      </c>
+      <c r="AC21">
+        <v>-0.2215943246450724</v>
+      </c>
+      <c r="AD21">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AG21">
+        <v>73.19999999999999</v>
+      </c>
+      <c r="AH21">
+        <v>0.2814153439153439</v>
+      </c>
+      <c r="AI21">
+        <v>0.1290175864160097</v>
+      </c>
+      <c r="AJ21">
+        <v>0.2519793459552495</v>
+      </c>
+      <c r="AK21">
+        <v>0.1130152848540991</v>
+      </c>
+      <c r="AL21">
+        <v>6.7</v>
+      </c>
+      <c r="AM21">
+        <v>4.07</v>
+      </c>
+      <c r="AN21">
+        <v>-0.6802557953637091</v>
+      </c>
+      <c r="AO21">
+        <v>-18.67164179104477</v>
+      </c>
+      <c r="AP21">
+        <v>-0.5851318944844124</v>
+      </c>
+      <c r="AQ21">
+        <v>-30.73710073710073</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Flat Capital AB (publ) (OM:FLAT B)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K22">
+        <v>-4.49</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>8.49</v>
+      </c>
+      <c r="V22">
+        <v>0.1274774774774775</v>
+      </c>
+      <c r="W22">
+        <v>-0.1116915422885572</v>
+      </c>
+      <c r="X22">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1796200906276922</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>-0.2008163265306122</v>
+      </c>
+      <c r="AB22">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC22">
+        <v>-0.2687448748697472</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>-8.49</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.1461022199277233</v>
+      </c>
+      <c r="AK22">
+        <v>-0.2810327706057597</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-0.505</v>
+      </c>
+      <c r="AN22">
+        <v>-0</v>
+      </c>
+      <c r="AP22">
+        <v>1.725609756097561</v>
+      </c>
+      <c r="AQ22">
+        <v>9.742574257425742</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nordic Asia Investment Group 1987 AB (publ) (OM:NAIG B)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K23">
+        <v>-2.96</v>
+      </c>
+      <c r="M23">
+        <v>1.778</v>
+      </c>
+      <c r="N23">
+        <v>0.2389784946236559</v>
+      </c>
+      <c r="O23">
+        <v>-0.6006756756756757</v>
+      </c>
+      <c r="P23">
+        <v>0.348</v>
+      </c>
+      <c r="Q23">
+        <v>0.04677419354838709</v>
+      </c>
+      <c r="R23">
+        <v>-0.1175675675675676</v>
+      </c>
+      <c r="S23">
+        <v>1.43</v>
+      </c>
+      <c r="T23">
+        <v>0.8042744656917886</v>
+      </c>
+      <c r="U23">
+        <v>0.372</v>
+      </c>
+      <c r="V23">
+        <v>0.05</v>
+      </c>
+      <c r="W23">
+        <v>-0.1873417721518987</v>
+      </c>
+      <c r="X23">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y23">
+        <v>-0.2552703204910338</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>-0.2193851346393719</v>
+      </c>
+      <c r="AB23">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC23">
+        <v>-0.287313682978507</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>-0.372</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.05263157894736842</v>
+      </c>
+      <c r="AK23">
+        <v>-0.03145079472438282</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-0.024</v>
+      </c>
+      <c r="AN23">
+        <v>-0</v>
+      </c>
+      <c r="AP23">
+        <v>0.1252525252525253</v>
+      </c>
+      <c r="AQ23">
+        <v>124.5833333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>eBlitz Group AB (publ) (NGM:EBLITZ)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.551</v>
+      </c>
+      <c r="G24">
+        <v>-2.957805907172996</v>
+      </c>
+      <c r="H24">
+        <v>-2.957805907172996</v>
+      </c>
+      <c r="I24">
+        <v>-2.729957805907173</v>
+      </c>
+      <c r="J24">
+        <v>-2.729957805907173</v>
+      </c>
+      <c r="K24">
+        <v>-0.5679999999999999</v>
+      </c>
+      <c r="L24">
+        <v>-2.39662447257384</v>
+      </c>
+      <c r="M24">
+        <v>-0</v>
+      </c>
+      <c r="N24">
+        <v>-0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0.093</v>
+      </c>
+      <c r="V24">
+        <v>0.0372</v>
+      </c>
+      <c r="W24">
+        <v>-0.1931972789115646</v>
+      </c>
+      <c r="X24">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y24">
+        <v>-0.2611258272506996</v>
+      </c>
+      <c r="Z24">
+        <v>0.08383445348425893</v>
+      </c>
+      <c r="AA24">
+        <v>-0.2288645206933145</v>
+      </c>
+      <c r="AB24">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC24">
+        <v>-0.2967930690324495</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>-0.093</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.03863730785209805</v>
+      </c>
+      <c r="AK24">
+        <v>-0.04176021553659632</v>
+      </c>
+      <c r="AL24">
+        <v>0.001</v>
+      </c>
+      <c r="AM24">
+        <v>-0.001</v>
+      </c>
+      <c r="AN24">
+        <v>-0</v>
+      </c>
+      <c r="AO24">
+        <v>-647</v>
+      </c>
+      <c r="AP24">
+        <v>0.1469194312796208</v>
+      </c>
+      <c r="AQ24">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Athanase Innovation AB (publ) (OM:ATIN)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>-0.4651851851851852</v>
+      </c>
+      <c r="H25">
+        <v>-0.4651851851851852</v>
+      </c>
+      <c r="I25">
+        <v>-0.3207407407407408</v>
+      </c>
+      <c r="J25">
+        <v>-0.3207407407407408</v>
+      </c>
+      <c r="K25">
+        <v>-3.19</v>
+      </c>
+      <c r="L25">
+        <v>-0.2362962962962963</v>
+      </c>
+      <c r="M25">
+        <v>10</v>
+      </c>
+      <c r="N25">
+        <v>0.2369668246445497</v>
+      </c>
+      <c r="O25">
+        <v>-3.134796238244514</v>
+      </c>
+      <c r="P25">
+        <v>-0</v>
+      </c>
+      <c r="Q25">
+        <v>-0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>10</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>42</v>
+      </c>
+      <c r="V25">
+        <v>0.995260663507109</v>
+      </c>
+      <c r="W25">
+        <v>-0.04984375</v>
+      </c>
+      <c r="X25">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y25">
+        <v>-0.117772298339135</v>
+      </c>
+      <c r="Z25">
+        <v>0.9163725224002173</v>
+      </c>
+      <c r="AA25">
+        <v>-0.2939180016291068</v>
+      </c>
+      <c r="AB25">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC25">
+        <v>-0.3618465499682418</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>-42</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25">
+        <v>-209.999999999997</v>
+      </c>
+      <c r="AK25">
+        <v>-2.625</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1.68</v>
+      </c>
+      <c r="AN25">
+        <v>-0</v>
+      </c>
+      <c r="AP25">
+        <v>14.09395973154362</v>
+      </c>
+      <c r="AQ25">
+        <v>2.577380952380953</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Northern CapSek Ventures AB (publ) (NGM:CAPS)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>-23.76</v>
+      </c>
+      <c r="H26">
+        <v>-23.76</v>
+      </c>
+      <c r="I26">
+        <v>-39.72</v>
+      </c>
+      <c r="J26">
+        <v>-39.72</v>
+      </c>
+      <c r="K26">
+        <v>-0.113</v>
+      </c>
+      <c r="L26">
+        <v>-4.52</v>
+      </c>
+      <c r="M26">
+        <v>-0</v>
+      </c>
+      <c r="N26">
+        <v>-0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>-0</v>
+      </c>
+      <c r="Q26">
+        <v>-0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>-0.03156424581005587</v>
+      </c>
+      <c r="X26">
+        <v>0.06866535761641422</v>
+      </c>
+      <c r="Y26">
+        <v>-0.1002296034264701</v>
+      </c>
+      <c r="Z26">
+        <v>0.009035056017347307</v>
+      </c>
+      <c r="AA26">
+        <v>-0.358872425009035</v>
+      </c>
+      <c r="AB26">
+        <v>0.06766893950801366</v>
+      </c>
+      <c r="AC26">
+        <v>-0.4265413645170487</v>
+      </c>
+      <c r="AD26">
+        <v>0.026</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0.026</v>
+      </c>
+      <c r="AG26">
+        <v>0.026</v>
+      </c>
+      <c r="AH26">
+        <v>0.04024767801857585</v>
+      </c>
+      <c r="AI26">
+        <v>0.006137865911237016</v>
+      </c>
+      <c r="AJ26">
+        <v>0.04024767801857585</v>
+      </c>
+      <c r="AK26">
+        <v>0.006137865911237016</v>
+      </c>
+      <c r="AL26">
+        <v>0.001</v>
+      </c>
+      <c r="AM26">
+        <v>-0.013</v>
+      </c>
+      <c r="AN26">
+        <v>-0.04297520661157025</v>
+      </c>
+      <c r="AO26">
+        <v>-993</v>
+      </c>
+      <c r="AP26">
+        <v>-0.04297520661157025</v>
+      </c>
+      <c r="AQ26">
+        <v>76.38461538461537</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cardeon AB (publ) (NGM:CARDEO)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>-2.18586387434555</v>
+      </c>
+      <c r="H27">
+        <v>-2.18586387434555</v>
+      </c>
+      <c r="I27">
+        <v>-3.821989528795811</v>
+      </c>
+      <c r="J27">
+        <v>-3.821989528795811</v>
+      </c>
+      <c r="K27">
+        <v>-6.12</v>
+      </c>
+      <c r="L27">
+        <v>-8.010471204188482</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0.135</v>
+      </c>
+      <c r="V27">
+        <v>0.06338028169014086</v>
+      </c>
+      <c r="W27">
+        <v>-0.4467153284671533</v>
+      </c>
+      <c r="X27">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y27">
+        <v>-0.5146438768062883</v>
+      </c>
+      <c r="Z27">
+        <v>0.1369666547149516</v>
+      </c>
+      <c r="AA27">
+        <v>-0.5234851201147365</v>
+      </c>
+      <c r="AB27">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC27">
+        <v>-0.5914136684538714</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>-0.135</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.06766917293233084</v>
+      </c>
+      <c r="AK27">
+        <v>-0.01995565410199556</v>
+      </c>
+      <c r="AL27">
+        <v>0.15</v>
+      </c>
+      <c r="AM27">
+        <v>0.117</v>
+      </c>
+      <c r="AN27">
+        <v>-0</v>
+      </c>
+      <c r="AO27">
+        <v>-19.46666666666667</v>
+      </c>
+      <c r="AP27">
+        <v>0.1097560975609756</v>
+      </c>
+      <c r="AQ27">
+        <v>-24.95726495726496</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>oodash Group AB (publ) (OM:OODA)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>-2.475675675675676</v>
+      </c>
+      <c r="H28">
+        <v>-2.495495495495495</v>
+      </c>
+      <c r="I28">
+        <v>-2.945945945945946</v>
+      </c>
+      <c r="J28">
+        <v>-2.945945945945946</v>
+      </c>
+      <c r="K28">
+        <v>-5.92</v>
+      </c>
+      <c r="L28">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0.013</v>
+      </c>
+      <c r="V28">
+        <v>0.001111111111111111</v>
+      </c>
+      <c r="W28">
+        <v>-0.5238938053097345</v>
+      </c>
+      <c r="X28">
+        <v>0.06899176267297616</v>
+      </c>
+      <c r="Y28">
+        <v>-0.5928855679827106</v>
+      </c>
+      <c r="Z28">
+        <v>0.2190213101815311</v>
+      </c>
+      <c r="AA28">
+        <v>-0.6452249408050511</v>
+      </c>
+      <c r="AB28">
+        <v>0.06767375958041756</v>
+      </c>
+      <c r="AC28">
+        <v>-0.7128987003854687</v>
+      </c>
+      <c r="AD28">
+        <v>0.708</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0.708</v>
+      </c>
+      <c r="AG28">
+        <v>0.695</v>
+      </c>
+      <c r="AH28">
+        <v>0.05705996131528046</v>
+      </c>
+      <c r="AI28">
+        <v>0.1020466993369847</v>
+      </c>
+      <c r="AJ28">
+        <v>0.05607099636950383</v>
+      </c>
+      <c r="AK28">
+        <v>0.1003610108303249</v>
+      </c>
+      <c r="AL28">
+        <v>1.73</v>
+      </c>
+      <c r="AM28">
+        <v>1.726</v>
+      </c>
+      <c r="AN28">
+        <v>-0.5404580152671755</v>
+      </c>
+      <c r="AO28">
+        <v>-1.890173410404624</v>
+      </c>
+      <c r="AP28">
+        <v>-0.5305343511450381</v>
+      </c>
+      <c r="AQ28">
+        <v>-1.894553881807648</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MTI Investment AB (publ) (OM:MTI)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>-4.462151394422311</v>
+      </c>
+      <c r="H29">
+        <v>-4.462151394422311</v>
+      </c>
+      <c r="I29">
+        <v>-4.462151394422311</v>
+      </c>
+      <c r="J29">
+        <v>-4.462151394422311</v>
+      </c>
+      <c r="K29">
+        <v>-1.49</v>
+      </c>
+      <c r="L29">
+        <v>-5.936254980079681</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.545</v>
+      </c>
+      <c r="V29">
+        <v>0.3732876712328768</v>
+      </c>
+      <c r="W29">
+        <v>-0.8465909090909091</v>
+      </c>
+      <c r="X29">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="Y29">
+        <v>-0.914519457430044</v>
+      </c>
+      <c r="Z29">
+        <v>0.4342560553633218</v>
+      </c>
+      <c r="AA29">
+        <v>-1</v>
+      </c>
+      <c r="AB29">
+        <v>0.06792854833913502</v>
+      </c>
+      <c r="AC29">
+        <v>-1.067928548339135</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>-0.545</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AI29">
+        <v>0</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.5956284153005466</v>
+      </c>
+      <c r="AK29">
+        <v>-0.6022099447513813</v>
+      </c>
+      <c r="AL29">
+        <v>0.125</v>
+      </c>
+      <c r="AM29">
+        <v>0.09</v>
+      </c>
+      <c r="AN29">
+        <v>-0</v>
+      </c>
+      <c r="AO29">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="AP29">
+        <v>0.4866071428571428</v>
+      </c>
+      <c r="AQ29">
+        <v>-12.44444444444445</v>
       </c>
     </row>
   </sheetData>
